--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122827606</v>
+        <v>122828815</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>74847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,51 +1041,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529023</v>
+        <v>529024</v>
       </c>
       <c r="R5" t="n">
-        <v>6999322</v>
+        <v>6999406</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,14 +1102,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 12 st skott och 1 st vinterståndare.</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,31 +1130,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122828815</v>
+        <v>122828672</v>
       </c>
       <c r="B6" t="n">
-        <v>74847</v>
+        <v>98347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,38 +1158,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529024</v>
+        <v>529025</v>
       </c>
       <c r="R6" t="n">
-        <v>6999406</v>
+        <v>6999399</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,12 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På sälgstubbe</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122828672</v>
+        <v>122827346</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>79843</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,52 +1284,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529025</v>
+        <v>528959</v>
       </c>
       <c r="R7" t="n">
-        <v>6999399</v>
+        <v>6999360</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,19 +1345,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,22 +1362,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122827346</v>
+        <v>122827285</v>
       </c>
       <c r="B8" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1410,21 +1390,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1434,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528959</v>
+        <v>528951</v>
       </c>
       <c r="R8" t="n">
-        <v>6999360</v>
+        <v>6999355</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1496,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122827285</v>
+        <v>122828769</v>
       </c>
       <c r="B9" t="n">
-        <v>79844</v>
+        <v>79843</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,21 +1492,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1536,10 +1516,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528951</v>
+        <v>529028</v>
       </c>
       <c r="R9" t="n">
-        <v>6999355</v>
+        <v>6999409</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,9 +1549,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,22 +1581,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122828769</v>
+        <v>122828537</v>
       </c>
       <c r="B10" t="n">
-        <v>79843</v>
+        <v>78762</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,21 +1609,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1638,13 +1633,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529028</v>
+        <v>529161</v>
       </c>
       <c r="R10" t="n">
-        <v>6999409</v>
+        <v>6999364</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1671,24 +1666,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,26 +1684,51 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122828537</v>
+        <v>122827718</v>
       </c>
       <c r="B11" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,21 +1741,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1755,13 +1765,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529161</v>
+        <v>529085</v>
       </c>
       <c r="R11" t="n">
-        <v>6999364</v>
+        <v>6999343</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,14 +1798,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,51 +1826,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827718</v>
+        <v>122827187</v>
       </c>
       <c r="B12" t="n">
-        <v>74863</v>
+        <v>98347</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,41 +1854,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529085</v>
+        <v>529024</v>
       </c>
       <c r="R12" t="n">
-        <v>6999343</v>
+        <v>6999326</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1926,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,12 +1936,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal i gammal granskog</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,22 +1951,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122827187</v>
+        <v>122827504</v>
       </c>
       <c r="B13" t="n">
-        <v>98347</v>
+        <v>78762</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1976,50 +1975,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529024</v>
+        <v>529070</v>
       </c>
       <c r="R13" t="n">
-        <v>6999326</v>
+        <v>6999301</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2048,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2058,7 +2048,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,22 +2068,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827504</v>
+        <v>122827355</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>79844</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2101,21 +2096,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2125,10 +2120,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529070</v>
+        <v>528972</v>
       </c>
       <c r="R14" t="n">
-        <v>6999301</v>
+        <v>6999362</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2158,24 +2153,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,22 +2170,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827355</v>
+        <v>122827280</v>
       </c>
       <c r="B15" t="n">
-        <v>79844</v>
+        <v>98347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2214,35 +2194,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528972</v>
+        <v>529040</v>
       </c>
       <c r="R15" t="n">
         <v>6999362</v>
@@ -2275,9 +2269,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,22 +2301,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122827280</v>
+        <v>122827543</v>
       </c>
       <c r="B16" t="n">
-        <v>98347</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2316,52 +2325,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529040</v>
+        <v>529010</v>
       </c>
       <c r="R16" t="n">
-        <v>6999362</v>
+        <v>6999427</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>3 vinterståndare i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,22 +2423,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122827543</v>
+        <v>122828604</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>98347</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2447,43 +2447,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529010</v>
+        <v>529051</v>
       </c>
       <c r="R17" t="n">
-        <v>6999427</v>
+        <v>6999391</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,7 +2524,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2525,12 +2534,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,22 +2549,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122828604</v>
+        <v>122827366</v>
       </c>
       <c r="B18" t="n">
-        <v>98347</v>
+        <v>79843</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2569,52 +2573,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529051</v>
+        <v>528972</v>
       </c>
       <c r="R18" t="n">
-        <v>6999391</v>
+        <v>6999362</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2644,19 +2634,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2671,22 +2651,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122827366</v>
+        <v>122827275</v>
       </c>
       <c r="B19" t="n">
-        <v>79843</v>
+        <v>74863</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2699,21 +2679,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2723,10 +2703,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528972</v>
+        <v>529045</v>
       </c>
       <c r="R19" t="n">
-        <v>6999362</v>
+        <v>6999365</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,9 +2736,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2773,22 +2768,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122827275</v>
+        <v>122828804</v>
       </c>
       <c r="B20" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2801,34 +2796,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529045</v>
+        <v>529036</v>
       </c>
       <c r="R20" t="n">
-        <v>6999365</v>
+        <v>6999404</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2858,24 +2858,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2890,22 +2880,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122828817</v>
+        <v>122827341</v>
       </c>
       <c r="B21" t="n">
-        <v>98347</v>
+        <v>79844</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2914,55 +2904,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529183</v>
+        <v>528959</v>
       </c>
       <c r="R21" t="n">
-        <v>6999378</v>
+        <v>6999360</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2994,11 +2970,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Minst 30 st skott och 5 st vinterståndare.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3007,11 +2978,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3028,10 +2994,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122828804</v>
+        <v>122828442</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,39 +3010,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529036</v>
+        <v>529071</v>
       </c>
       <c r="R22" t="n">
-        <v>6999404</v>
+        <v>6999422</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3106,14 +3067,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3128,22 +3099,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122827341</v>
+        <v>122828006</v>
       </c>
       <c r="B23" t="n">
-        <v>79844</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3156,34 +3127,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528959</v>
+        <v>529145</v>
       </c>
       <c r="R23" t="n">
-        <v>6999360</v>
+        <v>6999399</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3216,6 +3192,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3242,10 +3223,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122828006</v>
+        <v>122827410</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3258,39 +3239,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529145</v>
+        <v>528970</v>
       </c>
       <c r="R24" t="n">
-        <v>6999399</v>
+        <v>6999398</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3323,11 +3299,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3354,10 +3325,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122828442</v>
+        <v>122828175</v>
       </c>
       <c r="B25" t="n">
-        <v>77699</v>
+        <v>98347</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3366,41 +3337,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529071</v>
+        <v>529118</v>
       </c>
       <c r="R25" t="n">
-        <v>6999422</v>
+        <v>6999441</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3429,7 +3414,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3439,12 +3424,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3471,10 +3451,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122827410</v>
+        <v>122827848</v>
       </c>
       <c r="B26" t="n">
-        <v>79843</v>
+        <v>98347</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3483,41 +3463,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528970</v>
+        <v>529118</v>
       </c>
       <c r="R26" t="n">
-        <v>6999398</v>
+        <v>6999379</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3544,9 +3538,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3561,19 +3565,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122828175</v>
+        <v>122827930</v>
       </c>
       <c r="B27" t="n">
         <v>98347</v>
@@ -3608,12 +3612,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3627,13 +3631,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529118</v>
+        <v>529127</v>
       </c>
       <c r="R27" t="n">
-        <v>6999441</v>
+        <v>6999402</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3662,7 +3666,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3672,7 +3676,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3699,7 +3703,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122827848</v>
+        <v>122828745</v>
       </c>
       <c r="B28" t="n">
         <v>98347</v>
@@ -3734,17 +3738,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3753,13 +3747,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529118</v>
+        <v>529035</v>
       </c>
       <c r="R28" t="n">
-        <v>6999379</v>
+        <v>6999405</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3786,19 +3780,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3813,22 +3797,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122827930</v>
+        <v>122828304</v>
       </c>
       <c r="B29" t="n">
-        <v>98347</v>
+        <v>78762</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3837,40 +3821,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3879,10 +3858,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529127</v>
+        <v>529073</v>
       </c>
       <c r="R29" t="n">
-        <v>6999402</v>
+        <v>6999451</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3914,7 +3893,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3924,7 +3903,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3951,10 +3935,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122828304</v>
+        <v>122827382</v>
       </c>
       <c r="B30" t="n">
-        <v>78762</v>
+        <v>98347</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3963,35 +3947,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4000,10 +3984,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529073</v>
+        <v>529080</v>
       </c>
       <c r="R30" t="n">
-        <v>6999451</v>
+        <v>6999334</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4035,7 +4019,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4045,12 +4029,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4077,7 +4061,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122828745</v>
+        <v>122828216</v>
       </c>
       <c r="B31" t="n">
         <v>98347</v>
@@ -4112,7 +4096,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4121,13 +4115,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529035</v>
+        <v>529096</v>
       </c>
       <c r="R31" t="n">
-        <v>6999405</v>
+        <v>6999434</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4154,9 +4148,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4171,22 +4175,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122827382</v>
+        <v>122827824</v>
       </c>
       <c r="B32" t="n">
-        <v>98347</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4195,50 +4199,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529080</v>
+        <v>529074</v>
       </c>
       <c r="R32" t="n">
-        <v>6999334</v>
+        <v>6999358</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4277,12 +4277,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4297,19 +4297,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122828216</v>
+        <v>122827390</v>
       </c>
       <c r="B33" t="n">
         <v>98347</v>
@@ -4344,17 +4344,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4363,13 +4358,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529096</v>
+        <v>529042</v>
       </c>
       <c r="R33" t="n">
-        <v>6999434</v>
+        <v>6999393</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4398,7 +4393,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4408,7 +4403,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4423,22 +4418,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122827824</v>
+        <v>122827617</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4451,42 +4446,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529074</v>
+        <v>528989</v>
       </c>
       <c r="R34" t="n">
-        <v>6999358</v>
+        <v>6999409</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4515,7 +4505,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4525,12 +4515,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4557,7 +4547,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122827390</v>
+        <v>122827147</v>
       </c>
       <c r="B35" t="n">
         <v>98347</v>
@@ -4592,27 +4582,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529042</v>
+        <v>529019</v>
       </c>
       <c r="R35" t="n">
-        <v>6999393</v>
+        <v>6999321</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4641,7 +4636,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4651,7 +4646,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4666,22 +4666,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122827617</v>
+        <v>122827825</v>
       </c>
       <c r="B36" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4694,37 +4694,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528989</v>
+        <v>529088</v>
       </c>
       <c r="R36" t="n">
-        <v>6999409</v>
+        <v>6999396</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4751,24 +4756,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4783,22 +4778,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122827147</v>
+        <v>122828385</v>
       </c>
       <c r="B37" t="n">
-        <v>98347</v>
+        <v>77699</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4807,55 +4802,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529019</v>
+        <v>529065</v>
       </c>
       <c r="R37" t="n">
-        <v>6999321</v>
+        <v>6999450</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4884,7 +4865,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4894,12 +4875,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1 vinterståndare på marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4926,10 +4907,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122827825</v>
+        <v>122828091</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4942,42 +4923,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529088</v>
+        <v>529125</v>
       </c>
       <c r="R38" t="n">
-        <v>6999396</v>
+        <v>6999359</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5009,11 +4985,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5022,6 +4993,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5038,10 +5034,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122828385</v>
+        <v>122827484</v>
       </c>
       <c r="B39" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5054,37 +5050,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529065</v>
+        <v>528970</v>
       </c>
       <c r="R39" t="n">
-        <v>6999450</v>
+        <v>6999399</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5111,24 +5112,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5143,22 +5134,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122828091</v>
+        <v>122827232</v>
       </c>
       <c r="B40" t="n">
-        <v>78762</v>
+        <v>79843</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5171,37 +5162,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529125</v>
+        <v>528947</v>
       </c>
       <c r="R40" t="n">
-        <v>6999359</v>
+        <v>6999334</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5241,31 +5237,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5282,10 +5253,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122827484</v>
+        <v>122827180</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5298,39 +5269,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528970</v>
+        <v>529019</v>
       </c>
       <c r="R41" t="n">
-        <v>6999399</v>
+        <v>6999321</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5360,14 +5326,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5382,19 +5358,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122827232</v>
+        <v>122827290</v>
       </c>
       <c r="B42" t="n">
         <v>79843</v>
@@ -5439,10 +5415,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528947</v>
+        <v>528951</v>
       </c>
       <c r="R42" t="n">
-        <v>6999334</v>
+        <v>6999355</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5501,10 +5477,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827180</v>
+        <v>122827958</v>
       </c>
       <c r="B43" t="n">
-        <v>78762</v>
+        <v>77699</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5517,37 +5493,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529019</v>
+        <v>529113</v>
       </c>
       <c r="R43" t="n">
-        <v>6999321</v>
+        <v>6999364</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5576,7 +5552,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5586,12 +5562,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5606,22 +5582,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122827290</v>
+        <v>122827686</v>
       </c>
       <c r="B44" t="n">
-        <v>79843</v>
+        <v>78762</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5634,39 +5610,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528951</v>
+        <v>529073</v>
       </c>
       <c r="R44" t="n">
-        <v>6999355</v>
+        <v>6999336</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5696,9 +5667,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5713,22 +5699,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122827958</v>
+        <v>122827642</v>
       </c>
       <c r="B45" t="n">
-        <v>77699</v>
+        <v>98347</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5737,41 +5723,55 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529113</v>
+        <v>529076</v>
       </c>
       <c r="R45" t="n">
-        <v>6999364</v>
+        <v>6999342</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5810,12 +5810,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5830,22 +5825,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122827686</v>
+        <v>122827178</v>
       </c>
       <c r="B46" t="n">
-        <v>78762</v>
+        <v>79843</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5858,21 +5853,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5882,10 +5877,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529073</v>
+        <v>528960</v>
       </c>
       <c r="R46" t="n">
-        <v>6999336</v>
+        <v>6999325</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5915,24 +5910,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5947,22 +5927,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122827642</v>
+        <v>122827222</v>
       </c>
       <c r="B47" t="n">
-        <v>98347</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5971,55 +5951,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>529076</v>
+        <v>529007</v>
       </c>
       <c r="R47" t="n">
-        <v>6999342</v>
+        <v>6999319</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6046,19 +6012,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:00</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6069,26 +6030,51 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122827222</v>
+        <v>122827606</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>98347</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6097,38 +6083,48 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529007</v>
+        <v>529023</v>
       </c>
       <c r="R48" t="n">
-        <v>6999319</v>
+        <v>6999322</v>
       </c>
       <c r="S48" t="n">
         <v>8</v>
@@ -6165,7 +6161,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Minst 12 st skott och 1 st vinterståndare.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6180,26 +6176,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6217,10 +6193,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122827178</v>
+        <v>122828817</v>
       </c>
       <c r="B49" t="n">
-        <v>79843</v>
+        <v>98347</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6229,41 +6205,55 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528960</v>
+        <v>529183</v>
       </c>
       <c r="R49" t="n">
-        <v>6999325</v>
+        <v>6999378</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6295,6 +6285,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 30 st skott och 5 st vinterståndare.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6303,6 +6298,11 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122827466</v>
+        <v>122828804</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529066</v>
+        <v>529036</v>
       </c>
       <c r="R2" t="n">
-        <v>6999328</v>
+        <v>6999404</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +753,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:56</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122827556</v>
+        <v>122827824</v>
       </c>
       <c r="B3" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,37 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528995</v>
+        <v>529074</v>
       </c>
       <c r="R3" t="n">
-        <v>6999419</v>
+        <v>6999358</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,9 +865,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827597</v>
+        <v>122828442</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>77699</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,52 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529078</v>
+        <v>529071</v>
       </c>
       <c r="R4" t="n">
-        <v>6999325</v>
+        <v>6999422</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122828815</v>
+        <v>122827504</v>
       </c>
       <c r="B5" t="n">
-        <v>74847</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529024</v>
+        <v>529070</v>
       </c>
       <c r="R5" t="n">
-        <v>6999406</v>
+        <v>6999301</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122828672</v>
+        <v>122827686</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,52 +1155,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529025</v>
+        <v>529073</v>
       </c>
       <c r="R6" t="n">
-        <v>6999399</v>
+        <v>6999336</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122827346</v>
+        <v>122827366</v>
       </c>
       <c r="B7" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528959</v>
+        <v>528972</v>
       </c>
       <c r="R7" t="n">
-        <v>6999360</v>
+        <v>6999362</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1374,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122827285</v>
+        <v>122827825</v>
       </c>
       <c r="B8" t="n">
-        <v>79844</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,34 +1378,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528951</v>
+        <v>529088</v>
       </c>
       <c r="R8" t="n">
-        <v>6999355</v>
+        <v>6999396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,6 +1443,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122828769</v>
+        <v>122827390</v>
       </c>
       <c r="B9" t="n">
-        <v>79843</v>
+        <v>98355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,38 +1486,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529028</v>
+        <v>529042</v>
       </c>
       <c r="R9" t="n">
-        <v>6999409</v>
+        <v>6999393</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,12 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På sälgstubbe</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,22 +1583,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122828537</v>
+        <v>122827290</v>
       </c>
       <c r="B10" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,37 +1611,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529161</v>
+        <v>528951</v>
       </c>
       <c r="R10" t="n">
-        <v>6999364</v>
+        <v>6999355</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1671,11 +1678,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1684,31 +1686,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1725,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122827718</v>
+        <v>122827410</v>
       </c>
       <c r="B11" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529085</v>
+        <v>528970</v>
       </c>
       <c r="R11" t="n">
-        <v>6999343</v>
+        <v>6999398</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,24 +1775,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,22 +1792,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827187</v>
+        <v>122827355</v>
       </c>
       <c r="B12" t="n">
-        <v>98347</v>
+        <v>79848</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,50 +1816,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529024</v>
+        <v>528972</v>
       </c>
       <c r="R12" t="n">
-        <v>6999326</v>
+        <v>6999362</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,19 +1877,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,22 +1894,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122827504</v>
+        <v>122827382</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>98355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,38 +1918,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529070</v>
+        <v>529080</v>
       </c>
       <c r="R13" t="n">
-        <v>6999301</v>
+        <v>6999334</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,12 +2000,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2080,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827355</v>
+        <v>122827466</v>
       </c>
       <c r="B14" t="n">
-        <v>79844</v>
+        <v>98355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2092,38 +2044,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528972</v>
+        <v>529066</v>
       </c>
       <c r="R14" t="n">
-        <v>6999362</v>
+        <v>6999328</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2153,9 +2119,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,22 +2146,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827280</v>
+        <v>122828216</v>
       </c>
       <c r="B15" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2217,17 +2193,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2236,13 +2212,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529040</v>
+        <v>529096</v>
       </c>
       <c r="R15" t="n">
-        <v>6999362</v>
+        <v>6999434</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2271,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2281,12 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>3 vinterståndare i gammal granskog</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2313,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122827543</v>
+        <v>122828745</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>98355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2325,43 +2296,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529010</v>
+        <v>529035</v>
       </c>
       <c r="R16" t="n">
-        <v>6999427</v>
+        <v>6999405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2391,24 +2361,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,22 +2378,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122828604</v>
+        <v>122828175</v>
       </c>
       <c r="B17" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2470,7 +2425,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2480,7 +2435,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2489,13 +2444,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529051</v>
+        <v>529118</v>
       </c>
       <c r="R17" t="n">
-        <v>6999391</v>
+        <v>6999441</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2524,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2534,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122827366</v>
+        <v>122827617</v>
       </c>
       <c r="B18" t="n">
-        <v>79843</v>
+        <v>74863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2577,21 +2532,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,13 +2556,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528972</v>
+        <v>528989</v>
       </c>
       <c r="R18" t="n">
-        <v>6999362</v>
+        <v>6999409</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2634,9 +2589,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,22 +2621,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122827275</v>
+        <v>122827341</v>
       </c>
       <c r="B19" t="n">
-        <v>74863</v>
+        <v>79848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,21 +2649,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2703,10 +2673,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529045</v>
+        <v>528959</v>
       </c>
       <c r="R19" t="n">
-        <v>6999365</v>
+        <v>6999360</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2736,24 +2706,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2768,22 +2723,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122828804</v>
+        <v>122827346</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2796,39 +2751,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529036</v>
+        <v>528959</v>
       </c>
       <c r="R20" t="n">
-        <v>6999404</v>
+        <v>6999360</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2861,11 +2811,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,10 +2837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122827341</v>
+        <v>122828304</v>
       </c>
       <c r="B21" t="n">
-        <v>79844</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2908,34 +2853,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528959</v>
+        <v>529073</v>
       </c>
       <c r="R21" t="n">
-        <v>6999360</v>
+        <v>6999451</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2965,9 +2919,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2982,19 +2951,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122828442</v>
+        <v>122828385</v>
       </c>
       <c r="B22" t="n">
         <v>77699</v>
@@ -3034,13 +3003,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529071</v>
+        <v>529065</v>
       </c>
       <c r="R22" t="n">
-        <v>6999422</v>
+        <v>6999450</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3069,7 +3038,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3079,12 +3048,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3111,10 +3080,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122828006</v>
+        <v>122827848</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>98355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3123,46 +3092,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529145</v>
+        <v>529118</v>
       </c>
       <c r="R23" t="n">
-        <v>6999399</v>
+        <v>6999379</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3189,14 +3167,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,22 +3194,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122827410</v>
+        <v>122827285</v>
       </c>
       <c r="B24" t="n">
-        <v>79843</v>
+        <v>79848</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3239,21 +3222,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3263,10 +3246,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528970</v>
+        <v>528951</v>
       </c>
       <c r="R24" t="n">
-        <v>6999398</v>
+        <v>6999355</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3325,10 +3308,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122828175</v>
+        <v>122827147</v>
       </c>
       <c r="B25" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3360,32 +3343,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529118</v>
+        <v>529019</v>
       </c>
       <c r="R25" t="n">
-        <v>6999441</v>
+        <v>6999321</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3414,7 +3397,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3424,7 +3407,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3451,10 +3439,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122827848</v>
+        <v>122828006</v>
       </c>
       <c r="B26" t="n">
-        <v>98347</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3463,55 +3451,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529118</v>
+        <v>529145</v>
       </c>
       <c r="R26" t="n">
-        <v>6999379</v>
+        <v>6999399</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3538,19 +3517,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:04</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3565,22 +3539,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122827930</v>
+        <v>122827280</v>
       </c>
       <c r="B27" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3612,17 +3586,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3631,10 +3605,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529127</v>
+        <v>529040</v>
       </c>
       <c r="R27" t="n">
-        <v>6999402</v>
+        <v>6999362</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3666,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3676,7 +3650,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3703,10 +3682,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122828745</v>
+        <v>122828091</v>
       </c>
       <c r="B28" t="n">
-        <v>98347</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3715,45 +3694,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529035</v>
+        <v>529125</v>
       </c>
       <c r="R28" t="n">
-        <v>6999405</v>
+        <v>6999359</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3793,6 +3768,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3809,10 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122828304</v>
+        <v>122827556</v>
       </c>
       <c r="B29" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3825,43 +3825,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529073</v>
+        <v>528995</v>
       </c>
       <c r="R29" t="n">
-        <v>6999451</v>
+        <v>6999419</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3891,24 +3882,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3923,22 +3899,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122827382</v>
+        <v>122827275</v>
       </c>
       <c r="B30" t="n">
-        <v>98347</v>
+        <v>74863</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3947,47 +3923,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529080</v>
+        <v>529045</v>
       </c>
       <c r="R30" t="n">
-        <v>6999334</v>
+        <v>6999365</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4019,7 +3986,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4029,12 +3996,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4049,22 +4016,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122828216</v>
+        <v>122827187</v>
       </c>
       <c r="B31" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4096,17 +4063,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4115,13 +4077,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529096</v>
+        <v>529024</v>
       </c>
       <c r="R31" t="n">
-        <v>6999434</v>
+        <v>6999326</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4150,7 +4112,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4160,7 +4122,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4175,22 +4137,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122827824</v>
+        <v>122828769</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4203,42 +4165,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529074</v>
+        <v>529028</v>
       </c>
       <c r="R32" t="n">
-        <v>6999358</v>
+        <v>6999409</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4267,7 +4224,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4277,12 +4234,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4297,7 +4254,7 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -4309,10 +4266,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122827390</v>
+        <v>122827958</v>
       </c>
       <c r="B33" t="n">
-        <v>98347</v>
+        <v>77699</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4321,50 +4278,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529042</v>
+        <v>529113</v>
       </c>
       <c r="R33" t="n">
-        <v>6999393</v>
+        <v>6999364</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4393,7 +4341,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4403,7 +4351,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4430,10 +4383,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122827617</v>
+        <v>122827543</v>
       </c>
       <c r="B34" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4446,37 +4399,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528989</v>
+        <v>529010</v>
       </c>
       <c r="R34" t="n">
-        <v>6999409</v>
+        <v>6999427</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4505,7 +4463,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4515,12 +4473,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4547,10 +4505,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122827147</v>
+        <v>122828815</v>
       </c>
       <c r="B35" t="n">
-        <v>98347</v>
+        <v>74847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4559,55 +4517,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529019</v>
+        <v>529024</v>
       </c>
       <c r="R35" t="n">
-        <v>6999321</v>
+        <v>6999406</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4636,7 +4580,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4646,12 +4590,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>1 vinterståndare på marken i gammal granskog</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4671,14 +4615,14 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122827825</v>
+        <v>122827484</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -4723,10 +4667,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529088</v>
+        <v>528970</v>
       </c>
       <c r="R36" t="n">
-        <v>6999396</v>
+        <v>6999399</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4790,10 +4734,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122828385</v>
+        <v>122827232</v>
       </c>
       <c r="B37" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4806,37 +4750,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529065</v>
+        <v>528947</v>
       </c>
       <c r="R37" t="n">
-        <v>6999450</v>
+        <v>6999334</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4863,24 +4812,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4895,22 +4829,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122828091</v>
+        <v>122828537</v>
       </c>
       <c r="B38" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4947,13 +4881,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529125</v>
+        <v>529161</v>
       </c>
       <c r="R38" t="n">
-        <v>6999359</v>
+        <v>6999364</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4985,6 +4919,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4996,7 +4935,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5034,10 +4973,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122827484</v>
+        <v>122828604</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>98355</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5046,43 +4985,52 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528970</v>
+        <v>529051</v>
       </c>
       <c r="R39" t="n">
-        <v>6999399</v>
+        <v>6999391</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5112,14 +5060,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5134,22 +5087,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122827232</v>
+        <v>122827180</v>
       </c>
       <c r="B40" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5162,39 +5115,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528947</v>
+        <v>529019</v>
       </c>
       <c r="R40" t="n">
-        <v>6999334</v>
+        <v>6999321</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5224,9 +5172,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5241,22 +5204,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122827180</v>
+        <v>122827718</v>
       </c>
       <c r="B41" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5269,34 +5232,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529019</v>
+        <v>529085</v>
       </c>
       <c r="R41" t="n">
-        <v>6999321</v>
+        <v>6999343</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5328,7 +5291,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5338,12 +5301,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5370,10 +5333,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122827290</v>
+        <v>122827930</v>
       </c>
       <c r="B42" t="n">
-        <v>79843</v>
+        <v>98355</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5382,31 +5345,40 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5415,10 +5387,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528951</v>
+        <v>529127</v>
       </c>
       <c r="R42" t="n">
-        <v>6999355</v>
+        <v>6999402</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5448,9 +5420,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5465,22 +5447,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827958</v>
+        <v>122827178</v>
       </c>
       <c r="B43" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5493,21 +5475,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5517,13 +5499,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529113</v>
+        <v>528960</v>
       </c>
       <c r="R43" t="n">
-        <v>6999364</v>
+        <v>6999325</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5550,24 +5532,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5582,22 +5549,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122827686</v>
+        <v>122827642</v>
       </c>
       <c r="B44" t="n">
-        <v>78762</v>
+        <v>98355</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5606,38 +5573,52 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529073</v>
+        <v>529076</v>
       </c>
       <c r="R44" t="n">
-        <v>6999336</v>
+        <v>6999342</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5680,11 +5661,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5711,10 +5687,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122827642</v>
+        <v>122828672</v>
       </c>
       <c r="B45" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5746,17 +5722,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5765,10 +5741,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529076</v>
+        <v>529025</v>
       </c>
       <c r="R45" t="n">
-        <v>6999342</v>
+        <v>6999399</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5800,7 +5776,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5810,7 +5786,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5837,10 +5813,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122827178</v>
+        <v>122827597</v>
       </c>
       <c r="B46" t="n">
-        <v>79843</v>
+        <v>98355</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5849,35 +5825,49 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528960</v>
+        <v>529078</v>
       </c>
       <c r="R46" t="n">
         <v>6999325</v>
@@ -5910,9 +5900,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5927,12 +5927,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6074,7 +6074,7 @@
         <v>122827606</v>
       </c>
       <c r="B48" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>122828817</v>
       </c>
       <c r="B49" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -1804,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827355</v>
+        <v>122827382</v>
       </c>
       <c r="B12" t="n">
-        <v>79848</v>
+        <v>98355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,38 +1816,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528972</v>
+        <v>529080</v>
       </c>
       <c r="R12" t="n">
-        <v>6999362</v>
+        <v>6999334</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,9 +1886,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,19 +1918,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122827382</v>
+        <v>122827466</v>
       </c>
       <c r="B13" t="n">
         <v>98355</v>
@@ -1941,7 +1965,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1949,16 +1973,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529080</v>
+        <v>529066</v>
       </c>
       <c r="R13" t="n">
-        <v>6999334</v>
+        <v>6999328</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1990,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2000,12 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,7 +2056,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827466</v>
+        <v>122828216</v>
       </c>
       <c r="B14" t="n">
         <v>98355</v>
@@ -2067,17 +2091,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2086,13 +2110,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529066</v>
+        <v>529096</v>
       </c>
       <c r="R14" t="n">
-        <v>6999328</v>
+        <v>6999434</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2121,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,7 +2182,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122828216</v>
+        <v>122828745</v>
       </c>
       <c r="B15" t="n">
         <v>98355</v>
@@ -2193,17 +2217,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2212,13 +2226,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529096</v>
+        <v>529035</v>
       </c>
       <c r="R15" t="n">
-        <v>6999434</v>
+        <v>6999405</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2245,19 +2259,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,22 +2276,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122828745</v>
+        <v>122827355</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>79848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,42 +2300,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529035</v>
+        <v>528972</v>
       </c>
       <c r="R16" t="n">
-        <v>6999405</v>
+        <v>6999362</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122828091</v>
+        <v>122827556</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3698,21 +3698,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3722,13 +3722,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529125</v>
+        <v>528995</v>
       </c>
       <c r="R28" t="n">
-        <v>6999359</v>
+        <v>6999419</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3768,31 +3768,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3809,10 +3784,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122827556</v>
+        <v>122827275</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3825,21 +3800,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3849,10 +3824,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528995</v>
+        <v>529045</v>
       </c>
       <c r="R29" t="n">
-        <v>6999419</v>
+        <v>6999365</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3882,9 +3857,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3899,22 +3889,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122827275</v>
+        <v>122828091</v>
       </c>
       <c r="B30" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3927,21 +3917,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3951,13 +3941,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529045</v>
+        <v>529125</v>
       </c>
       <c r="R30" t="n">
-        <v>6999365</v>
+        <v>6999359</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3984,26 +3974,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4012,16 +3987,41 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122827484</v>
+        <v>122827232</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4638,39 +4638,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528970</v>
+        <v>528947</v>
       </c>
       <c r="R36" t="n">
-        <v>6999399</v>
+        <v>6999334</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4703,11 +4703,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4734,10 +4729,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122827232</v>
+        <v>122827484</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4750,39 +4745,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528947</v>
+        <v>528970</v>
       </c>
       <c r="R37" t="n">
-        <v>6999334</v>
+        <v>6999399</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4815,6 +4810,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5459,10 +5459,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827178</v>
+        <v>122827642</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>98355</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5471,38 +5471,52 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528960</v>
+        <v>529076</v>
       </c>
       <c r="R43" t="n">
-        <v>6999325</v>
+        <v>6999342</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5532,9 +5546,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5549,19 +5573,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122827642</v>
+        <v>122828672</v>
       </c>
       <c r="B44" t="n">
         <v>98355</v>
@@ -5596,17 +5620,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5615,10 +5639,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529076</v>
+        <v>529025</v>
       </c>
       <c r="R44" t="n">
-        <v>6999342</v>
+        <v>6999399</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5650,7 +5674,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5660,7 +5684,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5687,10 +5711,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122828672</v>
+        <v>122827178</v>
       </c>
       <c r="B45" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5699,52 +5723,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529025</v>
+        <v>528960</v>
       </c>
       <c r="R45" t="n">
-        <v>6999399</v>
+        <v>6999325</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5774,19 +5784,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5801,12 +5801,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122827824</v>
+        <v>122827466</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,46 +799,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529074</v>
+        <v>529066</v>
       </c>
       <c r="R3" t="n">
-        <v>6999358</v>
+        <v>6999328</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122828442</v>
+        <v>122827355</v>
       </c>
       <c r="B4" t="n">
-        <v>77699</v>
+        <v>79848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529071</v>
+        <v>528972</v>
       </c>
       <c r="R4" t="n">
-        <v>6999422</v>
+        <v>6999362</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,24 +986,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122827504</v>
+        <v>122827718</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529070</v>
+        <v>529085</v>
       </c>
       <c r="R5" t="n">
-        <v>6999301</v>
+        <v>6999343</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122827686</v>
+        <v>122828304</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1176,7 +1165,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
@@ -1186,7 +1184,7 @@
         <v>529073</v>
       </c>
       <c r="R6" t="n">
-        <v>6999336</v>
+        <v>6999451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1226,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Längsta bål 60 cm</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122827366</v>
+        <v>122827504</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1274,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528972</v>
+        <v>529070</v>
       </c>
       <c r="R7" t="n">
-        <v>6999362</v>
+        <v>6999301</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,9 +1331,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,22 +1363,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122827825</v>
+        <v>122827232</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,39 +1391,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529088</v>
+        <v>528947</v>
       </c>
       <c r="R8" t="n">
-        <v>6999396</v>
+        <v>6999334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,11 +1456,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122827390</v>
+        <v>122827275</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>74863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,47 +1494,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529042</v>
+        <v>529045</v>
       </c>
       <c r="R9" t="n">
-        <v>6999393</v>
+        <v>6999365</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1567,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122827290</v>
+        <v>122828006</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,39 +1615,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528951</v>
+        <v>529145</v>
       </c>
       <c r="R10" t="n">
-        <v>6999355</v>
+        <v>6999399</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,6 +1680,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122827410</v>
+        <v>122827341</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,21 +1727,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528970</v>
+        <v>528959</v>
       </c>
       <c r="R11" t="n">
-        <v>6999398</v>
+        <v>6999360</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,10 +1813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827382</v>
+        <v>122827686</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,47 +1825,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529080</v>
+        <v>529073</v>
       </c>
       <c r="R12" t="n">
-        <v>6999334</v>
+        <v>6999336</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122827466</v>
+        <v>122828537</v>
       </c>
       <c r="B13" t="n">
-        <v>98355</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,55 +1942,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529066</v>
+        <v>529161</v>
       </c>
       <c r="R13" t="n">
-        <v>6999328</v>
+        <v>6999364</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2017,19 +2003,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:56</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,26 +2021,51 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122828216</v>
+        <v>122827824</v>
       </c>
       <c r="B14" t="n">
-        <v>98355</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,55 +2074,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529096</v>
+        <v>529074</v>
       </c>
       <c r="R14" t="n">
-        <v>6999434</v>
+        <v>6999358</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2145,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2152,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,19 +2172,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122828745</v>
+        <v>122827187</v>
       </c>
       <c r="B15" t="n">
         <v>98355</v>
@@ -2217,7 +2219,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2226,13 +2233,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529035</v>
+        <v>529024</v>
       </c>
       <c r="R15" t="n">
-        <v>6999405</v>
+        <v>6999326</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2259,9 +2266,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,22 +2293,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122827355</v>
+        <v>122827346</v>
       </c>
       <c r="B16" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,21 +2321,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2345,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528972</v>
+        <v>528959</v>
       </c>
       <c r="R16" t="n">
-        <v>6999362</v>
+        <v>6999360</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,7 +2407,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122828175</v>
+        <v>122828604</v>
       </c>
       <c r="B17" t="n">
         <v>98355</v>
@@ -2425,7 +2442,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2435,7 +2452,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2444,13 +2461,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529118</v>
+        <v>529051</v>
       </c>
       <c r="R17" t="n">
-        <v>6999441</v>
+        <v>6999391</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2479,7 +2496,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2506,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2533,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122827617</v>
+        <v>122827390</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>98355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,41 +2545,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528989</v>
+        <v>529042</v>
       </c>
       <c r="R18" t="n">
-        <v>6999409</v>
+        <v>6999393</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,7 +2617,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,12 +2627,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,10 +2654,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122827341</v>
+        <v>122827178</v>
       </c>
       <c r="B19" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2649,21 +2670,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2673,10 +2694,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528959</v>
+        <v>528960</v>
       </c>
       <c r="R19" t="n">
-        <v>6999360</v>
+        <v>6999325</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2735,10 +2756,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122827346</v>
+        <v>122827642</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>98355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2747,38 +2768,52 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528959</v>
+        <v>529076</v>
       </c>
       <c r="R20" t="n">
-        <v>6999360</v>
+        <v>6999342</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2808,9 +2843,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,22 +2870,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122828304</v>
+        <v>122827825</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2853,43 +2898,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529073</v>
+        <v>529088</v>
       </c>
       <c r="R21" t="n">
-        <v>6999451</v>
+        <v>6999396</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2919,24 +2960,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2951,22 +2982,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122828385</v>
+        <v>122828769</v>
       </c>
       <c r="B22" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2979,21 +3010,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3003,13 +3034,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529065</v>
+        <v>529028</v>
       </c>
       <c r="R22" t="n">
-        <v>6999450</v>
+        <v>6999409</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3038,7 +3069,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3048,12 +3079,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,7 +3111,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122827848</v>
+        <v>122828216</v>
       </c>
       <c r="B23" t="n">
         <v>98355</v>
@@ -3120,12 +3151,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3134,10 +3165,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529118</v>
+        <v>529096</v>
       </c>
       <c r="R23" t="n">
-        <v>6999379</v>
+        <v>6999434</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3169,7 +3200,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3179,7 +3210,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3206,10 +3237,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122827285</v>
+        <v>122827280</v>
       </c>
       <c r="B24" t="n">
-        <v>79848</v>
+        <v>98355</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3218,38 +3249,52 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528951</v>
+        <v>529040</v>
       </c>
       <c r="R24" t="n">
-        <v>6999355</v>
+        <v>6999362</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3279,9 +3324,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3296,19 +3356,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122827147</v>
+        <v>122827930</v>
       </c>
       <c r="B25" t="n">
         <v>98355</v>
@@ -3343,7 +3403,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3353,22 +3413,22 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529019</v>
+        <v>529127</v>
       </c>
       <c r="R25" t="n">
-        <v>6999321</v>
+        <v>6999402</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3397,7 +3457,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3407,12 +3467,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1 vinterståndare på marken i gammal granskog</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,10 +3494,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122828006</v>
+        <v>122828815</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>74847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,43 +3506,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529145</v>
+        <v>529024</v>
       </c>
       <c r="R26" t="n">
-        <v>6999399</v>
+        <v>6999406</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3517,14 +3567,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,19 +3599,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122827280</v>
+        <v>122828175</v>
       </c>
       <c r="B27" t="n">
         <v>98355</v>
@@ -3586,7 +3646,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3596,7 +3656,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3605,13 +3665,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529040</v>
+        <v>529118</v>
       </c>
       <c r="R27" t="n">
-        <v>6999362</v>
+        <v>6999441</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3640,7 +3700,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,12 +3710,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>3 vinterståndare i gammal granskog</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3682,10 +3737,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122827556</v>
+        <v>122827597</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>98355</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3694,38 +3749,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528995</v>
+        <v>529078</v>
       </c>
       <c r="R28" t="n">
-        <v>6999419</v>
+        <v>6999325</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3755,9 +3824,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3772,22 +3851,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122827275</v>
+        <v>122827147</v>
       </c>
       <c r="B29" t="n">
-        <v>74863</v>
+        <v>98355</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3796,41 +3875,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529045</v>
+        <v>529019</v>
       </c>
       <c r="R29" t="n">
-        <v>6999365</v>
+        <v>6999321</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3859,7 +3952,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3869,12 +3962,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3889,12 +3982,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4028,7 +4121,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122827187</v>
+        <v>122827382</v>
       </c>
       <c r="B31" t="n">
         <v>98355</v>
@@ -4063,7 +4156,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4077,13 +4170,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529024</v>
+        <v>529080</v>
       </c>
       <c r="R31" t="n">
-        <v>6999326</v>
+        <v>6999334</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4112,7 +4205,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4122,7 +4215,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4137,22 +4235,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122828769</v>
+        <v>122828385</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4165,21 +4263,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4189,13 +4287,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529028</v>
+        <v>529065</v>
       </c>
       <c r="R32" t="n">
-        <v>6999409</v>
+        <v>6999450</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4224,7 +4322,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4234,12 +4332,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4259,17 +4357,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122827958</v>
+        <v>122827290</v>
       </c>
       <c r="B33" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4282,37 +4380,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529113</v>
+        <v>528951</v>
       </c>
       <c r="R33" t="n">
-        <v>6999364</v>
+        <v>6999355</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4339,24 +4442,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4371,22 +4459,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122827543</v>
+        <v>122827410</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4399,39 +4487,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529010</v>
+        <v>528970</v>
       </c>
       <c r="R34" t="n">
-        <v>6999427</v>
+        <v>6999398</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4461,24 +4544,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4493,22 +4561,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122828815</v>
+        <v>122827180</v>
       </c>
       <c r="B35" t="n">
-        <v>74847</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4517,38 +4585,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529024</v>
+        <v>529019</v>
       </c>
       <c r="R35" t="n">
-        <v>6999406</v>
+        <v>6999321</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4580,7 +4648,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4590,12 +4658,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4615,17 +4683,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122827232</v>
+        <v>122827848</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>98355</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4634,31 +4702,40 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4667,13 +4744,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528947</v>
+        <v>529118</v>
       </c>
       <c r="R36" t="n">
-        <v>6999334</v>
+        <v>6999379</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4700,9 +4777,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4717,22 +4804,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122827484</v>
+        <v>122827958</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4745,42 +4832,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528970</v>
+        <v>529113</v>
       </c>
       <c r="R37" t="n">
-        <v>6999399</v>
+        <v>6999364</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4807,14 +4889,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4829,22 +4921,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122828537</v>
+        <v>122827366</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4857,21 +4949,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4881,13 +4973,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529161</v>
+        <v>528972</v>
       </c>
       <c r="R38" t="n">
-        <v>6999364</v>
+        <v>6999362</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4919,11 +5011,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4932,31 +5019,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4973,10 +5035,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122828604</v>
+        <v>122827617</v>
       </c>
       <c r="B39" t="n">
-        <v>98355</v>
+        <v>74863</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4985,55 +5047,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529051</v>
+        <v>528989</v>
       </c>
       <c r="R39" t="n">
-        <v>6999391</v>
+        <v>6999409</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5062,7 +5110,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5072,7 +5120,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5087,22 +5140,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122827180</v>
+        <v>122827484</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5115,34 +5168,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529019</v>
+        <v>528970</v>
       </c>
       <c r="R40" t="n">
-        <v>6999321</v>
+        <v>6999399</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5172,24 +5230,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5204,22 +5252,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122827718</v>
+        <v>122828442</v>
       </c>
       <c r="B41" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5232,21 +5280,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5256,10 +5304,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529085</v>
+        <v>529071</v>
       </c>
       <c r="R41" t="n">
-        <v>6999343</v>
+        <v>6999422</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5291,7 +5339,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5301,12 +5349,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal i gammal granskog</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5333,7 +5381,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122827930</v>
+        <v>122828672</v>
       </c>
       <c r="B42" t="n">
         <v>98355</v>
@@ -5368,17 +5416,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5387,10 +5435,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529127</v>
+        <v>529025</v>
       </c>
       <c r="R42" t="n">
-        <v>6999402</v>
+        <v>6999399</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5422,7 +5470,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5432,7 +5480,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5459,10 +5507,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827642</v>
+        <v>122827285</v>
       </c>
       <c r="B43" t="n">
-        <v>98355</v>
+        <v>79848</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5471,52 +5519,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529076</v>
+        <v>528951</v>
       </c>
       <c r="R43" t="n">
-        <v>6999342</v>
+        <v>6999355</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5546,19 +5580,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5573,22 +5597,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122828672</v>
+        <v>122827543</v>
       </c>
       <c r="B44" t="n">
-        <v>98355</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5597,52 +5621,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529025</v>
+        <v>529010</v>
       </c>
       <c r="R44" t="n">
-        <v>6999399</v>
+        <v>6999427</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5674,7 +5689,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5684,7 +5699,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5699,19 +5719,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122827178</v>
+        <v>122827556</v>
       </c>
       <c r="B45" t="n">
         <v>79847</v>
@@ -5751,10 +5771,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528960</v>
+        <v>528995</v>
       </c>
       <c r="R45" t="n">
-        <v>6999325</v>
+        <v>6999419</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5813,7 +5833,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122827597</v>
+        <v>122828745</v>
       </c>
       <c r="B46" t="n">
         <v>98355</v>
@@ -5848,17 +5868,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5867,10 +5877,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529078</v>
+        <v>529035</v>
       </c>
       <c r="R46" t="n">
-        <v>6999325</v>
+        <v>6999405</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5900,19 +5910,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5927,22 +5927,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122827222</v>
+        <v>122827606</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>98355</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5951,38 +5951,48 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>529007</v>
+        <v>529023</v>
       </c>
       <c r="R47" t="n">
-        <v>6999319</v>
+        <v>6999322</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6019,7 +6029,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Minst 12 st skott och 1 st vinterståndare.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6034,26 +6044,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6071,10 +6061,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122827606</v>
+        <v>122827222</v>
       </c>
       <c r="B48" t="n">
-        <v>98355</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6083,48 +6073,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529023</v>
+        <v>529007</v>
       </c>
       <c r="R48" t="n">
-        <v>6999322</v>
+        <v>6999319</v>
       </c>
       <c r="S48" t="n">
         <v>8</v>
@@ -6161,7 +6141,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Minst 12 st skott och 1 st vinterståndare.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6176,6 +6156,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122828804</v>
+        <v>122828006</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529036</v>
+        <v>529145</v>
       </c>
       <c r="R2" t="n">
-        <v>6999404</v>
+        <v>6999399</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122827466</v>
+        <v>122828604</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529066</v>
+        <v>529051</v>
       </c>
       <c r="R3" t="n">
-        <v>6999328</v>
+        <v>6999391</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,17 +906,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827355</v>
+        <v>122827280</v>
       </c>
       <c r="B4" t="n">
-        <v>79848</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,35 +925,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528972</v>
+        <v>529040</v>
       </c>
       <c r="R4" t="n">
         <v>6999362</v>
@@ -986,9 +1000,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,12 +1032,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1132,7 +1161,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122828304</v>
+        <v>122827504</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1165,26 +1194,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529073</v>
+        <v>529070</v>
       </c>
       <c r="R6" t="n">
-        <v>6999451</v>
+        <v>6999301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1258,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122827504</v>
+        <v>122827290</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,34 +1294,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529070</v>
+        <v>528951</v>
       </c>
       <c r="R7" t="n">
-        <v>6999301</v>
+        <v>6999355</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,24 +1356,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,19 +1373,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122827232</v>
+        <v>122828769</v>
       </c>
       <c r="B8" t="n">
         <v>79847</v>
@@ -1409,21 +1419,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528947</v>
+        <v>529028</v>
       </c>
       <c r="R8" t="n">
-        <v>6999334</v>
+        <v>6999409</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,9 +1458,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,22 +1490,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122827275</v>
+        <v>122828385</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,21 +1518,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,13 +1542,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529045</v>
+        <v>529065</v>
       </c>
       <c r="R9" t="n">
-        <v>6999365</v>
+        <v>6999450</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,12 +1587,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,22 +1607,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122828006</v>
+        <v>122827382</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,43 +1631,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529145</v>
+        <v>529080</v>
       </c>
       <c r="R10" t="n">
-        <v>6999399</v>
+        <v>6999334</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,14 +1701,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,22 +1733,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122827341</v>
+        <v>122827390</v>
       </c>
       <c r="B11" t="n">
-        <v>79848</v>
+        <v>98357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,38 +1757,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528959</v>
+        <v>529042</v>
       </c>
       <c r="R11" t="n">
-        <v>6999360</v>
+        <v>6999393</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,9 +1827,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,22 +1854,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827686</v>
+        <v>122827958</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,21 +1882,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1853,13 +1906,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529073</v>
+        <v>529113</v>
       </c>
       <c r="R12" t="n">
-        <v>6999336</v>
+        <v>6999364</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,12 +1951,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Längsta bål 60 cm</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,19 +1971,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122828537</v>
+        <v>122828091</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1970,13 +2023,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529161</v>
+        <v>529125</v>
       </c>
       <c r="R13" t="n">
-        <v>6999364</v>
+        <v>6999359</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2008,11 +2061,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2024,7 +2072,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2062,10 +2110,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827824</v>
+        <v>122827556</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,42 +2126,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529074</v>
+        <v>528995</v>
       </c>
       <c r="R14" t="n">
-        <v>6999358</v>
+        <v>6999419</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2140,24 +2183,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,22 +2200,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827187</v>
+        <v>122827825</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2196,50 +2224,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529024</v>
+        <v>529088</v>
       </c>
       <c r="R15" t="n">
-        <v>6999326</v>
+        <v>6999396</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2266,19 +2290,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,22 +2312,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122827346</v>
+        <v>122828804</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2321,34 +2340,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528959</v>
+        <v>529036</v>
       </c>
       <c r="R16" t="n">
-        <v>6999360</v>
+        <v>6999404</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2381,6 +2405,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,10 +2436,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122828604</v>
+        <v>122827341</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>79848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,52 +2448,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529051</v>
+        <v>528959</v>
       </c>
       <c r="R17" t="n">
-        <v>6999391</v>
+        <v>6999360</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2494,19 +2509,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,22 +2526,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122827390</v>
+        <v>122827355</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>79848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2545,47 +2550,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529042</v>
+        <v>528972</v>
       </c>
       <c r="R18" t="n">
-        <v>6999393</v>
+        <v>6999362</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2615,19 +2611,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2642,22 +2628,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122827178</v>
+        <v>122827642</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2666,38 +2652,52 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528960</v>
+        <v>529076</v>
       </c>
       <c r="R19" t="n">
-        <v>6999325</v>
+        <v>6999342</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2727,9 +2727,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,22 +2754,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122827642</v>
+        <v>122827543</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2768,52 +2778,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529076</v>
+        <v>529010</v>
       </c>
       <c r="R20" t="n">
-        <v>6999342</v>
+        <v>6999427</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2845,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2855,7 +2856,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,7 +2876,7 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2882,10 +2888,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122827825</v>
+        <v>122827597</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2894,43 +2900,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529088</v>
+        <v>529078</v>
       </c>
       <c r="R21" t="n">
-        <v>6999396</v>
+        <v>6999325</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2960,14 +2975,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2982,22 +3002,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122828769</v>
+        <v>122827466</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3006,38 +3026,52 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529028</v>
+        <v>529066</v>
       </c>
       <c r="R22" t="n">
-        <v>6999409</v>
+        <v>6999328</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3069,7 +3103,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3079,12 +3113,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På sälgstubbe</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3111,10 +3140,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122828216</v>
+        <v>122827617</v>
       </c>
       <c r="B23" t="n">
-        <v>98355</v>
+        <v>74863</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3123,55 +3152,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529096</v>
+        <v>528989</v>
       </c>
       <c r="R23" t="n">
-        <v>6999434</v>
+        <v>6999409</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3200,7 +3215,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3210,7 +3225,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3225,7 +3245,7 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3237,10 +3257,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122827280</v>
+        <v>122827410</v>
       </c>
       <c r="B24" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3249,52 +3269,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529040</v>
+        <v>528970</v>
       </c>
       <c r="R24" t="n">
-        <v>6999362</v>
+        <v>6999398</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3324,24 +3330,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3356,22 +3347,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122827930</v>
+        <v>122827178</v>
       </c>
       <c r="B25" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3380,52 +3371,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529127</v>
+        <v>528960</v>
       </c>
       <c r="R25" t="n">
-        <v>6999402</v>
+        <v>6999325</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3455,19 +3432,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3482,22 +3449,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122828815</v>
+        <v>122827824</v>
       </c>
       <c r="B26" t="n">
-        <v>74847</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3506,41 +3473,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529024</v>
+        <v>529074</v>
       </c>
       <c r="R26" t="n">
-        <v>6999406</v>
+        <v>6999358</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3569,7 +3541,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3579,12 +3551,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,22 +3571,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122828175</v>
+        <v>122827930</v>
       </c>
       <c r="B27" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3646,12 +3618,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3665,13 +3637,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529118</v>
+        <v>529127</v>
       </c>
       <c r="R27" t="n">
-        <v>6999441</v>
+        <v>6999402</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3700,7 +3672,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3710,7 +3682,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3737,10 +3709,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122827597</v>
+        <v>122828216</v>
       </c>
       <c r="B28" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3791,13 +3763,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529078</v>
+        <v>529096</v>
       </c>
       <c r="R28" t="n">
-        <v>6999325</v>
+        <v>6999434</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3826,7 +3798,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3836,7 +3808,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3863,10 +3835,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122827147</v>
+        <v>122828175</v>
       </c>
       <c r="B29" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3898,32 +3870,32 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529019</v>
+        <v>529118</v>
       </c>
       <c r="R29" t="n">
-        <v>6999321</v>
+        <v>6999441</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3952,7 +3924,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3962,12 +3934,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>1 vinterståndare på marken i gammal granskog</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3994,7 +3961,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122828091</v>
+        <v>122828304</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -4027,20 +3994,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529125</v>
+        <v>529073</v>
       </c>
       <c r="R30" t="n">
-        <v>6999359</v>
+        <v>6999451</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4067,11 +4043,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4080,51 +4071,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122827382</v>
+        <v>122827180</v>
       </c>
       <c r="B31" t="n">
-        <v>98355</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4133,47 +4099,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529080</v>
+        <v>529019</v>
       </c>
       <c r="R31" t="n">
-        <v>6999334</v>
+        <v>6999321</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4205,7 +4162,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4215,12 +4172,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4247,10 +4204,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122828385</v>
+        <v>122827848</v>
       </c>
       <c r="B32" t="n">
-        <v>77699</v>
+        <v>98357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4259,41 +4216,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529065</v>
+        <v>529118</v>
       </c>
       <c r="R32" t="n">
-        <v>6999450</v>
+        <v>6999379</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4322,7 +4293,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4332,12 +4303,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4364,10 +4330,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122827290</v>
+        <v>122827285</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4380,29 +4346,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
@@ -4471,10 +4432,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122827410</v>
+        <v>122828672</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4483,38 +4444,52 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528970</v>
+        <v>529025</v>
       </c>
       <c r="R34" t="n">
-        <v>6999398</v>
+        <v>6999399</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4544,9 +4519,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4561,22 +4546,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122827180</v>
+        <v>122827187</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4585,41 +4570,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529019</v>
+        <v>529024</v>
       </c>
       <c r="R35" t="n">
-        <v>6999321</v>
+        <v>6999326</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4659,11 +4653,6 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4678,22 +4667,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122827848</v>
+        <v>122827346</v>
       </c>
       <c r="B36" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4702,55 +4691,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529118</v>
+        <v>528959</v>
       </c>
       <c r="R36" t="n">
-        <v>6999379</v>
+        <v>6999360</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4777,19 +4752,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4804,22 +4769,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122827958</v>
+        <v>122827366</v>
       </c>
       <c r="B37" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4832,21 +4797,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4856,13 +4821,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529113</v>
+        <v>528972</v>
       </c>
       <c r="R37" t="n">
-        <v>6999364</v>
+        <v>6999362</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4889,24 +4854,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4921,22 +4871,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122827366</v>
+        <v>122827275</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4949,21 +4899,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4973,10 +4923,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528972</v>
+        <v>529045</v>
       </c>
       <c r="R38" t="n">
-        <v>6999362</v>
+        <v>6999365</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5006,9 +4956,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5023,22 +4988,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122827617</v>
+        <v>122828442</v>
       </c>
       <c r="B39" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5051,21 +5016,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5075,13 +5040,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528989</v>
+        <v>529071</v>
       </c>
       <c r="R39" t="n">
-        <v>6999409</v>
+        <v>6999422</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5110,7 +5075,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5120,12 +5085,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5140,22 +5105,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122827484</v>
+        <v>122828745</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5164,43 +5129,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528970</v>
+        <v>529035</v>
       </c>
       <c r="R40" t="n">
-        <v>6999399</v>
+        <v>6999405</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5233,11 +5197,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5264,10 +5223,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122828442</v>
+        <v>122828537</v>
       </c>
       <c r="B41" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5280,21 +5239,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5304,13 +5263,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529071</v>
+        <v>529161</v>
       </c>
       <c r="R41" t="n">
-        <v>6999422</v>
+        <v>6999364</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5337,24 +5296,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5365,26 +5314,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122828672</v>
+        <v>122827484</v>
       </c>
       <c r="B42" t="n">
-        <v>98355</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5393,49 +5367,40 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529025</v>
+        <v>528970</v>
       </c>
       <c r="R42" t="n">
         <v>6999399</v>
@@ -5468,19 +5433,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:29</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5495,22 +5455,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827285</v>
+        <v>122827686</v>
       </c>
       <c r="B43" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5523,21 +5483,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5547,10 +5507,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528951</v>
+        <v>529073</v>
       </c>
       <c r="R43" t="n">
-        <v>6999355</v>
+        <v>6999336</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5580,9 +5540,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5597,22 +5572,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122827543</v>
+        <v>122828815</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>74847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5621,43 +5596,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529010</v>
+        <v>529024</v>
       </c>
       <c r="R44" t="n">
-        <v>6999427</v>
+        <v>6999406</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5689,7 +5659,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5699,12 +5669,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5719,22 +5689,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122827556</v>
+        <v>122827147</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5743,41 +5713,55 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528995</v>
+        <v>529019</v>
       </c>
       <c r="R45" t="n">
-        <v>6999419</v>
+        <v>6999321</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5804,9 +5788,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5821,22 +5820,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122828745</v>
+        <v>122827232</v>
       </c>
       <c r="B46" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5845,30 +5844,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529035</v>
+        <v>528947</v>
       </c>
       <c r="R46" t="n">
-        <v>6999405</v>
+        <v>6999334</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5942,7 +5942,7 @@
         <v>122827606</v>
       </c>
       <c r="B47" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>122828817</v>
       </c>
       <c r="B49" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122828604</v>
+        <v>122827718</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,52 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529051</v>
+        <v>529085</v>
       </c>
       <c r="R3" t="n">
-        <v>6999391</v>
+        <v>6999343</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,17 +897,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827280</v>
+        <v>122827504</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,52 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529040</v>
+        <v>529070</v>
       </c>
       <c r="R4" t="n">
-        <v>6999362</v>
+        <v>6999301</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>3 vinterståndare i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122827718</v>
+        <v>122827290</v>
       </c>
       <c r="B5" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529085</v>
+        <v>528951</v>
       </c>
       <c r="R5" t="n">
-        <v>6999343</v>
+        <v>6999355</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,24 +1099,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122827504</v>
+        <v>122828604</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,38 +1140,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529070</v>
+        <v>529051</v>
       </c>
       <c r="R6" t="n">
-        <v>6999301</v>
+        <v>6999391</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,12 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,17 +1247,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122827290</v>
+        <v>122827280</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,31 +1266,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1323,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528951</v>
+        <v>529040</v>
       </c>
       <c r="R7" t="n">
-        <v>6999355</v>
+        <v>6999362</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,9 +1341,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,12 +1373,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827556</v>
+        <v>122827825</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2126,34 +2126,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528995</v>
+        <v>529088</v>
       </c>
       <c r="R14" t="n">
-        <v>6999419</v>
+        <v>6999396</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2186,6 +2191,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2212,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827825</v>
+        <v>122827556</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2228,39 +2238,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529088</v>
+        <v>528995</v>
       </c>
       <c r="R15" t="n">
-        <v>6999396</v>
+        <v>6999419</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2293,11 +2298,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2538,10 +2538,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122827355</v>
+        <v>122827642</v>
       </c>
       <c r="B18" t="n">
-        <v>79848</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2550,38 +2550,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528972</v>
+        <v>529076</v>
       </c>
       <c r="R18" t="n">
-        <v>6999362</v>
+        <v>6999342</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2611,9 +2625,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,22 +2652,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122827642</v>
+        <v>122827355</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>79848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,52 +2676,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529076</v>
+        <v>528972</v>
       </c>
       <c r="R19" t="n">
-        <v>6999342</v>
+        <v>6999362</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2727,19 +2737,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,12 +2754,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -4204,10 +4204,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122827848</v>
+        <v>122827285</v>
       </c>
       <c r="B32" t="n">
-        <v>98357</v>
+        <v>79848</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4216,55 +4216,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529118</v>
+        <v>528951</v>
       </c>
       <c r="R32" t="n">
-        <v>6999379</v>
+        <v>6999355</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4291,19 +4277,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4318,22 +4294,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122827285</v>
+        <v>122828672</v>
       </c>
       <c r="B33" t="n">
-        <v>79848</v>
+        <v>98357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4342,38 +4318,52 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528951</v>
+        <v>529025</v>
       </c>
       <c r="R33" t="n">
-        <v>6999355</v>
+        <v>6999399</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4403,9 +4393,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4420,19 +4420,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122828672</v>
+        <v>122827848</v>
       </c>
       <c r="B34" t="n">
         <v>98357</v>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4486,13 +4486,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529025</v>
+        <v>529118</v>
       </c>
       <c r="R34" t="n">
-        <v>6999399</v>
+        <v>6999379</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -1385,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122828769</v>
+        <v>122828385</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,21 +1401,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1425,13 +1425,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529028</v>
+        <v>529065</v>
       </c>
       <c r="R8" t="n">
-        <v>6999409</v>
+        <v>6999450</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122828385</v>
+        <v>122828769</v>
       </c>
       <c r="B9" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,21 +1518,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529065</v>
+        <v>529028</v>
       </c>
       <c r="R9" t="n">
-        <v>6999450</v>
+        <v>6999409</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2110,10 +2110,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827825</v>
+        <v>122827556</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2126,39 +2126,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529088</v>
+        <v>528995</v>
       </c>
       <c r="R14" t="n">
-        <v>6999396</v>
+        <v>6999419</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2191,11 +2186,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2222,10 +2212,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827556</v>
+        <v>122827825</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2238,34 +2228,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528995</v>
+        <v>529088</v>
       </c>
       <c r="R15" t="n">
-        <v>6999419</v>
+        <v>6999396</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2298,6 +2293,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122828804</v>
+        <v>122827341</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2340,39 +2340,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529036</v>
+        <v>528959</v>
       </c>
       <c r="R16" t="n">
-        <v>6999404</v>
+        <v>6999360</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2405,11 +2400,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2436,10 +2426,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122827341</v>
+        <v>122828804</v>
       </c>
       <c r="B17" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2452,34 +2442,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528959</v>
+        <v>529036</v>
       </c>
       <c r="R17" t="n">
-        <v>6999360</v>
+        <v>6999404</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2512,6 +2507,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2766,10 +2766,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122827543</v>
+        <v>122827617</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2782,42 +2782,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529010</v>
+        <v>528989</v>
       </c>
       <c r="R20" t="n">
-        <v>6999427</v>
+        <v>6999409</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2846,7 +2841,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2856,12 +2851,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2888,10 +2883,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122827597</v>
+        <v>122827410</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2900,52 +2895,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529078</v>
+        <v>528970</v>
       </c>
       <c r="R21" t="n">
-        <v>6999325</v>
+        <v>6999398</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2975,19 +2956,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3002,22 +2973,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122827466</v>
+        <v>122827543</v>
       </c>
       <c r="B22" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3026,52 +2997,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529066</v>
+        <v>529010</v>
       </c>
       <c r="R22" t="n">
-        <v>6999328</v>
+        <v>6999427</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3103,7 +3065,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3113,7 +3075,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3128,7 +3095,7 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3140,10 +3107,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122827617</v>
+        <v>122827597</v>
       </c>
       <c r="B23" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3152,41 +3119,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528989</v>
+        <v>529078</v>
       </c>
       <c r="R23" t="n">
-        <v>6999409</v>
+        <v>6999325</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3226,11 +3207,6 @@
       <c r="AB23" t="inlineStr">
         <is>
           <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3245,22 +3221,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122827410</v>
+        <v>122827466</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3269,38 +3245,52 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528970</v>
+        <v>529066</v>
       </c>
       <c r="R24" t="n">
-        <v>6999398</v>
+        <v>6999328</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3330,9 +3320,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3347,12 +3347,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122828175</v>
+        <v>122828304</v>
       </c>
       <c r="B29" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3847,40 +3847,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3889,13 +3884,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529118</v>
+        <v>529073</v>
       </c>
       <c r="R29" t="n">
-        <v>6999441</v>
+        <v>6999451</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3924,7 +3919,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3934,7 +3929,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3961,7 +3961,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122828304</v>
+        <v>122827180</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3994,26 +3994,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529073</v>
+        <v>529019</v>
       </c>
       <c r="R30" t="n">
-        <v>6999451</v>
+        <v>6999321</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4045,7 +4036,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4055,12 +4046,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4087,10 +4078,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122827180</v>
+        <v>122828175</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4099,41 +4090,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529019</v>
+        <v>529118</v>
       </c>
       <c r="R31" t="n">
-        <v>6999321</v>
+        <v>6999441</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4162,7 +4167,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4172,12 +4177,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4679,10 +4679,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122827346</v>
+        <v>122828442</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4695,21 +4695,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528959</v>
+        <v>529071</v>
       </c>
       <c r="R36" t="n">
-        <v>6999360</v>
+        <v>6999422</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4752,9 +4752,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4769,19 +4784,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122827366</v>
+        <v>122827346</v>
       </c>
       <c r="B37" t="n">
         <v>79847</v>
@@ -4821,10 +4836,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528972</v>
+        <v>528959</v>
       </c>
       <c r="R37" t="n">
-        <v>6999362</v>
+        <v>6999360</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4883,10 +4898,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122827275</v>
+        <v>122827366</v>
       </c>
       <c r="B38" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4899,21 +4914,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4923,10 +4938,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529045</v>
+        <v>528972</v>
       </c>
       <c r="R38" t="n">
-        <v>6999365</v>
+        <v>6999362</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4956,24 +4971,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4988,22 +4988,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122828442</v>
+        <v>122827275</v>
       </c>
       <c r="B39" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5016,21 +5016,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529071</v>
+        <v>529045</v>
       </c>
       <c r="R39" t="n">
-        <v>6999422</v>
+        <v>6999365</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5105,12 +5105,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122827484</v>
+        <v>122827686</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5371,39 +5371,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528970</v>
+        <v>529073</v>
       </c>
       <c r="R42" t="n">
-        <v>6999399</v>
+        <v>6999336</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5433,14 +5428,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5455,22 +5460,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827686</v>
+        <v>122827484</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5483,34 +5488,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529073</v>
+        <v>528970</v>
       </c>
       <c r="R43" t="n">
-        <v>6999336</v>
+        <v>6999399</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5540,24 +5550,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Längsta bål 60 cm</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5572,12 +5572,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -1385,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122828385</v>
+        <v>122828769</v>
       </c>
       <c r="B8" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,21 +1401,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1425,13 +1425,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529065</v>
+        <v>529028</v>
       </c>
       <c r="R8" t="n">
-        <v>6999450</v>
+        <v>6999409</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122828769</v>
+        <v>122828385</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,21 +1518,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529028</v>
+        <v>529065</v>
       </c>
       <c r="R9" t="n">
-        <v>6999409</v>
+        <v>6999450</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2110,10 +2110,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827556</v>
+        <v>122827825</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2126,34 +2126,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528995</v>
+        <v>529088</v>
       </c>
       <c r="R14" t="n">
-        <v>6999419</v>
+        <v>6999396</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2186,6 +2191,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2212,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827825</v>
+        <v>122827556</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2228,39 +2238,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529088</v>
+        <v>528995</v>
       </c>
       <c r="R15" t="n">
-        <v>6999396</v>
+        <v>6999419</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2293,11 +2298,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122827341</v>
+        <v>122828804</v>
       </c>
       <c r="B16" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2340,34 +2340,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528959</v>
+        <v>529036</v>
       </c>
       <c r="R16" t="n">
-        <v>6999360</v>
+        <v>6999404</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2400,6 +2405,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,10 +2436,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122828804</v>
+        <v>122827341</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,39 +2452,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529036</v>
+        <v>528959</v>
       </c>
       <c r="R17" t="n">
-        <v>6999404</v>
+        <v>6999360</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2507,11 +2512,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,10 +2538,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122827642</v>
+        <v>122827355</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>79848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2550,52 +2550,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529076</v>
+        <v>528972</v>
       </c>
       <c r="R18" t="n">
-        <v>6999342</v>
+        <v>6999362</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2625,19 +2611,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2652,22 +2628,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122827355</v>
+        <v>122827642</v>
       </c>
       <c r="B19" t="n">
-        <v>79848</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2676,38 +2652,52 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528972</v>
+        <v>529076</v>
       </c>
       <c r="R19" t="n">
-        <v>6999362</v>
+        <v>6999342</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2737,9 +2727,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,22 +2754,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122827617</v>
+        <v>122827543</v>
       </c>
       <c r="B20" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2782,37 +2782,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528989</v>
+        <v>529010</v>
       </c>
       <c r="R20" t="n">
-        <v>6999409</v>
+        <v>6999427</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2841,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2851,12 +2856,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,10 +2888,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122827410</v>
+        <v>122827597</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2895,38 +2900,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528970</v>
+        <v>529078</v>
       </c>
       <c r="R21" t="n">
-        <v>6999398</v>
+        <v>6999325</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2956,9 +2975,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,22 +3002,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122827543</v>
+        <v>122827466</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2997,43 +3026,52 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529010</v>
+        <v>529066</v>
       </c>
       <c r="R22" t="n">
-        <v>6999427</v>
+        <v>6999328</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3065,7 +3103,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3075,12 +3113,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3095,7 +3128,7 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3107,10 +3140,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122827597</v>
+        <v>122827617</v>
       </c>
       <c r="B23" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3119,55 +3152,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529078</v>
+        <v>528989</v>
       </c>
       <c r="R23" t="n">
-        <v>6999325</v>
+        <v>6999409</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3207,6 +3226,11 @@
       <c r="AB23" t="inlineStr">
         <is>
           <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,22 +3245,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122827466</v>
+        <v>122827410</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3245,52 +3269,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529066</v>
+        <v>528970</v>
       </c>
       <c r="R24" t="n">
-        <v>6999328</v>
+        <v>6999398</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3320,19 +3330,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3347,12 +3347,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122828304</v>
+        <v>122828175</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3847,35 +3847,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3884,13 +3889,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529073</v>
+        <v>529118</v>
       </c>
       <c r="R29" t="n">
-        <v>6999451</v>
+        <v>6999441</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3919,7 +3924,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3929,12 +3934,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3961,7 +3961,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122827180</v>
+        <v>122828304</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3994,17 +3994,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529019</v>
+        <v>529073</v>
       </c>
       <c r="R30" t="n">
-        <v>6999321</v>
+        <v>6999451</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4036,7 +4045,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4046,12 +4055,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4078,10 +4087,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122828175</v>
+        <v>122827180</v>
       </c>
       <c r="B31" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4090,55 +4099,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529118</v>
+        <v>529019</v>
       </c>
       <c r="R31" t="n">
-        <v>6999441</v>
+        <v>6999321</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4167,7 +4162,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4177,7 +4172,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4679,10 +4679,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122828442</v>
+        <v>122827346</v>
       </c>
       <c r="B36" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4695,21 +4695,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529071</v>
+        <v>528959</v>
       </c>
       <c r="R36" t="n">
-        <v>6999422</v>
+        <v>6999360</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4752,24 +4752,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4784,19 +4769,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122827346</v>
+        <v>122827366</v>
       </c>
       <c r="B37" t="n">
         <v>79847</v>
@@ -4836,10 +4821,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528959</v>
+        <v>528972</v>
       </c>
       <c r="R37" t="n">
-        <v>6999360</v>
+        <v>6999362</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4898,10 +4883,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122827366</v>
+        <v>122827275</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4914,21 +4899,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4938,10 +4923,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528972</v>
+        <v>529045</v>
       </c>
       <c r="R38" t="n">
-        <v>6999362</v>
+        <v>6999365</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4971,9 +4956,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4988,22 +4988,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122827275</v>
+        <v>122828442</v>
       </c>
       <c r="B39" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5016,21 +5016,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529045</v>
+        <v>529071</v>
       </c>
       <c r="R39" t="n">
-        <v>6999365</v>
+        <v>6999422</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5105,12 +5105,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122828006</v>
+        <v>122828604</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529145</v>
+        <v>529051</v>
       </c>
       <c r="R2" t="n">
-        <v>6999399</v>
+        <v>6999391</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,14 +762,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122827718</v>
+        <v>122827382</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +813,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529085</v>
+        <v>529080</v>
       </c>
       <c r="R3" t="n">
-        <v>6999343</v>
+        <v>6999334</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827504</v>
+        <v>122827366</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529070</v>
+        <v>528972</v>
       </c>
       <c r="R4" t="n">
-        <v>6999301</v>
+        <v>6999362</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,24 +1000,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1017,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122827290</v>
+        <v>122828304</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,27 +1045,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528951</v>
+        <v>529073</v>
       </c>
       <c r="R5" t="n">
-        <v>6999355</v>
+        <v>6999451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,9 +1111,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1143,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122828604</v>
+        <v>122827232</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,40 +1167,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1182,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529051</v>
+        <v>528947</v>
       </c>
       <c r="R6" t="n">
-        <v>6999391</v>
+        <v>6999334</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,19 +1233,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,22 +1250,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122827280</v>
+        <v>122827718</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,52 +1274,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529040</v>
+        <v>529085</v>
       </c>
       <c r="R7" t="n">
-        <v>6999362</v>
+        <v>6999343</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1347,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>3 vinterståndare i gammal granskog</t>
+          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122828769</v>
+        <v>122827686</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,21 +1395,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1425,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529028</v>
+        <v>529073</v>
       </c>
       <c r="R8" t="n">
-        <v>6999409</v>
+        <v>6999336</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1464,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1496,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122828385</v>
+        <v>122827178</v>
       </c>
       <c r="B9" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,21 +1512,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1542,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529065</v>
+        <v>528960</v>
       </c>
       <c r="R9" t="n">
-        <v>6999450</v>
+        <v>6999325</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1575,24 +1569,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,19 +1586,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122827382</v>
+        <v>122828745</v>
       </c>
       <c r="B10" t="n">
         <v>98357</v>
@@ -1654,12 +1633,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1668,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529080</v>
+        <v>529035</v>
       </c>
       <c r="R10" t="n">
-        <v>6999334</v>
+        <v>6999405</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,24 +1675,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,22 +1692,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122827390</v>
+        <v>122828769</v>
       </c>
       <c r="B11" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,47 +1716,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529042</v>
+        <v>529028</v>
       </c>
       <c r="R11" t="n">
-        <v>6999393</v>
+        <v>6999409</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1839,7 +1789,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,22 +1809,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827958</v>
+        <v>122827556</v>
       </c>
       <c r="B12" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1882,21 +1837,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1906,13 +1861,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529113</v>
+        <v>528995</v>
       </c>
       <c r="R12" t="n">
-        <v>6999364</v>
+        <v>6999419</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1939,24 +1894,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,22 +1911,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122828091</v>
+        <v>122827410</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,21 +1939,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2023,13 +1963,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529125</v>
+        <v>528970</v>
       </c>
       <c r="R13" t="n">
-        <v>6999359</v>
+        <v>6999398</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2069,31 +2009,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2110,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827825</v>
+        <v>122827958</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2126,42 +2041,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529088</v>
+        <v>529113</v>
       </c>
       <c r="R14" t="n">
-        <v>6999396</v>
+        <v>6999364</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2188,14 +2098,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,22 +2130,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827556</v>
+        <v>122827597</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,38 +2154,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528995</v>
+        <v>529078</v>
       </c>
       <c r="R15" t="n">
-        <v>6999419</v>
+        <v>6999325</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,9 +2229,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,22 +2256,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122828804</v>
+        <v>122827466</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,43 +2280,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529036</v>
+        <v>529066</v>
       </c>
       <c r="R16" t="n">
-        <v>6999404</v>
+        <v>6999328</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2402,14 +2355,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2424,22 +2382,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122827341</v>
+        <v>122827825</v>
       </c>
       <c r="B17" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2452,34 +2410,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528959</v>
+        <v>529088</v>
       </c>
       <c r="R17" t="n">
-        <v>6999360</v>
+        <v>6999396</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2512,6 +2475,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122827355</v>
+        <v>122828672</v>
       </c>
       <c r="B18" t="n">
-        <v>79848</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2550,38 +2518,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528972</v>
+        <v>529025</v>
       </c>
       <c r="R18" t="n">
-        <v>6999362</v>
+        <v>6999399</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2611,9 +2593,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,22 +2620,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122827642</v>
+        <v>122827355</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>79848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,52 +2644,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529076</v>
+        <v>528972</v>
       </c>
       <c r="R19" t="n">
-        <v>6999342</v>
+        <v>6999362</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2727,19 +2705,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,22 +2722,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122827543</v>
+        <v>122828091</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2782,42 +2750,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529010</v>
+        <v>529125</v>
       </c>
       <c r="R20" t="n">
-        <v>6999427</v>
+        <v>6999359</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2844,26 +2807,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2872,23 +2820,48 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122827597</v>
+        <v>122828175</v>
       </c>
       <c r="B21" t="n">
         <v>98357</v>
@@ -2923,12 +2896,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2942,13 +2915,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529078</v>
+        <v>529118</v>
       </c>
       <c r="R21" t="n">
-        <v>6999325</v>
+        <v>6999441</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2977,7 +2950,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2987,7 +2960,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3007,17 +2980,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122827466</v>
+        <v>122828385</v>
       </c>
       <c r="B22" t="n">
-        <v>98357</v>
+        <v>77699</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3026,55 +2999,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529066</v>
+        <v>529065</v>
       </c>
       <c r="R22" t="n">
-        <v>6999328</v>
+        <v>6999450</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3103,7 +3062,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3113,7 +3072,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3140,10 +3104,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122827617</v>
+        <v>122827504</v>
       </c>
       <c r="B23" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3156,21 +3120,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3180,13 +3144,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528989</v>
+        <v>529070</v>
       </c>
       <c r="R23" t="n">
-        <v>6999409</v>
+        <v>6999301</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3215,7 +3179,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3225,12 +3189,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3245,7 +3209,7 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3257,10 +3221,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122827410</v>
+        <v>122828537</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3273,21 +3237,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3297,13 +3261,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528970</v>
+        <v>529161</v>
       </c>
       <c r="R24" t="n">
-        <v>6999398</v>
+        <v>6999364</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3335,6 +3299,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3343,6 +3312,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3359,10 +3353,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122827178</v>
+        <v>122828804</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3375,34 +3369,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528960</v>
+        <v>529036</v>
       </c>
       <c r="R25" t="n">
-        <v>6999325</v>
+        <v>6999404</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3435,6 +3434,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3461,7 +3465,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122827824</v>
+        <v>122827543</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3497,7 +3501,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3506,13 +3510,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529074</v>
+        <v>529010</v>
       </c>
       <c r="R26" t="n">
-        <v>6999358</v>
+        <v>6999427</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3541,7 +3545,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3551,12 +3555,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3583,7 +3587,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122827930</v>
+        <v>122827848</v>
       </c>
       <c r="B27" t="n">
         <v>98357</v>
@@ -3618,17 +3622,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3637,13 +3641,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529127</v>
+        <v>529118</v>
       </c>
       <c r="R27" t="n">
-        <v>6999402</v>
+        <v>6999379</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3672,7 +3676,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3682,7 +3686,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3709,7 +3713,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122828216</v>
+        <v>122827147</v>
       </c>
       <c r="B28" t="n">
         <v>98357</v>
@@ -3744,7 +3748,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3754,22 +3758,22 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529096</v>
+        <v>529019</v>
       </c>
       <c r="R28" t="n">
-        <v>6999434</v>
+        <v>6999321</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3798,7 +3802,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3808,7 +3812,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3828,14 +3837,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122828175</v>
+        <v>122828216</v>
       </c>
       <c r="B29" t="n">
         <v>98357</v>
@@ -3870,12 +3879,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3889,13 +3898,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529118</v>
+        <v>529096</v>
       </c>
       <c r="R29" t="n">
-        <v>6999441</v>
+        <v>6999434</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3924,7 +3933,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3934,7 +3943,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3961,10 +3970,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122828304</v>
+        <v>122827275</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3977,43 +3986,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529073</v>
+        <v>529045</v>
       </c>
       <c r="R30" t="n">
-        <v>6999451</v>
+        <v>6999365</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4075,12 +4075,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4197,17 +4197,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122827285</v>
+        <v>122827280</v>
       </c>
       <c r="B32" t="n">
-        <v>79848</v>
+        <v>98357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4216,38 +4216,52 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528951</v>
+        <v>529040</v>
       </c>
       <c r="R32" t="n">
-        <v>6999355</v>
+        <v>6999362</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4277,9 +4291,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4294,22 +4323,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122828672</v>
+        <v>122828815</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>74847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4318,52 +4347,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529025</v>
+        <v>529024</v>
       </c>
       <c r="R33" t="n">
-        <v>6999399</v>
+        <v>6999406</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4395,7 +4410,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4405,7 +4420,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4425,17 +4445,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122827848</v>
+        <v>122827484</v>
       </c>
       <c r="B34" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4444,55 +4464,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529118</v>
+        <v>528970</v>
       </c>
       <c r="R34" t="n">
-        <v>6999379</v>
+        <v>6999399</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4519,19 +4530,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>16:04</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4546,22 +4552,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122827187</v>
+        <v>122828442</v>
       </c>
       <c r="B35" t="n">
-        <v>98357</v>
+        <v>77699</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4570,50 +4576,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529024</v>
+        <v>529071</v>
       </c>
       <c r="R35" t="n">
-        <v>6999326</v>
+        <v>6999422</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4642,7 +4639,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4652,7 +4649,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4667,22 +4669,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122827346</v>
+        <v>122827642</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4691,38 +4693,52 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528959</v>
+        <v>529076</v>
       </c>
       <c r="R36" t="n">
-        <v>6999360</v>
+        <v>6999342</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4752,9 +4768,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4769,22 +4795,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122827366</v>
+        <v>122827390</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4793,38 +4819,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528972</v>
+        <v>529042</v>
       </c>
       <c r="R37" t="n">
-        <v>6999362</v>
+        <v>6999393</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4854,9 +4889,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4871,19 +4916,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122827275</v>
+        <v>122827617</v>
       </c>
       <c r="B38" t="n">
         <v>74863</v>
@@ -4923,13 +4968,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529045</v>
+        <v>528989</v>
       </c>
       <c r="R38" t="n">
-        <v>6999365</v>
+        <v>6999409</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4958,7 +5003,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4968,7 +5013,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5000,10 +5045,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122828442</v>
+        <v>122827285</v>
       </c>
       <c r="B39" t="n">
-        <v>77699</v>
+        <v>79848</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5016,21 +5061,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5040,10 +5085,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529071</v>
+        <v>528951</v>
       </c>
       <c r="R39" t="n">
-        <v>6999422</v>
+        <v>6999355</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5073,24 +5118,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5105,22 +5135,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122828745</v>
+        <v>122827824</v>
       </c>
       <c r="B40" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5129,45 +5159,46 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529035</v>
+        <v>529074</v>
       </c>
       <c r="R40" t="n">
-        <v>6999405</v>
+        <v>6999358</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5194,9 +5225,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5211,22 +5257,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122828537</v>
+        <v>122827187</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5235,41 +5281,50 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529161</v>
+        <v>529024</v>
       </c>
       <c r="R41" t="n">
-        <v>6999364</v>
+        <v>6999326</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5296,14 +5351,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5314,51 +5374,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122827686</v>
+        <v>122827930</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5367,38 +5402,52 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529073</v>
+        <v>529127</v>
       </c>
       <c r="R42" t="n">
-        <v>6999336</v>
+        <v>6999402</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5430,7 +5479,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5440,12 +5489,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Längsta bål 60 cm</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5472,10 +5516,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827484</v>
+        <v>122827341</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5488,39 +5532,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528970</v>
+        <v>528959</v>
       </c>
       <c r="R43" t="n">
-        <v>6999399</v>
+        <v>6999360</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5553,11 +5592,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5584,10 +5618,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122828815</v>
+        <v>122827346</v>
       </c>
       <c r="B44" t="n">
-        <v>74847</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5596,25 +5630,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5624,10 +5658,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529024</v>
+        <v>528959</v>
       </c>
       <c r="R44" t="n">
-        <v>6999406</v>
+        <v>6999360</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5657,24 +5691,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5689,22 +5708,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122827147</v>
+        <v>122827290</v>
       </c>
       <c r="B45" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5713,55 +5732,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529019</v>
+        <v>528951</v>
       </c>
       <c r="R45" t="n">
-        <v>6999321</v>
+        <v>6999355</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5788,24 +5798,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5820,22 +5815,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122827232</v>
+        <v>122828006</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5848,39 +5843,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528947</v>
+        <v>529145</v>
       </c>
       <c r="R46" t="n">
-        <v>6999334</v>
+        <v>6999399</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5913,6 +5908,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5939,10 +5939,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122827606</v>
+        <v>122827222</v>
       </c>
       <c r="B47" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5951,48 +5951,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>529023</v>
+        <v>529007</v>
       </c>
       <c r="R47" t="n">
-        <v>6999322</v>
+        <v>6999319</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6029,7 +6019,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 12 st skott och 1 st vinterståndare.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6044,6 +6034,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6061,10 +6071,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122827222</v>
+        <v>122827606</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6073,38 +6083,48 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529007</v>
+        <v>529023</v>
       </c>
       <c r="R48" t="n">
-        <v>6999319</v>
+        <v>6999322</v>
       </c>
       <c r="S48" t="n">
         <v>8</v>
@@ -6141,7 +6161,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Minst 12 st skott och 1 st vinterståndare.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6156,26 +6176,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122828304</v>
+        <v>122827232</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,31 +1045,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1078,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529073</v>
+        <v>528947</v>
       </c>
       <c r="R5" t="n">
-        <v>6999451</v>
+        <v>6999334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,24 +1107,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,22 +1124,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122827232</v>
+        <v>122828304</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,27 +1152,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528947</v>
+        <v>529073</v>
       </c>
       <c r="R6" t="n">
-        <v>6999334</v>
+        <v>6999451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,9 +1218,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,12 +1250,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827556</v>
+        <v>122827597</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,38 +1833,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528995</v>
+        <v>529078</v>
       </c>
       <c r="R12" t="n">
-        <v>6999419</v>
+        <v>6999325</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1894,9 +1908,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,22 +1935,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122827410</v>
+        <v>122827466</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,38 +1959,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528970</v>
+        <v>529066</v>
       </c>
       <c r="R13" t="n">
-        <v>6999398</v>
+        <v>6999328</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,9 +2034,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,22 +2061,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827958</v>
+        <v>122827556</v>
       </c>
       <c r="B14" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,21 +2089,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2065,13 +2113,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529113</v>
+        <v>528995</v>
       </c>
       <c r="R14" t="n">
-        <v>6999364</v>
+        <v>6999419</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,24 +2146,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,22 +2163,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827597</v>
+        <v>122827410</v>
       </c>
       <c r="B15" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,52 +2187,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529078</v>
+        <v>528970</v>
       </c>
       <c r="R15" t="n">
-        <v>6999325</v>
+        <v>6999398</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,19 +2248,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,22 +2265,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122827466</v>
+        <v>122827958</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>77699</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,55 +2289,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529066</v>
+        <v>529113</v>
       </c>
       <c r="R16" t="n">
-        <v>6999328</v>
+        <v>6999364</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2357,7 +2352,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2362,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,22 +2382,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122827825</v>
+        <v>122828672</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,43 +2406,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529088</v>
+        <v>529025</v>
       </c>
       <c r="R17" t="n">
-        <v>6999396</v>
+        <v>6999399</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,14 +2481,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,22 +2508,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122828672</v>
+        <v>122827825</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2518,52 +2532,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529025</v>
+        <v>529088</v>
       </c>
       <c r="R18" t="n">
-        <v>6999399</v>
+        <v>6999396</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2593,19 +2598,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:29</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,12 +2620,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -4335,10 +4335,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122828815</v>
+        <v>122827484</v>
       </c>
       <c r="B33" t="n">
-        <v>74847</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4347,38 +4347,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529024</v>
+        <v>528970</v>
       </c>
       <c r="R33" t="n">
-        <v>6999406</v>
+        <v>6999399</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4408,24 +4413,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4440,22 +4435,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122827484</v>
+        <v>122828442</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4468,39 +4463,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528970</v>
+        <v>529071</v>
       </c>
       <c r="R34" t="n">
-        <v>6999399</v>
+        <v>6999422</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4530,14 +4520,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,22 +4552,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122828442</v>
+        <v>122828815</v>
       </c>
       <c r="B35" t="n">
-        <v>77699</v>
+        <v>74847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4576,25 +4576,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>6439</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529071</v>
+        <v>529024</v>
       </c>
       <c r="R35" t="n">
-        <v>6999422</v>
+        <v>6999406</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5390,10 +5390,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122827930</v>
+        <v>122828006</v>
       </c>
       <c r="B42" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5402,52 +5402,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529127</v>
+        <v>529145</v>
       </c>
       <c r="R42" t="n">
-        <v>6999402</v>
+        <v>6999399</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5477,19 +5468,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:07</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5504,22 +5490,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827341</v>
+        <v>122827346</v>
       </c>
       <c r="B43" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5532,21 +5518,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5618,10 +5604,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122827346</v>
+        <v>122827341</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5634,21 +5620,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5827,10 +5813,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122828006</v>
+        <v>122827930</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5839,43 +5825,52 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529145</v>
+        <v>529127</v>
       </c>
       <c r="R46" t="n">
-        <v>6999399</v>
+        <v>6999402</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5905,14 +5900,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5927,12 +5927,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122827232</v>
+        <v>122828304</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,27 +1045,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528947</v>
+        <v>529073</v>
       </c>
       <c r="R5" t="n">
-        <v>6999334</v>
+        <v>6999451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,9 +1111,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,22 +1143,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122828304</v>
+        <v>122827232</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,31 +1171,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1185,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529073</v>
+        <v>528947</v>
       </c>
       <c r="R6" t="n">
-        <v>6999451</v>
+        <v>6999334</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,24 +1233,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,12 +1250,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122827686</v>
+        <v>122828745</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,38 +1391,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529073</v>
+        <v>529035</v>
       </c>
       <c r="R8" t="n">
-        <v>6999336</v>
+        <v>6999405</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,24 +1456,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,22 +1473,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122827178</v>
+        <v>122827686</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,21 +1501,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1536,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528960</v>
+        <v>529073</v>
       </c>
       <c r="R9" t="n">
-        <v>6999325</v>
+        <v>6999336</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,9 +1558,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,22 +1590,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122828745</v>
+        <v>122827178</v>
       </c>
       <c r="B10" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,42 +1614,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529035</v>
+        <v>528960</v>
       </c>
       <c r="R10" t="n">
-        <v>6999405</v>
+        <v>6999325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827597</v>
+        <v>122827556</v>
       </c>
       <c r="B12" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,52 +1833,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529078</v>
+        <v>528995</v>
       </c>
       <c r="R12" t="n">
-        <v>6999325</v>
+        <v>6999419</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,19 +1894,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,22 +1911,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122827466</v>
+        <v>122827410</v>
       </c>
       <c r="B13" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,52 +1935,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529066</v>
+        <v>528970</v>
       </c>
       <c r="R13" t="n">
-        <v>6999328</v>
+        <v>6999398</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,19 +1996,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,22 +2013,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827556</v>
+        <v>122827958</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,21 +2041,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2113,13 +2065,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528995</v>
+        <v>529113</v>
       </c>
       <c r="R14" t="n">
-        <v>6999419</v>
+        <v>6999364</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2146,9 +2098,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,22 +2130,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827410</v>
+        <v>122827597</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,38 +2154,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528970</v>
+        <v>529078</v>
       </c>
       <c r="R15" t="n">
-        <v>6999398</v>
+        <v>6999325</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,9 +2229,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,22 +2256,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122827958</v>
+        <v>122827466</v>
       </c>
       <c r="B16" t="n">
-        <v>77699</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,41 +2280,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529113</v>
+        <v>529066</v>
       </c>
       <c r="R16" t="n">
-        <v>6999364</v>
+        <v>6999328</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2352,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2362,12 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,22 +2382,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122828672</v>
+        <v>122827825</v>
       </c>
       <c r="B17" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,52 +2406,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529025</v>
+        <v>529088</v>
       </c>
       <c r="R17" t="n">
-        <v>6999399</v>
+        <v>6999396</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2481,19 +2472,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:29</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,22 +2494,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122827825</v>
+        <v>122828672</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,43 +2518,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529088</v>
+        <v>529025</v>
       </c>
       <c r="R18" t="n">
-        <v>6999396</v>
+        <v>6999399</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,14 +2593,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,12 +2620,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122827147</v>
+        <v>122827275</v>
       </c>
       <c r="B28" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3725,55 +3725,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529019</v>
+        <v>529045</v>
       </c>
       <c r="R28" t="n">
-        <v>6999321</v>
+        <v>6999365</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3802,7 +3788,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3812,12 +3798,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>1 vinterståndare på marken i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3832,7 +3818,7 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -3844,7 +3830,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122828216</v>
+        <v>122827147</v>
       </c>
       <c r="B29" t="n">
         <v>98357</v>
@@ -3879,7 +3865,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3889,22 +3875,22 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529096</v>
+        <v>529019</v>
       </c>
       <c r="R29" t="n">
-        <v>6999434</v>
+        <v>6999321</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3933,7 +3919,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3943,7 +3929,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3963,17 +3954,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122827275</v>
+        <v>122828216</v>
       </c>
       <c r="B30" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3982,41 +3973,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529045</v>
+        <v>529096</v>
       </c>
       <c r="R30" t="n">
-        <v>6999365</v>
+        <v>6999434</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4045,7 +4050,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4055,12 +4060,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4075,12 +4075,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4335,10 +4335,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122827484</v>
+        <v>122828815</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>74847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4347,43 +4347,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528970</v>
+        <v>529024</v>
       </c>
       <c r="R33" t="n">
-        <v>6999399</v>
+        <v>6999406</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4413,14 +4408,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4435,22 +4440,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122828442</v>
+        <v>122827484</v>
       </c>
       <c r="B34" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4463,34 +4468,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529071</v>
+        <v>528970</v>
       </c>
       <c r="R34" t="n">
-        <v>6999422</v>
+        <v>6999399</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4520,24 +4530,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,22 +4552,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122828815</v>
+        <v>122828442</v>
       </c>
       <c r="B35" t="n">
-        <v>74847</v>
+        <v>77699</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4576,25 +4576,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529024</v>
+        <v>529071</v>
       </c>
       <c r="R35" t="n">
-        <v>6999406</v>
+        <v>6999422</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5390,10 +5390,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122828006</v>
+        <v>122827930</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5402,43 +5402,52 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529145</v>
+        <v>529127</v>
       </c>
       <c r="R42" t="n">
-        <v>6999399</v>
+        <v>6999402</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5468,14 +5477,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5490,22 +5504,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827346</v>
+        <v>122827341</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5518,21 +5532,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5604,10 +5618,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122827341</v>
+        <v>122827346</v>
       </c>
       <c r="B44" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5620,21 +5634,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5813,10 +5827,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122827930</v>
+        <v>122828006</v>
       </c>
       <c r="B46" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5825,52 +5839,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529127</v>
+        <v>529145</v>
       </c>
       <c r="R46" t="n">
-        <v>6999402</v>
+        <v>6999399</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5900,19 +5905,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:07</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5927,12 +5927,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122828604</v>
+        <v>122827290</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529051</v>
+        <v>528951</v>
       </c>
       <c r="R2" t="n">
-        <v>6999391</v>
+        <v>6999355</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +753,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122827382</v>
+        <v>122827686</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,47 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529080</v>
+        <v>529073</v>
       </c>
       <c r="R3" t="n">
-        <v>6999334</v>
+        <v>6999336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827366</v>
+        <v>122827232</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -961,16 +933,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528972</v>
+        <v>528947</v>
       </c>
       <c r="R4" t="n">
-        <v>6999362</v>
+        <v>6999334</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122828304</v>
+        <v>122828006</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,43 +1022,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529073</v>
+        <v>529145</v>
       </c>
       <c r="R5" t="n">
-        <v>6999451</v>
+        <v>6999399</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,24 +1084,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,22 +1106,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122827232</v>
+        <v>122828091</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,42 +1134,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528947</v>
+        <v>529125</v>
       </c>
       <c r="R6" t="n">
-        <v>6999334</v>
+        <v>6999359</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,6 +1204,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1262,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122827718</v>
+        <v>122828604</v>
       </c>
       <c r="B7" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,38 +1257,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529085</v>
+        <v>529051</v>
       </c>
       <c r="R7" t="n">
-        <v>6999343</v>
+        <v>6999391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,12 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal i gammal granskog</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122828745</v>
+        <v>122828175</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,7 +1406,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1423,13 +1425,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529035</v>
+        <v>529118</v>
       </c>
       <c r="R8" t="n">
-        <v>6999405</v>
+        <v>6999441</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,9 +1458,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,22 +1485,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122827686</v>
+        <v>122827958</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,21 +1513,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1525,13 +1537,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529073</v>
+        <v>529113</v>
       </c>
       <c r="R9" t="n">
-        <v>6999336</v>
+        <v>6999364</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,12 +1582,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Längsta bål 60 cm</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,19 +1602,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122827178</v>
+        <v>122827556</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1642,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528960</v>
+        <v>528995</v>
       </c>
       <c r="R10" t="n">
-        <v>6999325</v>
+        <v>6999419</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122828769</v>
+        <v>122828804</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,34 +1732,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529028</v>
+        <v>529036</v>
       </c>
       <c r="R11" t="n">
-        <v>6999409</v>
+        <v>6999404</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,24 +1794,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,22 +1816,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827556</v>
+        <v>122827824</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,37 +1844,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528995</v>
+        <v>529074</v>
       </c>
       <c r="R12" t="n">
-        <v>6999419</v>
+        <v>6999358</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1894,9 +1906,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,22 +1938,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122827410</v>
+        <v>122828745</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,38 +1962,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528970</v>
+        <v>529035</v>
       </c>
       <c r="R13" t="n">
-        <v>6999398</v>
+        <v>6999405</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827958</v>
+        <v>122827390</v>
       </c>
       <c r="B14" t="n">
-        <v>77699</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,41 +2068,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529113</v>
+        <v>529042</v>
       </c>
       <c r="R14" t="n">
-        <v>6999364</v>
+        <v>6999393</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2100,7 +2140,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2110,12 +2150,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827597</v>
+        <v>122827484</v>
       </c>
       <c r="B15" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,52 +2189,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529078</v>
+        <v>528970</v>
       </c>
       <c r="R15" t="n">
-        <v>6999325</v>
+        <v>6999399</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,19 +2255,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:59</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,22 +2277,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122827466</v>
+        <v>122827147</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,12 +2324,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2318,17 +2339,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529066</v>
+        <v>529019</v>
       </c>
       <c r="R16" t="n">
-        <v>6999328</v>
+        <v>6999321</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2357,7 +2378,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2388,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122827825</v>
+        <v>122827848</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,46 +2432,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529088</v>
+        <v>529118</v>
       </c>
       <c r="R17" t="n">
-        <v>6999396</v>
+        <v>6999379</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2472,14 +2507,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,22 +2534,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122828672</v>
+        <v>122828537</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2518,55 +2558,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529025</v>
+        <v>529161</v>
       </c>
       <c r="R18" t="n">
-        <v>6999399</v>
+        <v>6999364</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2593,19 +2619,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:29</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,26 +2637,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122827355</v>
+        <v>122828815</v>
       </c>
       <c r="B19" t="n">
-        <v>79848</v>
+        <v>74847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,25 +2690,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2672,10 +2718,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528972</v>
+        <v>529024</v>
       </c>
       <c r="R19" t="n">
-        <v>6999362</v>
+        <v>6999406</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,9 +2751,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2722,22 +2783,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122828091</v>
+        <v>122827617</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,21 +2811,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2774,13 +2835,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529125</v>
+        <v>528989</v>
       </c>
       <c r="R20" t="n">
-        <v>6999359</v>
+        <v>6999409</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2807,11 +2868,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2820,51 +2896,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122828175</v>
+        <v>122827930</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2896,12 +2947,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2915,13 +2966,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529118</v>
+        <v>529127</v>
       </c>
       <c r="R21" t="n">
-        <v>6999441</v>
+        <v>6999402</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2950,7 +3001,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2960,7 +3011,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2987,10 +3038,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122828385</v>
+        <v>122827382</v>
       </c>
       <c r="B22" t="n">
-        <v>77699</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2999,41 +3050,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529065</v>
+        <v>529080</v>
       </c>
       <c r="R22" t="n">
-        <v>6999450</v>
+        <v>6999334</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3062,7 +3122,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3072,12 +3132,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3104,10 +3164,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122827504</v>
+        <v>122827466</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3116,38 +3176,52 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529070</v>
+        <v>529066</v>
       </c>
       <c r="R23" t="n">
-        <v>6999301</v>
+        <v>6999328</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3179,7 +3253,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3189,12 +3263,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,10 +3290,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122828537</v>
+        <v>122828385</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3237,21 +3306,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3261,13 +3330,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529161</v>
+        <v>529065</v>
       </c>
       <c r="R24" t="n">
-        <v>6999364</v>
+        <v>6999450</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3294,14 +3363,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3312,51 +3391,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122828804</v>
+        <v>122827275</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3369,39 +3423,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529036</v>
+        <v>529045</v>
       </c>
       <c r="R25" t="n">
-        <v>6999404</v>
+        <v>6999365</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3431,14 +3480,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3453,22 +3512,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122827543</v>
+        <v>122827178</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3481,39 +3540,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529010</v>
+        <v>528960</v>
       </c>
       <c r="R26" t="n">
-        <v>6999427</v>
+        <v>6999325</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3543,24 +3597,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3575,22 +3614,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122827848</v>
+        <v>122827504</v>
       </c>
       <c r="B27" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3599,55 +3638,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529118</v>
+        <v>529070</v>
       </c>
       <c r="R27" t="n">
-        <v>6999379</v>
+        <v>6999301</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3676,7 +3701,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3686,7 +3711,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3713,10 +3743,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122827275</v>
+        <v>122827366</v>
       </c>
       <c r="B28" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3729,21 +3759,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3753,10 +3783,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529045</v>
+        <v>528972</v>
       </c>
       <c r="R28" t="n">
-        <v>6999365</v>
+        <v>6999362</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3786,24 +3816,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3818,22 +3833,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122827147</v>
+        <v>122827543</v>
       </c>
       <c r="B29" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3842,55 +3857,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529019</v>
+        <v>529010</v>
       </c>
       <c r="R29" t="n">
-        <v>6999321</v>
+        <v>6999427</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3919,7 +3925,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3929,12 +3935,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1 vinterståndare på marken i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3949,7 +3955,7 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -3961,10 +3967,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122828216</v>
+        <v>122828442</v>
       </c>
       <c r="B30" t="n">
-        <v>98357</v>
+        <v>77699</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3973,55 +3979,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529096</v>
+        <v>529071</v>
       </c>
       <c r="R30" t="n">
-        <v>6999434</v>
+        <v>6999422</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4050,7 +4042,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4060,7 +4052,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4087,10 +4084,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122827180</v>
+        <v>122827597</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4099,38 +4096,52 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529019</v>
+        <v>529078</v>
       </c>
       <c r="R31" t="n">
-        <v>6999321</v>
+        <v>6999325</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4162,7 +4173,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4172,12 +4183,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4197,7 +4203,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4207,7 +4213,7 @@
         <v>122827280</v>
       </c>
       <c r="B32" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4335,10 +4341,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122828815</v>
+        <v>122828769</v>
       </c>
       <c r="B33" t="n">
-        <v>74847</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4347,25 +4353,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4375,10 +4381,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529024</v>
+        <v>529028</v>
       </c>
       <c r="R33" t="n">
-        <v>6999406</v>
+        <v>6999409</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4410,7 +4416,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4420,7 +4426,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4452,10 +4458,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122827484</v>
+        <v>122827642</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4464,43 +4470,52 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528970</v>
+        <v>529076</v>
       </c>
       <c r="R34" t="n">
-        <v>6999399</v>
+        <v>6999342</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4530,14 +4545,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,22 +4572,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122828442</v>
+        <v>122827355</v>
       </c>
       <c r="B35" t="n">
-        <v>77699</v>
+        <v>79848</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4580,21 +4600,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4604,10 +4624,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529071</v>
+        <v>528972</v>
       </c>
       <c r="R35" t="n">
-        <v>6999422</v>
+        <v>6999362</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4637,24 +4657,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4669,22 +4674,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122827642</v>
+        <v>122827180</v>
       </c>
       <c r="B36" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4693,52 +4698,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529076</v>
+        <v>529019</v>
       </c>
       <c r="R36" t="n">
-        <v>6999342</v>
+        <v>6999321</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4770,7 +4761,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4780,7 +4771,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4807,10 +4803,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122827390</v>
+        <v>122828304</v>
       </c>
       <c r="B37" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4819,35 +4815,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4856,10 +4852,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529042</v>
+        <v>529073</v>
       </c>
       <c r="R37" t="n">
-        <v>6999393</v>
+        <v>6999451</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4891,7 +4887,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4901,7 +4897,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4916,19 +4917,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122827617</v>
+        <v>122827718</v>
       </c>
       <c r="B38" t="n">
         <v>74863</v>
@@ -4968,13 +4969,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528989</v>
+        <v>529085</v>
       </c>
       <c r="R38" t="n">
-        <v>6999409</v>
+        <v>6999343</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5003,7 +5004,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5013,12 +5014,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5033,22 +5034,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122827285</v>
+        <v>122827410</v>
       </c>
       <c r="B39" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5061,21 +5062,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5085,10 +5086,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528951</v>
+        <v>528970</v>
       </c>
       <c r="R39" t="n">
-        <v>6999355</v>
+        <v>6999398</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5147,10 +5148,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122827824</v>
+        <v>122827346</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5163,42 +5164,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529074</v>
+        <v>528959</v>
       </c>
       <c r="R40" t="n">
-        <v>6999358</v>
+        <v>6999360</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5225,24 +5221,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5257,22 +5238,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122827187</v>
+        <v>122828216</v>
       </c>
       <c r="B41" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5304,12 +5285,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5318,13 +5304,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529024</v>
+        <v>529096</v>
       </c>
       <c r="R41" t="n">
-        <v>6999326</v>
+        <v>6999434</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5353,7 +5339,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5363,7 +5349,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5378,7 +5364,7 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -5390,10 +5376,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122827930</v>
+        <v>122827285</v>
       </c>
       <c r="B42" t="n">
-        <v>98357</v>
+        <v>79848</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5402,52 +5388,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529127</v>
+        <v>528951</v>
       </c>
       <c r="R42" t="n">
-        <v>6999402</v>
+        <v>6999355</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5477,19 +5449,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5504,22 +5466,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827341</v>
+        <v>122828672</v>
       </c>
       <c r="B43" t="n">
-        <v>79848</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5528,38 +5490,52 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528959</v>
+        <v>529025</v>
       </c>
       <c r="R43" t="n">
-        <v>6999360</v>
+        <v>6999399</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5589,9 +5565,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5606,22 +5592,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122827346</v>
+        <v>122827341</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5634,21 +5620,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5720,10 +5706,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122827290</v>
+        <v>122827187</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5732,31 +5718,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5765,13 +5755,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528951</v>
+        <v>529024</v>
       </c>
       <c r="R45" t="n">
-        <v>6999355</v>
+        <v>6999326</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5798,9 +5788,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5815,19 +5815,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122828006</v>
+        <v>122827825</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529145</v>
+        <v>529088</v>
       </c>
       <c r="R46" t="n">
-        <v>6999399</v>
+        <v>6999396</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6074,7 +6074,7 @@
         <v>122827606</v>
       </c>
       <c r="B48" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>122828817</v>
       </c>
       <c r="B49" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122828091</v>
+        <v>122828604</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,41 +1130,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529125</v>
+        <v>529051</v>
       </c>
       <c r="R6" t="n">
-        <v>6999359</v>
+        <v>6999391</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,11 +1205,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1204,48 +1228,23 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122828604</v>
+        <v>122828175</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1280,7 +1279,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1290,7 +1289,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,13 +1298,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529051</v>
+        <v>529118</v>
       </c>
       <c r="R7" t="n">
-        <v>6999391</v>
+        <v>6999441</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122828175</v>
+        <v>122828091</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,55 +1382,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529118</v>
+        <v>529125</v>
       </c>
       <c r="R8" t="n">
-        <v>6999441</v>
+        <v>6999359</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,21 +1443,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1481,16 +1456,41 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2420,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122827848</v>
+        <v>122828537</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,55 +2432,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529118</v>
+        <v>529161</v>
       </c>
       <c r="R17" t="n">
-        <v>6999379</v>
+        <v>6999364</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2507,19 +2493,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:04</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2530,26 +2511,51 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122828537</v>
+        <v>122827848</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2558,41 +2564,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529161</v>
+        <v>529118</v>
       </c>
       <c r="R18" t="n">
-        <v>6999364</v>
+        <v>6999379</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2619,14 +2639,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,41 +2662,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -5148,10 +5148,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122827346</v>
+        <v>122827285</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5164,21 +5164,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528959</v>
+        <v>528951</v>
       </c>
       <c r="R40" t="n">
-        <v>6999360</v>
+        <v>6999355</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5250,10 +5250,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122828216</v>
+        <v>122827346</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5262,55 +5262,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529096</v>
+        <v>528959</v>
       </c>
       <c r="R41" t="n">
-        <v>6999434</v>
+        <v>6999360</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5337,19 +5323,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>16:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5364,22 +5340,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122827285</v>
+        <v>122828216</v>
       </c>
       <c r="B42" t="n">
-        <v>79848</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5388,41 +5364,55 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528951</v>
+        <v>529096</v>
       </c>
       <c r="R42" t="n">
-        <v>6999355</v>
+        <v>6999434</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5449,9 +5439,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5466,22 +5466,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122828672</v>
+        <v>122827341</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>79848</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5490,52 +5490,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529025</v>
+        <v>528959</v>
       </c>
       <c r="R43" t="n">
-        <v>6999399</v>
+        <v>6999360</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5565,19 +5551,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5592,22 +5568,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122827341</v>
+        <v>122828672</v>
       </c>
       <c r="B44" t="n">
-        <v>79848</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5616,38 +5592,52 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528959</v>
+        <v>529025</v>
       </c>
       <c r="R44" t="n">
-        <v>6999360</v>
+        <v>6999399</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5677,9 +5667,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5694,22 +5694,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122827187</v>
+        <v>122827825</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5718,50 +5718,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529024</v>
+        <v>529088</v>
       </c>
       <c r="R45" t="n">
-        <v>6999326</v>
+        <v>6999396</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5788,19 +5784,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5815,22 +5806,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122827825</v>
+        <v>122827187</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5839,46 +5830,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529088</v>
+        <v>529024</v>
       </c>
       <c r="R46" t="n">
-        <v>6999396</v>
+        <v>6999326</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5905,14 +5900,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5927,12 +5927,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122827290</v>
+        <v>122827466</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528951</v>
+        <v>529066</v>
       </c>
       <c r="R2" t="n">
-        <v>6999355</v>
+        <v>6999328</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,9 +762,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122827686</v>
+        <v>122827285</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529073</v>
+        <v>528951</v>
       </c>
       <c r="R3" t="n">
-        <v>6999336</v>
+        <v>6999355</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,24 +874,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827232</v>
+        <v>122828385</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,42 +919,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528947</v>
+        <v>529065</v>
       </c>
       <c r="R4" t="n">
-        <v>6999334</v>
+        <v>6999450</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,9 +976,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122828006</v>
+        <v>122828442</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,39 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529145</v>
+        <v>529071</v>
       </c>
       <c r="R5" t="n">
-        <v>6999399</v>
+        <v>6999422</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,14 +1093,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122828604</v>
+        <v>122827825</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,52 +1149,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529051</v>
+        <v>529088</v>
       </c>
       <c r="R6" t="n">
-        <v>6999391</v>
+        <v>6999396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,19 +1215,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:27</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,22 +1237,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122828175</v>
+        <v>122827824</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,55 +1261,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529118</v>
+        <v>529074</v>
       </c>
       <c r="R7" t="n">
-        <v>6999441</v>
+        <v>6999358</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1339,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,22 +1359,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122828091</v>
+        <v>122828175</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,41 +1383,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529125</v>
+        <v>529118</v>
       </c>
       <c r="R8" t="n">
-        <v>6999359</v>
+        <v>6999441</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,11 +1458,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1456,51 +1481,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122827958</v>
+        <v>122827848</v>
       </c>
       <c r="B9" t="n">
-        <v>77699</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,41 +1509,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529113</v>
+        <v>529118</v>
       </c>
       <c r="R9" t="n">
-        <v>6999364</v>
+        <v>6999379</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1572,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,12 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,22 +1611,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122827556</v>
+        <v>122828672</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,38 +1635,52 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528995</v>
+        <v>529025</v>
       </c>
       <c r="R10" t="n">
-        <v>6999419</v>
+        <v>6999399</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,9 +1710,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,22 +1737,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122828804</v>
+        <v>122827597</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,43 +1761,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529036</v>
+        <v>529078</v>
       </c>
       <c r="R11" t="n">
-        <v>6999404</v>
+        <v>6999325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,14 +1836,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,22 +1863,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827824</v>
+        <v>122827280</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,46 +1887,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529074</v>
+        <v>529040</v>
       </c>
       <c r="R12" t="n">
-        <v>6999358</v>
+        <v>6999362</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1908,7 +1964,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1918,12 +1974,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,22 +1994,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122828745</v>
+        <v>122827180</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,42 +2018,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529035</v>
+        <v>529019</v>
       </c>
       <c r="R13" t="n">
-        <v>6999405</v>
+        <v>6999321</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2027,9 +2079,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,19 +2111,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827390</v>
+        <v>122827642</v>
       </c>
       <c r="B14" t="n">
         <v>98365</v>
@@ -2091,12 +2158,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2105,10 +2177,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529042</v>
+        <v>529076</v>
       </c>
       <c r="R14" t="n">
-        <v>6999393</v>
+        <v>6999342</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,7 +2212,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2150,7 +2222,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,22 +2237,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827484</v>
+        <v>122827390</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2189,43 +2261,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528970</v>
+        <v>529042</v>
       </c>
       <c r="R15" t="n">
-        <v>6999399</v>
+        <v>6999393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,14 +2331,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,22 +2358,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122827147</v>
+        <v>122827178</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,55 +2382,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529019</v>
+        <v>528960</v>
       </c>
       <c r="R16" t="n">
-        <v>6999321</v>
+        <v>6999325</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2376,24 +2443,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,22 +2460,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122828537</v>
+        <v>122827341</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2436,21 +2488,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2460,13 +2512,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529161</v>
+        <v>528959</v>
       </c>
       <c r="R17" t="n">
-        <v>6999364</v>
+        <v>6999360</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2498,11 +2550,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2511,31 +2558,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2552,10 +2574,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122827848</v>
+        <v>122827504</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2564,55 +2586,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529118</v>
+        <v>529070</v>
       </c>
       <c r="R18" t="n">
-        <v>6999379</v>
+        <v>6999301</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2641,7 +2649,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2651,7 +2659,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2678,10 +2691,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122828815</v>
+        <v>122827686</v>
       </c>
       <c r="B19" t="n">
-        <v>74847</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2690,25 +2703,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2718,10 +2731,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529024</v>
+        <v>529073</v>
       </c>
       <c r="R19" t="n">
-        <v>6999406</v>
+        <v>6999336</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2753,7 +2766,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2763,12 +2776,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2795,10 +2808,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122827617</v>
+        <v>122827484</v>
       </c>
       <c r="B20" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2811,37 +2824,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528989</v>
+        <v>528970</v>
       </c>
       <c r="R20" t="n">
-        <v>6999409</v>
+        <v>6999399</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2868,24 +2886,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2900,22 +2908,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122827930</v>
+        <v>122828815</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>74847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2924,52 +2932,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529127</v>
+        <v>529024</v>
       </c>
       <c r="R21" t="n">
-        <v>6999402</v>
+        <v>6999406</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3001,7 +2995,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3011,7 +3005,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3038,10 +3037,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122827382</v>
+        <v>122827958</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>77699</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3050,50 +3049,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529080</v>
+        <v>529113</v>
       </c>
       <c r="R22" t="n">
-        <v>6999334</v>
+        <v>6999364</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3122,7 +3112,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3132,12 +3122,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3152,22 +3142,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122827466</v>
+        <v>122828091</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3176,55 +3166,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529066</v>
+        <v>529125</v>
       </c>
       <c r="R23" t="n">
-        <v>6999328</v>
+        <v>6999359</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3251,21 +3227,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3274,26 +3240,51 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122828385</v>
+        <v>122827355</v>
       </c>
       <c r="B24" t="n">
-        <v>77699</v>
+        <v>79848</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3306,21 +3297,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3330,13 +3321,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529065</v>
+        <v>528972</v>
       </c>
       <c r="R24" t="n">
-        <v>6999450</v>
+        <v>6999362</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3363,24 +3354,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3395,22 +3371,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122827275</v>
+        <v>122827147</v>
       </c>
       <c r="B25" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3419,41 +3395,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529045</v>
+        <v>529019</v>
       </c>
       <c r="R25" t="n">
-        <v>6999365</v>
+        <v>6999321</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3482,7 +3472,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3492,12 +3482,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3512,22 +3502,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122827178</v>
+        <v>122828216</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3536,41 +3526,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528960</v>
+        <v>529096</v>
       </c>
       <c r="R26" t="n">
-        <v>6999325</v>
+        <v>6999434</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3597,9 +3601,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3614,22 +3628,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122827504</v>
+        <v>122827718</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3642,21 +3656,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3666,10 +3680,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529070</v>
+        <v>529085</v>
       </c>
       <c r="R27" t="n">
-        <v>6999301</v>
+        <v>6999343</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3701,7 +3715,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3711,12 +3725,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3743,10 +3757,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122827366</v>
+        <v>122828745</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3755,38 +3769,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528972</v>
+        <v>529035</v>
       </c>
       <c r="R28" t="n">
-        <v>6999362</v>
+        <v>6999405</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3845,10 +3863,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122827543</v>
+        <v>122827410</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3861,39 +3879,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529010</v>
+        <v>528970</v>
       </c>
       <c r="R29" t="n">
-        <v>6999427</v>
+        <v>6999398</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3923,24 +3936,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3955,22 +3953,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122828442</v>
+        <v>122827382</v>
       </c>
       <c r="B30" t="n">
-        <v>77699</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3979,38 +3977,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529071</v>
+        <v>529080</v>
       </c>
       <c r="R30" t="n">
-        <v>6999422</v>
+        <v>6999334</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4042,7 +4049,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4052,12 +4059,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4084,7 +4091,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122827597</v>
+        <v>122827187</v>
       </c>
       <c r="B31" t="n">
         <v>98365</v>
@@ -4119,17 +4126,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4138,13 +4140,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529078</v>
+        <v>529024</v>
       </c>
       <c r="R31" t="n">
-        <v>6999325</v>
+        <v>6999326</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4173,7 +4175,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4183,7 +4185,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4198,19 +4200,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122827280</v>
+        <v>122828604</v>
       </c>
       <c r="B32" t="n">
         <v>98365</v>
@@ -4245,7 +4247,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4264,10 +4266,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529040</v>
+        <v>529051</v>
       </c>
       <c r="R32" t="n">
-        <v>6999362</v>
+        <v>6999391</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4299,7 +4301,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4309,12 +4311,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>3 vinterståndare i gammal granskog</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4341,10 +4338,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122828769</v>
+        <v>122827930</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4353,38 +4350,52 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529028</v>
+        <v>529127</v>
       </c>
       <c r="R33" t="n">
-        <v>6999409</v>
+        <v>6999402</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4416,7 +4427,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4426,12 +4437,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På sälgstubbe</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4458,10 +4464,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122827642</v>
+        <v>122828006</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4470,52 +4476,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529076</v>
+        <v>529145</v>
       </c>
       <c r="R34" t="n">
-        <v>6999342</v>
+        <v>6999399</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4545,19 +4542,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>16:00</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4572,22 +4564,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122827355</v>
+        <v>122827543</v>
       </c>
       <c r="B35" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4600,34 +4592,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528972</v>
+        <v>529010</v>
       </c>
       <c r="R35" t="n">
-        <v>6999362</v>
+        <v>6999427</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4657,9 +4654,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4674,22 +4686,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122827180</v>
+        <v>122827290</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4702,34 +4714,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529019</v>
+        <v>528951</v>
       </c>
       <c r="R36" t="n">
-        <v>6999321</v>
+        <v>6999355</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4759,24 +4776,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4791,22 +4793,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122828304</v>
+        <v>122827346</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4819,43 +4821,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529073</v>
+        <v>528959</v>
       </c>
       <c r="R37" t="n">
-        <v>6999451</v>
+        <v>6999360</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4885,24 +4878,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4917,22 +4895,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122827718</v>
+        <v>122827556</v>
       </c>
       <c r="B38" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4945,21 +4923,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4969,10 +4947,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529085</v>
+        <v>528995</v>
       </c>
       <c r="R38" t="n">
-        <v>6999343</v>
+        <v>6999419</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5002,24 +4980,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5034,22 +4997,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122827410</v>
+        <v>122828804</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5062,34 +5025,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528970</v>
+        <v>529036</v>
       </c>
       <c r="R39" t="n">
-        <v>6999398</v>
+        <v>6999404</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5122,6 +5090,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5148,10 +5121,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122827285</v>
+        <v>122828304</v>
       </c>
       <c r="B40" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5164,34 +5137,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528951</v>
+        <v>529073</v>
       </c>
       <c r="R40" t="n">
-        <v>6999355</v>
+        <v>6999451</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5221,9 +5203,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5238,22 +5235,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122827346</v>
+        <v>122827617</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5266,21 +5263,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5290,13 +5287,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528959</v>
+        <v>528989</v>
       </c>
       <c r="R41" t="n">
-        <v>6999360</v>
+        <v>6999409</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5323,9 +5320,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5340,22 +5352,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122828216</v>
+        <v>122827275</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>74863</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5364,55 +5376,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529096</v>
+        <v>529045</v>
       </c>
       <c r="R42" t="n">
-        <v>6999434</v>
+        <v>6999365</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5441,7 +5439,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5451,7 +5449,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5466,22 +5469,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827341</v>
+        <v>122828537</v>
       </c>
       <c r="B43" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5494,21 +5497,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5518,13 +5521,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528959</v>
+        <v>529161</v>
       </c>
       <c r="R43" t="n">
-        <v>6999360</v>
+        <v>6999364</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5556,6 +5559,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5564,6 +5572,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5580,10 +5613,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122828672</v>
+        <v>122827232</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5592,40 +5625,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5634,10 +5658,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529025</v>
+        <v>528947</v>
       </c>
       <c r="R44" t="n">
-        <v>6999399</v>
+        <v>6999334</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5667,19 +5691,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5694,22 +5708,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122827825</v>
+        <v>122828769</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5722,39 +5736,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529088</v>
+        <v>529028</v>
       </c>
       <c r="R45" t="n">
-        <v>6999396</v>
+        <v>6999409</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5784,14 +5793,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5806,22 +5825,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122827187</v>
+        <v>122827366</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5830,50 +5849,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529024</v>
+        <v>528972</v>
       </c>
       <c r="R46" t="n">
-        <v>6999326</v>
+        <v>6999362</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5900,19 +5910,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5927,22 +5927,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122827222</v>
+        <v>122827606</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5951,38 +5951,48 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>529007</v>
+        <v>529023</v>
       </c>
       <c r="R47" t="n">
-        <v>6999319</v>
+        <v>6999322</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6019,7 +6029,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Minst 12 st skott och 1 st vinterståndare.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6034,26 +6044,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6071,10 +6061,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122827606</v>
+        <v>122827222</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6083,48 +6073,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529023</v>
+        <v>529007</v>
       </c>
       <c r="R48" t="n">
-        <v>6999322</v>
+        <v>6999319</v>
       </c>
       <c r="S48" t="n">
         <v>8</v>
@@ -6161,7 +6141,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Minst 12 st skott och 1 st vinterståndare.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6176,6 +6156,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122828385</v>
+        <v>122827848</v>
       </c>
       <c r="B4" t="n">
-        <v>77699</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,41 +915,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529065</v>
+        <v>529118</v>
       </c>
       <c r="R4" t="n">
-        <v>6999450</v>
+        <v>6999379</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122828442</v>
+        <v>122828385</v>
       </c>
       <c r="B5" t="n">
         <v>77699</v>
@@ -1060,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529071</v>
+        <v>529065</v>
       </c>
       <c r="R5" t="n">
-        <v>6999422</v>
+        <v>6999450</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122827825</v>
+        <v>122828442</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,39 +1162,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529088</v>
+        <v>529071</v>
       </c>
       <c r="R6" t="n">
-        <v>6999396</v>
+        <v>6999422</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,14 +1219,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1251,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122827824</v>
+        <v>122828175</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,46 +1275,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529074</v>
+        <v>529118</v>
       </c>
       <c r="R7" t="n">
-        <v>6999358</v>
+        <v>6999441</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,12 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,22 +1377,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122828175</v>
+        <v>122827825</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,55 +1401,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529118</v>
+        <v>529088</v>
       </c>
       <c r="R8" t="n">
-        <v>6999441</v>
+        <v>6999396</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,19 +1467,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:15</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,22 +1489,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122827848</v>
+        <v>122827824</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,55 +1513,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529118</v>
+        <v>529074</v>
       </c>
       <c r="R9" t="n">
-        <v>6999379</v>
+        <v>6999358</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,6 +1592,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,12 +1611,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827642</v>
+        <v>122827390</v>
       </c>
       <c r="B14" t="n">
         <v>98365</v>
@@ -2158,17 +2158,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2177,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529076</v>
+        <v>529042</v>
       </c>
       <c r="R14" t="n">
-        <v>6999342</v>
+        <v>6999393</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2212,7 +2207,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2222,7 +2217,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2237,19 +2232,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827390</v>
+        <v>122827642</v>
       </c>
       <c r="B15" t="n">
         <v>98365</v>
@@ -2284,12 +2279,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529042</v>
+        <v>529076</v>
       </c>
       <c r="R15" t="n">
-        <v>6999393</v>
+        <v>6999342</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,12 +2358,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -4212,10 +4212,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122828604</v>
+        <v>122828006</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4224,52 +4224,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529051</v>
+        <v>529145</v>
       </c>
       <c r="R32" t="n">
-        <v>6999391</v>
+        <v>6999399</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4299,19 +4290,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:27</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4326,22 +4312,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122827930</v>
+        <v>122827543</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4350,52 +4336,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529127</v>
+        <v>529010</v>
       </c>
       <c r="R33" t="n">
-        <v>6999402</v>
+        <v>6999427</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4427,7 +4404,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4437,7 +4414,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4452,22 +4434,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122828006</v>
+        <v>122828604</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4476,43 +4458,52 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529145</v>
+        <v>529051</v>
       </c>
       <c r="R34" t="n">
-        <v>6999399</v>
+        <v>6999391</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4542,14 +4533,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4564,22 +4560,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122827543</v>
+        <v>122827930</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4588,43 +4584,52 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529010</v>
+        <v>529127</v>
       </c>
       <c r="R35" t="n">
-        <v>6999427</v>
+        <v>6999402</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4656,7 +4661,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4666,12 +4671,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4686,12 +4686,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5121,10 +5121,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122828304</v>
+        <v>122827617</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5137,46 +5137,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529073</v>
+        <v>528989</v>
       </c>
       <c r="R40" t="n">
-        <v>6999451</v>
+        <v>6999409</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5205,7 +5196,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5215,12 +5206,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5235,19 +5226,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122827617</v>
+        <v>122827275</v>
       </c>
       <c r="B41" t="n">
         <v>74863</v>
@@ -5287,13 +5278,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528989</v>
+        <v>529045</v>
       </c>
       <c r="R41" t="n">
-        <v>6999409</v>
+        <v>6999365</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5322,7 +5313,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5332,7 +5323,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5364,10 +5355,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122827275</v>
+        <v>122828537</v>
       </c>
       <c r="B42" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5380,21 +5371,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5404,13 +5395,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529045</v>
+        <v>529161</v>
       </c>
       <c r="R42" t="n">
-        <v>6999365</v>
+        <v>6999364</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5437,24 +5428,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5465,26 +5446,51 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122828537</v>
+        <v>122827232</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5497,37 +5503,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529161</v>
+        <v>528947</v>
       </c>
       <c r="R43" t="n">
-        <v>6999364</v>
+        <v>6999334</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5559,11 +5570,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5572,31 +5578,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5613,10 +5594,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122827232</v>
+        <v>122828304</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5629,27 +5610,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5658,10 +5643,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528947</v>
+        <v>529073</v>
       </c>
       <c r="R44" t="n">
-        <v>6999334</v>
+        <v>6999451</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5691,9 +5676,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5708,12 +5708,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -1749,10 +1749,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122827597</v>
+        <v>122827180</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,52 +1761,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529078</v>
+        <v>529019</v>
       </c>
       <c r="R11" t="n">
-        <v>6999325</v>
+        <v>6999321</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1838,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1848,7 +1834,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1875,7 +1866,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827280</v>
+        <v>122827597</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1910,17 +1901,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1929,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529040</v>
+        <v>529078</v>
       </c>
       <c r="R12" t="n">
-        <v>6999362</v>
+        <v>6999325</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,7 +1955,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,12 +1965,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3 vinterståndare i gammal granskog</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2006,10 +1992,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122827180</v>
+        <v>122827280</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2018,38 +2004,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529019</v>
+        <v>529040</v>
       </c>
       <c r="R13" t="n">
-        <v>6999321</v>
+        <v>6999362</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2091,12 +2091,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,7 +2123,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827390</v>
+        <v>122827642</v>
       </c>
       <c r="B14" t="n">
         <v>98365</v>
@@ -2158,12 +2158,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2172,10 +2177,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529042</v>
+        <v>529076</v>
       </c>
       <c r="R14" t="n">
-        <v>6999393</v>
+        <v>6999342</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,7 +2212,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2217,7 +2222,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2232,19 +2237,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827642</v>
+        <v>122827390</v>
       </c>
       <c r="B15" t="n">
         <v>98365</v>
@@ -2279,17 +2284,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529076</v>
+        <v>529042</v>
       </c>
       <c r="R15" t="n">
-        <v>6999342</v>
+        <v>6999393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,12 +2358,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122827410</v>
+        <v>122827382</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3875,38 +3875,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528970</v>
+        <v>529080</v>
       </c>
       <c r="R29" t="n">
-        <v>6999398</v>
+        <v>6999334</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3936,9 +3945,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3953,19 +3977,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122827382</v>
+        <v>122827187</v>
       </c>
       <c r="B30" t="n">
         <v>98365</v>
@@ -4000,7 +4024,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4014,13 +4038,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529080</v>
+        <v>529024</v>
       </c>
       <c r="R30" t="n">
-        <v>6999334</v>
+        <v>6999326</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4049,7 +4073,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4059,12 +4083,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4079,22 +4098,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122827187</v>
+        <v>122827410</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4103,50 +4122,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529024</v>
+        <v>528970</v>
       </c>
       <c r="R31" t="n">
-        <v>6999326</v>
+        <v>6999398</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4173,19 +4183,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4200,12 +4200,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122827466</v>
+        <v>122827275</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529066</v>
+        <v>529045</v>
       </c>
       <c r="R2" t="n">
-        <v>6999328</v>
+        <v>6999365</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122827285</v>
+        <v>122827718</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528951</v>
+        <v>529085</v>
       </c>
       <c r="R3" t="n">
-        <v>6999355</v>
+        <v>6999343</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,9 +865,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827848</v>
+        <v>122828091</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,55 +921,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529118</v>
+        <v>529125</v>
       </c>
       <c r="R4" t="n">
-        <v>6999379</v>
+        <v>6999359</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,21 +982,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1013,26 +995,51 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122828385</v>
+        <v>122827366</v>
       </c>
       <c r="B5" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,21 +1052,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,13 +1076,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529065</v>
+        <v>528972</v>
       </c>
       <c r="R5" t="n">
-        <v>6999450</v>
+        <v>6999362</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,24 +1109,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122828442</v>
+        <v>122828804</v>
       </c>
       <c r="B6" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,34 +1154,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529071</v>
+        <v>529036</v>
       </c>
       <c r="R6" t="n">
-        <v>6999422</v>
+        <v>6999404</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,24 +1216,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,19 +1238,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122828175</v>
+        <v>122827280</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1298,7 +1285,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1308,7 +1295,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1317,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529118</v>
+        <v>529040</v>
       </c>
       <c r="R7" t="n">
-        <v>6999441</v>
+        <v>6999362</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122827825</v>
+        <v>122827355</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,39 +1397,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529088</v>
+        <v>528972</v>
       </c>
       <c r="R8" t="n">
-        <v>6999396</v>
+        <v>6999362</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,11 +1457,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122827824</v>
+        <v>122828442</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,42 +1499,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529074</v>
+        <v>529071</v>
       </c>
       <c r="R9" t="n">
-        <v>6999358</v>
+        <v>6999422</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1591,12 +1568,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,19 +1588,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122828672</v>
+        <v>122828745</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1658,17 +1635,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1677,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529025</v>
+        <v>529035</v>
       </c>
       <c r="R10" t="n">
-        <v>6999399</v>
+        <v>6999405</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,19 +1677,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,22 +1694,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122827180</v>
+        <v>122827187</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,41 +1718,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529019</v>
+        <v>529024</v>
       </c>
       <c r="R11" t="n">
-        <v>6999321</v>
+        <v>6999326</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1835,11 +1801,6 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,22 +1815,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827597</v>
+        <v>122827617</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>74863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,55 +1839,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529078</v>
+        <v>528989</v>
       </c>
       <c r="R12" t="n">
-        <v>6999325</v>
+        <v>6999409</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1966,6 +1913,11 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,19 +1932,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122827280</v>
+        <v>122827382</v>
       </c>
       <c r="B13" t="n">
         <v>98365</v>
@@ -2027,7 +1979,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2035,21 +1987,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529040</v>
+        <v>529080</v>
       </c>
       <c r="R13" t="n">
-        <v>6999362</v>
+        <v>6999334</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2081,7 +2028,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2091,12 +2038,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>3 vinterståndare i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,7 +2070,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827642</v>
+        <v>122827930</v>
       </c>
       <c r="B14" t="n">
         <v>98365</v>
@@ -2177,10 +2124,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529076</v>
+        <v>529127</v>
       </c>
       <c r="R14" t="n">
-        <v>6999342</v>
+        <v>6999402</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2212,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2222,7 +2169,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2249,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827390</v>
+        <v>122827341</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>79848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2261,47 +2208,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529042</v>
+        <v>528959</v>
       </c>
       <c r="R15" t="n">
-        <v>6999393</v>
+        <v>6999360</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2331,19 +2269,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,12 +2286,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2472,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122827341</v>
+        <v>122827848</v>
       </c>
       <c r="B17" t="n">
-        <v>79848</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2484,41 +2412,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528959</v>
+        <v>529118</v>
       </c>
       <c r="R17" t="n">
-        <v>6999360</v>
+        <v>6999379</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2545,9 +2487,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,22 +2514,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122827504</v>
+        <v>122827285</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2590,21 +2542,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2614,10 +2566,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529070</v>
+        <v>528951</v>
       </c>
       <c r="R18" t="n">
-        <v>6999301</v>
+        <v>6999355</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2647,24 +2599,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2679,22 +2616,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122827686</v>
+        <v>122827825</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2707,34 +2644,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529073</v>
+        <v>529088</v>
       </c>
       <c r="R19" t="n">
-        <v>6999336</v>
+        <v>6999396</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2764,24 +2706,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Längsta bål 60 cm</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2796,22 +2728,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122827484</v>
+        <v>122827686</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2824,39 +2756,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528970</v>
+        <v>529073</v>
       </c>
       <c r="R20" t="n">
-        <v>6999399</v>
+        <v>6999336</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2886,14 +2813,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2908,22 +2845,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122828815</v>
+        <v>122828006</v>
       </c>
       <c r="B21" t="n">
-        <v>74847</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2932,38 +2869,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529024</v>
+        <v>529145</v>
       </c>
       <c r="R21" t="n">
-        <v>6999406</v>
+        <v>6999399</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2993,24 +2935,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3025,12 +2957,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3154,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122828091</v>
+        <v>122827466</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3166,41 +3098,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529125</v>
+        <v>529066</v>
       </c>
       <c r="R23" t="n">
-        <v>6999359</v>
+        <v>6999328</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3227,11 +3173,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3240,51 +3196,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122827355</v>
+        <v>122827232</v>
       </c>
       <c r="B24" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3297,34 +3228,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528972</v>
+        <v>528947</v>
       </c>
       <c r="R24" t="n">
-        <v>6999362</v>
+        <v>6999334</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3383,10 +3319,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122827147</v>
+        <v>122827504</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3395,55 +3331,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529019</v>
+        <v>529070</v>
       </c>
       <c r="R25" t="n">
-        <v>6999321</v>
+        <v>6999301</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3472,7 +3394,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3482,12 +3404,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1 vinterståndare på marken i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122828216</v>
+        <v>122828769</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3526,55 +3448,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529096</v>
+        <v>529028</v>
       </c>
       <c r="R26" t="n">
-        <v>6999434</v>
+        <v>6999409</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3603,7 +3511,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3613,7 +3521,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3640,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122827718</v>
+        <v>122828815</v>
       </c>
       <c r="B27" t="n">
-        <v>74863</v>
+        <v>74847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3652,25 +3565,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3680,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529085</v>
+        <v>529024</v>
       </c>
       <c r="R27" t="n">
-        <v>6999343</v>
+        <v>6999406</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3715,7 +3628,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3725,12 +3638,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal i gammal granskog</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3757,10 +3670,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122828745</v>
+        <v>122827290</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3769,30 +3682,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3801,10 +3715,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529035</v>
+        <v>528951</v>
       </c>
       <c r="R28" t="n">
-        <v>6999405</v>
+        <v>6999355</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3863,7 +3777,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122827382</v>
+        <v>122827147</v>
       </c>
       <c r="B29" t="n">
         <v>98365</v>
@@ -3898,27 +3812,32 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529080</v>
+        <v>529019</v>
       </c>
       <c r="R29" t="n">
-        <v>6999334</v>
+        <v>6999321</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3947,7 +3866,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3957,12 +3876,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3989,10 +3908,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122827187</v>
+        <v>122828537</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4001,50 +3920,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529024</v>
+        <v>529161</v>
       </c>
       <c r="R30" t="n">
-        <v>6999326</v>
+        <v>6999364</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4071,19 +3981,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4094,26 +3999,51 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122827410</v>
+        <v>122827180</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4126,34 +4056,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528970</v>
+        <v>529019</v>
       </c>
       <c r="R31" t="n">
-        <v>6999398</v>
+        <v>6999321</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4183,9 +4113,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4200,22 +4145,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122828006</v>
+        <v>122828672</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4224,40 +4169,49 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529145</v>
+        <v>529025</v>
       </c>
       <c r="R32" t="n">
         <v>6999399</v>
@@ -4290,14 +4244,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4312,22 +4271,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122827543</v>
+        <v>122827642</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4336,43 +4295,52 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529010</v>
+        <v>529076</v>
       </c>
       <c r="R33" t="n">
-        <v>6999427</v>
+        <v>6999342</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4404,7 +4372,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4414,12 +4382,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4434,22 +4397,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122828604</v>
+        <v>122827824</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4458,55 +4421,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529051</v>
+        <v>529074</v>
       </c>
       <c r="R34" t="n">
-        <v>6999391</v>
+        <v>6999358</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4535,7 +4489,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4545,7 +4499,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4560,22 +4519,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122827930</v>
+        <v>122827346</v>
       </c>
       <c r="B35" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4584,52 +4543,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529127</v>
+        <v>528959</v>
       </c>
       <c r="R35" t="n">
-        <v>6999402</v>
+        <v>6999360</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4659,19 +4604,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4686,22 +4621,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122827290</v>
+        <v>122827597</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4710,31 +4645,40 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4743,10 +4687,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528951</v>
+        <v>529078</v>
       </c>
       <c r="R36" t="n">
-        <v>6999355</v>
+        <v>6999325</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4776,9 +4720,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4793,22 +4747,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122827346</v>
+        <v>122827390</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4817,38 +4771,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528959</v>
+        <v>529042</v>
       </c>
       <c r="R37" t="n">
-        <v>6999360</v>
+        <v>6999393</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4878,9 +4841,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4895,19 +4868,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122827556</v>
+        <v>122827410</v>
       </c>
       <c r="B38" t="n">
         <v>79847</v>
@@ -4947,10 +4920,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528995</v>
+        <v>528970</v>
       </c>
       <c r="R38" t="n">
-        <v>6999419</v>
+        <v>6999398</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5009,7 +4982,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122828804</v>
+        <v>122827543</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -5054,10 +5027,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529036</v>
+        <v>529010</v>
       </c>
       <c r="R39" t="n">
-        <v>6999404</v>
+        <v>6999427</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5087,9 +5060,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5109,22 +5092,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122827617</v>
+        <v>122828604</v>
       </c>
       <c r="B40" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5133,41 +5116,55 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528989</v>
+        <v>529051</v>
       </c>
       <c r="R40" t="n">
-        <v>6999409</v>
+        <v>6999391</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5196,7 +5193,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5206,12 +5203,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5226,22 +5218,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122827275</v>
+        <v>122828304</v>
       </c>
       <c r="B41" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5254,34 +5246,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529045</v>
+        <v>529073</v>
       </c>
       <c r="R41" t="n">
-        <v>6999365</v>
+        <v>6999451</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5313,7 +5314,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5323,12 +5324,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5343,22 +5344,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122828537</v>
+        <v>122827556</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5371,21 +5372,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5395,13 +5396,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529161</v>
+        <v>528995</v>
       </c>
       <c r="R42" t="n">
-        <v>6999364</v>
+        <v>6999419</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5433,11 +5434,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5446,31 +5442,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5487,10 +5458,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827232</v>
+        <v>122827484</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5503,39 +5474,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528947</v>
+        <v>528970</v>
       </c>
       <c r="R43" t="n">
-        <v>6999334</v>
+        <v>6999399</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5568,6 +5539,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5594,10 +5570,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122828304</v>
+        <v>122828216</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5606,35 +5582,40 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5643,13 +5624,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529073</v>
+        <v>529096</v>
       </c>
       <c r="R44" t="n">
-        <v>6999451</v>
+        <v>6999434</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5678,7 +5659,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5688,12 +5669,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5720,10 +5696,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122828769</v>
+        <v>122828175</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5732,41 +5708,55 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529028</v>
+        <v>529118</v>
       </c>
       <c r="R45" t="n">
-        <v>6999409</v>
+        <v>6999441</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5795,7 +5785,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5805,12 +5795,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På sälgstubbe</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5837,10 +5822,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122827366</v>
+        <v>122828385</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5853,21 +5838,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5877,13 +5862,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528972</v>
+        <v>529065</v>
       </c>
       <c r="R46" t="n">
-        <v>6999362</v>
+        <v>6999450</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5910,9 +5895,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5927,22 +5927,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122827606</v>
+        <v>122827222</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5951,48 +5951,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>529023</v>
+        <v>529007</v>
       </c>
       <c r="R47" t="n">
-        <v>6999322</v>
+        <v>6999319</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6029,7 +6019,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 12 st skott och 1 st vinterståndare.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6044,6 +6034,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6061,10 +6071,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122827222</v>
+        <v>122827606</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6073,38 +6083,48 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529007</v>
+        <v>529023</v>
       </c>
       <c r="R48" t="n">
-        <v>6999319</v>
+        <v>6999322</v>
       </c>
       <c r="S48" t="n">
         <v>8</v>
@@ -6141,7 +6161,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Minst 12 st skott och 1 st vinterståndare.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6156,26 +6176,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122827275</v>
+        <v>122828304</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529045</v>
+        <v>529073</v>
       </c>
       <c r="R2" t="n">
-        <v>6999365</v>
+        <v>6999451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122827718</v>
+        <v>122827504</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529085</v>
+        <v>529070</v>
       </c>
       <c r="R3" t="n">
-        <v>6999343</v>
+        <v>6999301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122828091</v>
+        <v>122827341</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529125</v>
+        <v>528959</v>
       </c>
       <c r="R4" t="n">
-        <v>6999359</v>
+        <v>6999360</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,31 +1004,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1036,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122827366</v>
+        <v>122828091</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528972</v>
+        <v>529125</v>
       </c>
       <c r="R5" t="n">
-        <v>6999362</v>
+        <v>6999359</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,6 +1106,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1138,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122828804</v>
+        <v>122827382</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,43 +1159,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529036</v>
+        <v>529080</v>
       </c>
       <c r="R6" t="n">
-        <v>6999404</v>
+        <v>6999334</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,14 +1229,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1261,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122827280</v>
+        <v>122827556</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,52 +1285,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529040</v>
+        <v>528995</v>
       </c>
       <c r="R7" t="n">
-        <v>6999362</v>
+        <v>6999419</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,24 +1346,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,22 +1363,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122827355</v>
+        <v>122827178</v>
       </c>
       <c r="B8" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,21 +1391,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528972</v>
+        <v>528960</v>
       </c>
       <c r="R8" t="n">
-        <v>6999362</v>
+        <v>6999325</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1483,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122828442</v>
+        <v>122828537</v>
       </c>
       <c r="B9" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,21 +1493,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,13 +1517,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529071</v>
+        <v>529161</v>
       </c>
       <c r="R9" t="n">
-        <v>6999422</v>
+        <v>6999364</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1556,24 +1550,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,26 +1568,51 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122828745</v>
+        <v>122828804</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,42 +1621,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529035</v>
+        <v>529036</v>
       </c>
       <c r="R10" t="n">
-        <v>6999405</v>
+        <v>6999404</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,6 +1690,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122827187</v>
+        <v>122827825</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,50 +1733,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529024</v>
+        <v>529088</v>
       </c>
       <c r="R11" t="n">
-        <v>6999326</v>
+        <v>6999396</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,19 +1799,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,22 +1821,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827617</v>
+        <v>122828442</v>
       </c>
       <c r="B12" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,21 +1849,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,13 +1873,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528989</v>
+        <v>529071</v>
       </c>
       <c r="R12" t="n">
-        <v>6999409</v>
+        <v>6999422</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1902,7 +1908,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,12 +1918,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,22 +1938,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122827382</v>
+        <v>122827718</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>74863</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,47 +1962,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529080</v>
+        <v>529085</v>
       </c>
       <c r="R13" t="n">
-        <v>6999334</v>
+        <v>6999343</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2038,12 +2035,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2070,10 +2067,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827930</v>
+        <v>122827290</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2082,40 +2079,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2124,10 +2112,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529127</v>
+        <v>528951</v>
       </c>
       <c r="R14" t="n">
-        <v>6999402</v>
+        <v>6999355</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2157,19 +2145,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,22 +2162,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827341</v>
+        <v>122827180</v>
       </c>
       <c r="B15" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,34 +2190,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528959</v>
+        <v>529019</v>
       </c>
       <c r="R15" t="n">
-        <v>6999360</v>
+        <v>6999321</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,9 +2247,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,22 +2279,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122827178</v>
+        <v>122827147</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,41 +2303,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528960</v>
+        <v>529019</v>
       </c>
       <c r="R16" t="n">
-        <v>6999325</v>
+        <v>6999321</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2371,9 +2378,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,19 +2410,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122827848</v>
+        <v>122827597</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2440,12 +2462,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2454,13 +2476,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529118</v>
+        <v>529078</v>
       </c>
       <c r="R17" t="n">
-        <v>6999379</v>
+        <v>6999325</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,7 +2511,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2521,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2548,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122827285</v>
+        <v>122827275</v>
       </c>
       <c r="B18" t="n">
-        <v>79848</v>
+        <v>74863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,21 +2564,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2566,10 +2588,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528951</v>
+        <v>529045</v>
       </c>
       <c r="R18" t="n">
-        <v>6999355</v>
+        <v>6999365</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2599,9 +2621,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,22 +2653,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122827825</v>
+        <v>122827285</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,39 +2681,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529088</v>
+        <v>528951</v>
       </c>
       <c r="R19" t="n">
-        <v>6999396</v>
+        <v>6999355</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,11 +2741,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,10 +2767,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122827686</v>
+        <v>122828745</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2752,38 +2779,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529073</v>
+        <v>529035</v>
       </c>
       <c r="R20" t="n">
-        <v>6999336</v>
+        <v>6999405</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2813,24 +2844,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,22 +2861,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122828006</v>
+        <v>122827617</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2873,42 +2889,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529145</v>
+        <v>528989</v>
       </c>
       <c r="R21" t="n">
-        <v>6999399</v>
+        <v>6999409</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2935,14 +2946,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,22 +2978,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122827958</v>
+        <v>122827930</v>
       </c>
       <c r="B22" t="n">
-        <v>77699</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2981,41 +3002,55 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529113</v>
+        <v>529127</v>
       </c>
       <c r="R22" t="n">
-        <v>6999364</v>
+        <v>6999402</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3044,7 +3079,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3054,12 +3089,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,12 +3104,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3212,10 +3242,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122827232</v>
+        <v>122827543</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3228,39 +3258,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528947</v>
+        <v>529010</v>
       </c>
       <c r="R24" t="n">
-        <v>6999334</v>
+        <v>6999427</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3290,9 +3320,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3307,22 +3352,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122827504</v>
+        <v>122827642</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3331,38 +3376,52 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529070</v>
+        <v>529076</v>
       </c>
       <c r="R25" t="n">
-        <v>6999301</v>
+        <v>6999342</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3453,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3404,12 +3463,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3436,7 +3490,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122828769</v>
+        <v>122827366</v>
       </c>
       <c r="B26" t="n">
         <v>79847</v>
@@ -3476,10 +3530,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529028</v>
+        <v>528972</v>
       </c>
       <c r="R26" t="n">
-        <v>6999409</v>
+        <v>6999362</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3509,24 +3563,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3541,22 +3580,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122828815</v>
+        <v>122828385</v>
       </c>
       <c r="B27" t="n">
-        <v>74847</v>
+        <v>77699</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3565,25 +3604,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3593,13 +3632,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529024</v>
+        <v>529065</v>
       </c>
       <c r="R27" t="n">
-        <v>6999406</v>
+        <v>6999450</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3628,7 +3667,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,12 +3677,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3670,7 +3709,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122827290</v>
+        <v>122828769</v>
       </c>
       <c r="B28" t="n">
         <v>79847</v>
@@ -3704,21 +3743,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528951</v>
+        <v>529028</v>
       </c>
       <c r="R28" t="n">
-        <v>6999355</v>
+        <v>6999409</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3748,9 +3782,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3765,19 +3814,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122827147</v>
+        <v>122827280</v>
       </c>
       <c r="B29" t="n">
         <v>98365</v>
@@ -3812,12 +3861,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3827,17 +3876,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529019</v>
+        <v>529040</v>
       </c>
       <c r="R29" t="n">
-        <v>6999321</v>
+        <v>6999362</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3866,7 +3915,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3876,12 +3925,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1 vinterståndare på marken i gammal granskog</t>
+          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3908,10 +3957,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122828537</v>
+        <v>122828216</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3920,41 +3969,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529161</v>
+        <v>529096</v>
       </c>
       <c r="R30" t="n">
-        <v>6999364</v>
+        <v>6999434</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3981,14 +4044,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3999,51 +4067,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122827180</v>
+        <v>122827232</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4056,34 +4099,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529019</v>
+        <v>528947</v>
       </c>
       <c r="R31" t="n">
-        <v>6999321</v>
+        <v>6999334</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4113,24 +4161,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4145,22 +4178,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122828672</v>
+        <v>122827410</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4169,52 +4202,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529025</v>
+        <v>528970</v>
       </c>
       <c r="R32" t="n">
-        <v>6999399</v>
+        <v>6999398</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4244,19 +4263,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4271,22 +4280,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122827642</v>
+        <v>122827484</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4295,52 +4304,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529076</v>
+        <v>528970</v>
       </c>
       <c r="R33" t="n">
-        <v>6999342</v>
+        <v>6999399</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4370,19 +4370,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:00</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4397,19 +4392,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122827824</v>
+        <v>122828006</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4445,7 +4440,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4454,13 +4449,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529074</v>
+        <v>529145</v>
       </c>
       <c r="R34" t="n">
-        <v>6999358</v>
+        <v>6999399</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4487,24 +4482,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4519,22 +4504,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122827346</v>
+        <v>122828175</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4543,41 +4528,55 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528959</v>
+        <v>529118</v>
       </c>
       <c r="R35" t="n">
-        <v>6999360</v>
+        <v>6999441</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4604,9 +4603,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4621,22 +4630,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122827597</v>
+        <v>122828815</v>
       </c>
       <c r="B36" t="n">
-        <v>98365</v>
+        <v>74847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4645,52 +4654,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529078</v>
+        <v>529024</v>
       </c>
       <c r="R36" t="n">
-        <v>6999325</v>
+        <v>6999406</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4722,7 +4717,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4732,7 +4727,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4759,7 +4759,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122827390</v>
+        <v>122828604</v>
       </c>
       <c r="B37" t="n">
         <v>98365</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4802,16 +4802,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529042</v>
+        <v>529051</v>
       </c>
       <c r="R37" t="n">
-        <v>6999393</v>
+        <v>6999391</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4843,7 +4848,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4853,7 +4858,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4868,22 +4873,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122827410</v>
+        <v>122827390</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4892,38 +4897,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528970</v>
+        <v>529042</v>
       </c>
       <c r="R38" t="n">
-        <v>6999398</v>
+        <v>6999393</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4953,9 +4967,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4970,22 +4994,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122827543</v>
+        <v>122827355</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4998,39 +5022,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529010</v>
+        <v>528972</v>
       </c>
       <c r="R39" t="n">
-        <v>6999427</v>
+        <v>6999362</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5060,24 +5079,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5092,22 +5096,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122828604</v>
+        <v>122827346</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5116,52 +5120,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529051</v>
+        <v>528959</v>
       </c>
       <c r="R40" t="n">
-        <v>6999391</v>
+        <v>6999360</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5191,19 +5181,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>16:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5218,22 +5198,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122828304</v>
+        <v>122827824</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5246,46 +5226,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529073</v>
+        <v>529074</v>
       </c>
       <c r="R41" t="n">
-        <v>6999451</v>
+        <v>6999358</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5314,7 +5290,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5324,12 +5300,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5344,22 +5320,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122827556</v>
+        <v>122828672</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5368,38 +5344,52 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528995</v>
+        <v>529025</v>
       </c>
       <c r="R42" t="n">
-        <v>6999419</v>
+        <v>6999399</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5429,9 +5419,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5446,22 +5446,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827484</v>
+        <v>122827848</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5470,46 +5470,55 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528970</v>
+        <v>529118</v>
       </c>
       <c r="R43" t="n">
-        <v>6999399</v>
+        <v>6999379</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5536,14 +5545,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5558,22 +5572,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122828216</v>
+        <v>122827686</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5582,55 +5596,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529096</v>
+        <v>529073</v>
       </c>
       <c r="R44" t="n">
-        <v>6999434</v>
+        <v>6999336</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5669,7 +5669,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5696,10 +5701,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122828175</v>
+        <v>122827958</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>77699</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5708,55 +5713,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529118</v>
+        <v>529113</v>
       </c>
       <c r="R45" t="n">
-        <v>6999441</v>
+        <v>6999364</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5785,7 +5776,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5795,7 +5786,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5810,22 +5806,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122828385</v>
+        <v>122827187</v>
       </c>
       <c r="B46" t="n">
-        <v>77699</v>
+        <v>98365</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5834,41 +5830,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529065</v>
+        <v>529024</v>
       </c>
       <c r="R46" t="n">
-        <v>6999450</v>
+        <v>6999326</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5897,7 +5902,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5907,12 +5912,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5927,12 +5927,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122827556</v>
+        <v>122828442</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528995</v>
+        <v>529071</v>
       </c>
       <c r="R7" t="n">
-        <v>6999419</v>
+        <v>6999422</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,9 +1346,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,19 +1378,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122827178</v>
+        <v>122827556</v>
       </c>
       <c r="B8" t="n">
         <v>79847</v>
@@ -1415,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528960</v>
+        <v>528995</v>
       </c>
       <c r="R8" t="n">
-        <v>6999325</v>
+        <v>6999419</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122828537</v>
+        <v>122827178</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,21 +1508,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,13 +1532,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529161</v>
+        <v>528960</v>
       </c>
       <c r="R9" t="n">
-        <v>6999364</v>
+        <v>6999325</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1555,11 +1570,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1568,31 +1578,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1609,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122828804</v>
+        <v>122828537</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,42 +1610,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529036</v>
+        <v>529161</v>
       </c>
       <c r="R10" t="n">
-        <v>6999404</v>
+        <v>6999364</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1694,7 +1674,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,6 +1685,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1721,7 +1726,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122827825</v>
+        <v>122828804</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1766,10 +1771,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529088</v>
+        <v>529036</v>
       </c>
       <c r="R11" t="n">
-        <v>6999396</v>
+        <v>6999404</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,10 +1838,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122828442</v>
+        <v>122827825</v>
       </c>
       <c r="B12" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,34 +1854,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529071</v>
+        <v>529088</v>
       </c>
       <c r="R12" t="n">
-        <v>6999422</v>
+        <v>6999396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1906,24 +1916,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,12 +1938,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122828216</v>
+        <v>122827484</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3969,55 +3969,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529096</v>
+        <v>528970</v>
       </c>
       <c r="R30" t="n">
-        <v>6999434</v>
+        <v>6999399</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4044,19 +4035,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:16</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4071,12 +4057,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4292,10 +4278,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122827484</v>
+        <v>122828216</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4304,46 +4290,55 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528970</v>
+        <v>529096</v>
       </c>
       <c r="R33" t="n">
-        <v>6999399</v>
+        <v>6999434</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4370,14 +4365,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4392,12 +4392,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122828442</v>
+        <v>122827556</v>
       </c>
       <c r="B7" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529071</v>
+        <v>528995</v>
       </c>
       <c r="R7" t="n">
-        <v>6999422</v>
+        <v>6999419</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,24 +1346,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,19 +1363,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122827556</v>
+        <v>122827178</v>
       </c>
       <c r="B8" t="n">
         <v>79847</v>
@@ -1430,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528995</v>
+        <v>528960</v>
       </c>
       <c r="R8" t="n">
-        <v>6999419</v>
+        <v>6999325</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122827178</v>
+        <v>122828537</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,21 +1493,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1532,13 +1517,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528960</v>
+        <v>529161</v>
       </c>
       <c r="R9" t="n">
-        <v>6999325</v>
+        <v>6999364</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,6 +1555,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1578,6 +1568,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1594,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122828537</v>
+        <v>122828804</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,37 +1625,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529161</v>
+        <v>529036</v>
       </c>
       <c r="R10" t="n">
-        <v>6999364</v>
+        <v>6999404</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1674,7 +1694,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,31 +1705,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1726,7 +1721,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122828804</v>
+        <v>122827825</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1771,10 +1766,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529036</v>
+        <v>529088</v>
       </c>
       <c r="R11" t="n">
-        <v>6999404</v>
+        <v>6999396</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1838,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827825</v>
+        <v>122828442</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,39 +1849,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529088</v>
+        <v>529071</v>
       </c>
       <c r="R12" t="n">
-        <v>6999396</v>
+        <v>6999422</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,14 +1906,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,12 +1938,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122828304</v>
+        <v>122828006</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529073</v>
+        <v>529145</v>
       </c>
       <c r="R2" t="n">
-        <v>6999451</v>
+        <v>6999399</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +753,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122827504</v>
+        <v>122827484</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529070</v>
+        <v>528970</v>
       </c>
       <c r="R3" t="n">
-        <v>6999301</v>
+        <v>6999399</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,24 +865,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827341</v>
+        <v>122827410</v>
       </c>
       <c r="B4" t="n">
-        <v>79848</v>
+        <v>79850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528959</v>
+        <v>528970</v>
       </c>
       <c r="R4" t="n">
-        <v>6999360</v>
+        <v>6999398</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122828091</v>
+        <v>122828769</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,13 +1041,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529125</v>
+        <v>529028</v>
       </c>
       <c r="R5" t="n">
-        <v>6999359</v>
+        <v>6999409</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,11 +1074,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På sälgstubbe</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1106,41 +1102,16 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1150,7 +1121,7 @@
         <v>122827382</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1266,17 +1237,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122827556</v>
+        <v>122827178</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1313,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528995</v>
+        <v>528960</v>
       </c>
       <c r="R7" t="n">
-        <v>6999419</v>
+        <v>6999325</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122827178</v>
+        <v>122827848</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,41 +1358,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528960</v>
+        <v>529118</v>
       </c>
       <c r="R8" t="n">
-        <v>6999325</v>
+        <v>6999379</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1448,9 +1433,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,22 +1460,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122828537</v>
+        <v>122827280</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,41 +1484,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529161</v>
+        <v>529040</v>
       </c>
       <c r="R9" t="n">
-        <v>6999364</v>
+        <v>6999362</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,14 +1559,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,51 +1587,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122828804</v>
+        <v>122827346</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,39 +1619,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529036</v>
+        <v>528959</v>
       </c>
       <c r="R10" t="n">
-        <v>6999404</v>
+        <v>6999360</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,11 +1679,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122827825</v>
+        <v>122827366</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,39 +1721,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529088</v>
+        <v>528972</v>
       </c>
       <c r="R11" t="n">
-        <v>6999396</v>
+        <v>6999362</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,11 +1781,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,10 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122828442</v>
+        <v>122827390</v>
       </c>
       <c r="B12" t="n">
-        <v>77699</v>
+        <v>98368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,38 +1819,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529071</v>
+        <v>529042</v>
       </c>
       <c r="R12" t="n">
-        <v>6999422</v>
+        <v>6999393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,7 +1891,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1918,12 +1901,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,22 +1916,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122827718</v>
+        <v>122828175</v>
       </c>
       <c r="B13" t="n">
-        <v>74863</v>
+        <v>98368</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,41 +1940,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529085</v>
+        <v>529118</v>
       </c>
       <c r="R13" t="n">
-        <v>6999343</v>
+        <v>6999441</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2025,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,12 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal i gammal granskog</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827290</v>
+        <v>122827187</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>98368</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,31 +2066,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2112,13 +2103,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528951</v>
+        <v>529024</v>
       </c>
       <c r="R14" t="n">
-        <v>6999355</v>
+        <v>6999326</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2145,9 +2136,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,22 +2163,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827180</v>
+        <v>122827686</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2210,14 +2211,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529019</v>
+        <v>529073</v>
       </c>
       <c r="R15" t="n">
-        <v>6999321</v>
+        <v>6999336</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,12 +2260,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122827147</v>
+        <v>122828442</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>77702</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,55 +2304,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529019</v>
+        <v>529071</v>
       </c>
       <c r="R16" t="n">
-        <v>6999321</v>
+        <v>6999422</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2380,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2390,12 +2377,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>1 vinterståndare på marken i gammal granskog</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122827597</v>
+        <v>122827825</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2434,52 +2421,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529078</v>
+        <v>529088</v>
       </c>
       <c r="R17" t="n">
-        <v>6999325</v>
+        <v>6999396</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2509,19 +2487,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:59</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2536,22 +2509,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122827275</v>
+        <v>122828304</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>78769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2564,34 +2537,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529045</v>
+        <v>529073</v>
       </c>
       <c r="R18" t="n">
-        <v>6999365</v>
+        <v>6999451</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2623,7 +2605,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2633,12 +2615,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,22 +2635,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122827285</v>
+        <v>122827180</v>
       </c>
       <c r="B19" t="n">
-        <v>79848</v>
+        <v>78769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2681,34 +2663,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528951</v>
+        <v>529019</v>
       </c>
       <c r="R19" t="n">
-        <v>6999355</v>
+        <v>6999321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2738,9 +2720,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,22 +2752,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122828745</v>
+        <v>122827275</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>74866</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2779,42 +2776,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529035</v>
+        <v>529045</v>
       </c>
       <c r="R20" t="n">
-        <v>6999405</v>
+        <v>6999365</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2844,9 +2837,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,22 +2869,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122827617</v>
+        <v>122828672</v>
       </c>
       <c r="B21" t="n">
-        <v>74863</v>
+        <v>98368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,41 +2893,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528989</v>
+        <v>529025</v>
       </c>
       <c r="R21" t="n">
-        <v>6999409</v>
+        <v>6999399</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2948,7 +2970,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2958,12 +2980,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,22 +2995,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122827930</v>
+        <v>122827642</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,10 +3061,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529127</v>
+        <v>529076</v>
       </c>
       <c r="R22" t="n">
-        <v>6999402</v>
+        <v>6999342</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3079,7 +3096,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3089,7 +3106,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,10 +3133,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122827466</v>
+        <v>122827504</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3128,52 +3145,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529066</v>
+        <v>529070</v>
       </c>
       <c r="R23" t="n">
-        <v>6999328</v>
+        <v>6999301</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3205,7 +3208,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3215,7 +3218,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3235,17 +3243,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122827543</v>
+        <v>122827285</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>79851</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3258,39 +3266,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529010</v>
+        <v>528951</v>
       </c>
       <c r="R24" t="n">
-        <v>6999427</v>
+        <v>6999355</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3320,24 +3323,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3352,22 +3340,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122827642</v>
+        <v>122828804</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3376,52 +3364,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529076</v>
+        <v>529036</v>
       </c>
       <c r="R25" t="n">
-        <v>6999342</v>
+        <v>6999404</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3451,19 +3430,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:00</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3478,22 +3452,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122827366</v>
+        <v>122827355</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>79851</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3506,21 +3480,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3592,10 +3566,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122828385</v>
+        <v>122827617</v>
       </c>
       <c r="B27" t="n">
-        <v>77699</v>
+        <v>74866</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3608,21 +3582,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3632,13 +3606,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529065</v>
+        <v>528989</v>
       </c>
       <c r="R27" t="n">
-        <v>6999450</v>
+        <v>6999409</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3667,7 +3641,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3677,12 +3651,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3697,22 +3671,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122828769</v>
+        <v>122827718</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>74866</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3725,21 +3699,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3749,10 +3723,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529028</v>
+        <v>529085</v>
       </c>
       <c r="R28" t="n">
-        <v>6999409</v>
+        <v>6999343</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3784,7 +3758,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3794,12 +3768,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,10 +3800,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122827280</v>
+        <v>122828091</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3838,55 +3812,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529040</v>
+        <v>529125</v>
       </c>
       <c r="R29" t="n">
-        <v>6999362</v>
+        <v>6999359</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3913,26 +3873,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>3 vinterståndare i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3941,26 +3886,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122827484</v>
+        <v>122828815</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>74850</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3969,43 +3939,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528970</v>
+        <v>529024</v>
       </c>
       <c r="R30" t="n">
-        <v>6999399</v>
+        <v>6999406</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4035,14 +4000,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4057,22 +4032,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122827232</v>
+        <v>122827147</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>98368</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4081,46 +4056,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528947</v>
+        <v>529019</v>
       </c>
       <c r="R31" t="n">
-        <v>6999334</v>
+        <v>6999321</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4147,9 +4131,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4164,22 +4163,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122827410</v>
+        <v>122827930</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>98368</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4188,38 +4187,52 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528970</v>
+        <v>529127</v>
       </c>
       <c r="R32" t="n">
-        <v>6999398</v>
+        <v>6999402</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4249,9 +4262,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4266,22 +4289,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122828216</v>
+        <v>122827466</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4313,17 +4336,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4332,13 +4355,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529096</v>
+        <v>529066</v>
       </c>
       <c r="R33" t="n">
-        <v>6999434</v>
+        <v>6999328</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4367,7 +4390,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4377,7 +4400,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4397,17 +4420,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122828006</v>
+        <v>122827597</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>98368</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4416,43 +4439,52 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529145</v>
+        <v>529078</v>
       </c>
       <c r="R34" t="n">
-        <v>6999399</v>
+        <v>6999325</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4482,14 +4514,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4504,22 +4541,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122828175</v>
+        <v>122827824</v>
       </c>
       <c r="B35" t="n">
-        <v>98365</v>
+        <v>57481</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4528,55 +4565,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529118</v>
+        <v>529074</v>
       </c>
       <c r="R35" t="n">
-        <v>6999441</v>
+        <v>6999358</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4605,7 +4633,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4615,7 +4643,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4630,22 +4663,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122828815</v>
+        <v>122827958</v>
       </c>
       <c r="B36" t="n">
-        <v>74847</v>
+        <v>77702</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4654,25 +4687,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4682,13 +4715,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529024</v>
+        <v>529113</v>
       </c>
       <c r="R36" t="n">
-        <v>6999406</v>
+        <v>6999364</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4717,7 +4750,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4727,12 +4760,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4747,22 +4780,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122828604</v>
+        <v>122828745</v>
       </c>
       <c r="B37" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4794,17 +4827,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4813,10 +4836,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529051</v>
+        <v>529035</v>
       </c>
       <c r="R37" t="n">
-        <v>6999391</v>
+        <v>6999405</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4846,19 +4869,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4873,22 +4886,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122827390</v>
+        <v>122827290</v>
       </c>
       <c r="B38" t="n">
-        <v>98365</v>
+        <v>79850</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4897,35 +4910,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4934,10 +4943,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529042</v>
+        <v>528951</v>
       </c>
       <c r="R38" t="n">
-        <v>6999393</v>
+        <v>6999355</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4967,19 +4976,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4994,22 +4993,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122827355</v>
+        <v>122828385</v>
       </c>
       <c r="B39" t="n">
-        <v>79848</v>
+        <v>77702</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5022,21 +5021,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5046,13 +5045,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528972</v>
+        <v>529065</v>
       </c>
       <c r="R39" t="n">
-        <v>6999362</v>
+        <v>6999450</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5079,9 +5078,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5096,22 +5110,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122827346</v>
+        <v>122828604</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>98368</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5120,38 +5134,52 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528959</v>
+        <v>529051</v>
       </c>
       <c r="R40" t="n">
-        <v>6999360</v>
+        <v>6999391</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5181,9 +5209,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5198,22 +5236,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122827824</v>
+        <v>122828216</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>98368</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5222,46 +5260,55 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529074</v>
+        <v>529096</v>
       </c>
       <c r="R41" t="n">
-        <v>6999358</v>
+        <v>6999434</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5290,7 +5337,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5300,12 +5347,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5320,22 +5362,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122828672</v>
+        <v>122827341</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>79851</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5344,52 +5386,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529025</v>
+        <v>528959</v>
       </c>
       <c r="R42" t="n">
-        <v>6999399</v>
+        <v>6999360</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5419,19 +5447,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5446,22 +5464,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827848</v>
+        <v>122827232</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>79850</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5470,40 +5488,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5512,13 +5521,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529118</v>
+        <v>528947</v>
       </c>
       <c r="R43" t="n">
-        <v>6999379</v>
+        <v>6999334</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5545,19 +5554,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5572,22 +5571,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122827686</v>
+        <v>122828537</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5624,13 +5623,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529073</v>
+        <v>529161</v>
       </c>
       <c r="R44" t="n">
-        <v>6999336</v>
+        <v>6999364</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5657,24 +5656,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Längsta bål 60 cm</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5685,26 +5674,51 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122827958</v>
+        <v>122827543</v>
       </c>
       <c r="B45" t="n">
-        <v>77699</v>
+        <v>57481</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5717,37 +5731,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529113</v>
+        <v>529010</v>
       </c>
       <c r="R45" t="n">
-        <v>6999364</v>
+        <v>6999427</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5776,7 +5795,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5786,12 +5805,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5818,10 +5837,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122827187</v>
+        <v>122827556</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>79850</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5830,50 +5849,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529024</v>
+        <v>528995</v>
       </c>
       <c r="R46" t="n">
-        <v>6999326</v>
+        <v>6999419</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5900,19 +5910,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5927,12 +5927,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
         <v>122827222</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>122827606</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>122828817</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122828006</v>
+        <v>122828604</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529145</v>
+        <v>529051</v>
       </c>
       <c r="R2" t="n">
-        <v>6999399</v>
+        <v>6999391</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,14 +762,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122827484</v>
+        <v>122827382</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +813,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528970</v>
+        <v>529080</v>
       </c>
       <c r="R3" t="n">
-        <v>6999399</v>
+        <v>6999334</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,14 +883,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +915,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827410</v>
+        <v>122827466</v>
       </c>
       <c r="B4" t="n">
-        <v>79850</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +939,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528970</v>
+        <v>529066</v>
       </c>
       <c r="R4" t="n">
-        <v>6999398</v>
+        <v>6999328</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,9 +1014,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,22 +1041,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122828769</v>
+        <v>122827543</v>
       </c>
       <c r="B5" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,34 +1069,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529028</v>
+        <v>529010</v>
       </c>
       <c r="R5" t="n">
-        <v>6999409</v>
+        <v>6999427</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1133,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,12 +1143,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,22 +1163,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122827382</v>
+        <v>122827825</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,47 +1187,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529080</v>
+        <v>529088</v>
       </c>
       <c r="R6" t="n">
-        <v>6999334</v>
+        <v>6999396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,24 +1253,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,22 +1275,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122827178</v>
+        <v>122827232</v>
       </c>
       <c r="B7" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,16 +1321,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528960</v>
+        <v>528947</v>
       </c>
       <c r="R7" t="n">
-        <v>6999325</v>
+        <v>6999334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122827848</v>
+        <v>122828672</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,7 +1429,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1400,13 +1448,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529118</v>
+        <v>529025</v>
       </c>
       <c r="R8" t="n">
-        <v>6999379</v>
+        <v>6999399</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,7 +1483,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1493,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1520,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122827280</v>
+        <v>122828745</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,26 +1558,16 @@
           <t>17</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529040</v>
+        <v>529035</v>
       </c>
       <c r="R9" t="n">
-        <v>6999362</v>
+        <v>6999405</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,24 +1597,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,22 +1614,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122827346</v>
+        <v>122827930</v>
       </c>
       <c r="B10" t="n">
-        <v>79850</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,38 +1638,52 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528959</v>
+        <v>529127</v>
       </c>
       <c r="R10" t="n">
-        <v>6999360</v>
+        <v>6999402</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,9 +1713,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,22 +1740,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122827366</v>
+        <v>122827556</v>
       </c>
       <c r="B11" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,10 +1792,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528972</v>
+        <v>528995</v>
       </c>
       <c r="R11" t="n">
-        <v>6999362</v>
+        <v>6999419</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827390</v>
+        <v>122827617</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>74866</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,50 +1866,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529042</v>
+        <v>528989</v>
       </c>
       <c r="R12" t="n">
-        <v>6999393</v>
+        <v>6999409</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1891,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1901,7 +1939,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,10 +1971,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122828175</v>
+        <v>122827597</v>
       </c>
       <c r="B13" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1963,12 +2006,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1982,13 +2025,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529118</v>
+        <v>529078</v>
       </c>
       <c r="R13" t="n">
-        <v>6999441</v>
+        <v>6999325</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2017,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2070,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827187</v>
+        <v>122827280</v>
       </c>
       <c r="B14" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,7 +2132,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2097,19 +2140,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529024</v>
+        <v>529040</v>
       </c>
       <c r="R14" t="n">
-        <v>6999326</v>
+        <v>6999362</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2138,7 +2186,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,7 +2196,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,7 +2216,7 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2175,10 +2228,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827686</v>
+        <v>122828216</v>
       </c>
       <c r="B15" t="n">
-        <v>78769</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,41 +2240,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529073</v>
+        <v>529096</v>
       </c>
       <c r="R15" t="n">
-        <v>6999336</v>
+        <v>6999434</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2250,7 +2317,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,12 +2327,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Längsta bål 60 cm</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122828442</v>
+        <v>122828175</v>
       </c>
       <c r="B16" t="n">
-        <v>77702</v>
+        <v>98370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,41 +2366,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529071</v>
+        <v>529118</v>
       </c>
       <c r="R16" t="n">
-        <v>6999422</v>
+        <v>6999441</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2367,7 +2443,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,12 +2453,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,10 +2480,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122827825</v>
+        <v>122827366</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,39 +2496,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529088</v>
+        <v>528972</v>
       </c>
       <c r="R17" t="n">
-        <v>6999396</v>
+        <v>6999362</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,11 +2556,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,10 +2582,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122828304</v>
+        <v>122827504</v>
       </c>
       <c r="B18" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2554,26 +2615,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529073</v>
+        <v>529070</v>
       </c>
       <c r="R18" t="n">
-        <v>6999451</v>
+        <v>6999301</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2605,7 +2657,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2615,7 +2667,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2647,10 +2699,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122827180</v>
+        <v>122827848</v>
       </c>
       <c r="B19" t="n">
-        <v>78769</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2659,41 +2711,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529019</v>
+        <v>529118</v>
       </c>
       <c r="R19" t="n">
-        <v>6999321</v>
+        <v>6999379</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2722,7 +2788,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2732,12 +2798,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,17 +2818,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122827275</v>
+        <v>122827824</v>
       </c>
       <c r="B20" t="n">
-        <v>74866</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2780,37 +2841,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529045</v>
+        <v>529074</v>
       </c>
       <c r="R20" t="n">
-        <v>6999365</v>
+        <v>6999358</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2839,7 +2905,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2849,12 +2915,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2881,10 +2947,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122828672</v>
+        <v>122827178</v>
       </c>
       <c r="B21" t="n">
-        <v>98368</v>
+        <v>79852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2893,52 +2959,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529025</v>
+        <v>528960</v>
       </c>
       <c r="R21" t="n">
-        <v>6999399</v>
+        <v>6999325</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2968,19 +3020,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2995,22 +3037,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122827642</v>
+        <v>122827341</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>79853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3019,52 +3061,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529076</v>
+        <v>528959</v>
       </c>
       <c r="R22" t="n">
-        <v>6999342</v>
+        <v>6999360</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3094,19 +3122,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3121,22 +3139,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122827504</v>
+        <v>122827275</v>
       </c>
       <c r="B23" t="n">
-        <v>78769</v>
+        <v>74866</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3149,21 +3167,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3173,10 +3191,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529070</v>
+        <v>529045</v>
       </c>
       <c r="R23" t="n">
-        <v>6999301</v>
+        <v>6999365</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3208,7 +3226,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3218,12 +3236,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3238,7 +3256,7 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3250,10 +3268,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122827285</v>
+        <v>122827958</v>
       </c>
       <c r="B24" t="n">
-        <v>79851</v>
+        <v>77704</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3266,21 +3284,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3290,13 +3308,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528951</v>
+        <v>529113</v>
       </c>
       <c r="R24" t="n">
-        <v>6999355</v>
+        <v>6999364</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3323,9 +3341,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3340,22 +3373,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122828804</v>
+        <v>122828769</v>
       </c>
       <c r="B25" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3368,39 +3401,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529036</v>
+        <v>529028</v>
       </c>
       <c r="R25" t="n">
-        <v>6999404</v>
+        <v>6999409</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3430,14 +3458,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3452,22 +3490,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122827355</v>
+        <v>122827410</v>
       </c>
       <c r="B26" t="n">
-        <v>79851</v>
+        <v>79852</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3480,21 +3518,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3504,10 +3542,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528972</v>
+        <v>528970</v>
       </c>
       <c r="R26" t="n">
-        <v>6999362</v>
+        <v>6999398</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3566,10 +3604,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122827617</v>
+        <v>122827290</v>
       </c>
       <c r="B27" t="n">
-        <v>74866</v>
+        <v>79852</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3582,37 +3620,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528989</v>
+        <v>528951</v>
       </c>
       <c r="R27" t="n">
-        <v>6999409</v>
+        <v>6999355</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3639,24 +3682,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3671,22 +3699,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122827718</v>
+        <v>122827180</v>
       </c>
       <c r="B28" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3699,34 +3727,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529085</v>
+        <v>529019</v>
       </c>
       <c r="R28" t="n">
-        <v>6999343</v>
+        <v>6999321</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3758,7 +3786,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3768,12 +3796,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3800,10 +3828,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122828091</v>
+        <v>122827390</v>
       </c>
       <c r="B29" t="n">
-        <v>78769</v>
+        <v>98370</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3812,41 +3840,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529125</v>
+        <v>529042</v>
       </c>
       <c r="R29" t="n">
-        <v>6999359</v>
+        <v>6999393</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,11 +3910,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3886,51 +3933,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122828815</v>
+        <v>122828304</v>
       </c>
       <c r="B30" t="n">
-        <v>74850</v>
+        <v>78771</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3939,38 +3961,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529024</v>
+        <v>529073</v>
       </c>
       <c r="R30" t="n">
-        <v>6999406</v>
+        <v>6999451</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4002,7 +4033,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4012,12 +4043,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4044,10 +4075,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122827147</v>
+        <v>122827686</v>
       </c>
       <c r="B31" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4056,55 +4087,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529019</v>
+        <v>529073</v>
       </c>
       <c r="R31" t="n">
-        <v>6999321</v>
+        <v>6999336</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4133,7 +4150,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4143,12 +4160,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 vinterståndare på marken i gammal granskog</t>
+          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4168,17 +4185,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122827930</v>
+        <v>122827718</v>
       </c>
       <c r="B32" t="n">
-        <v>98368</v>
+        <v>74866</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4187,52 +4204,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529127</v>
+        <v>529085</v>
       </c>
       <c r="R32" t="n">
-        <v>6999402</v>
+        <v>6999343</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4264,7 +4267,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4274,7 +4277,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4301,10 +4309,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122827466</v>
+        <v>122827187</v>
       </c>
       <c r="B33" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4336,7 +4344,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4344,24 +4352,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529066</v>
+        <v>529024</v>
       </c>
       <c r="R33" t="n">
-        <v>6999328</v>
+        <v>6999326</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4390,7 +4393,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4400,7 +4403,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4415,7 +4418,7 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -4427,10 +4430,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122827597</v>
+        <v>122828385</v>
       </c>
       <c r="B34" t="n">
-        <v>98368</v>
+        <v>77704</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4439,55 +4442,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529078</v>
+        <v>529065</v>
       </c>
       <c r="R34" t="n">
-        <v>6999325</v>
+        <v>6999450</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4516,7 +4505,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4526,7 +4515,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4553,10 +4547,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122827824</v>
+        <v>122827147</v>
       </c>
       <c r="B35" t="n">
-        <v>57481</v>
+        <v>98370</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4565,46 +4559,55 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529074</v>
+        <v>529019</v>
       </c>
       <c r="R35" t="n">
-        <v>6999358</v>
+        <v>6999321</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4633,7 +4636,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4643,12 +4646,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4663,22 +4666,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122827958</v>
+        <v>122827355</v>
       </c>
       <c r="B36" t="n">
-        <v>77702</v>
+        <v>79853</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4691,21 +4694,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4715,13 +4718,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529113</v>
+        <v>528972</v>
       </c>
       <c r="R36" t="n">
-        <v>6999364</v>
+        <v>6999362</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4748,24 +4751,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4780,22 +4768,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122828745</v>
+        <v>122828442</v>
       </c>
       <c r="B37" t="n">
-        <v>98368</v>
+        <v>77704</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4804,42 +4792,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529035</v>
+        <v>529071</v>
       </c>
       <c r="R37" t="n">
-        <v>6999405</v>
+        <v>6999422</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4869,9 +4853,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4886,22 +4885,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122827290</v>
+        <v>122827346</v>
       </c>
       <c r="B38" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4932,21 +4931,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528951</v>
+        <v>528959</v>
       </c>
       <c r="R38" t="n">
-        <v>6999355</v>
+        <v>6999360</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5005,10 +4999,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122828385</v>
+        <v>122828537</v>
       </c>
       <c r="B39" t="n">
-        <v>77702</v>
+        <v>78771</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5021,21 +5015,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5045,13 +5039,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529065</v>
+        <v>529161</v>
       </c>
       <c r="R39" t="n">
-        <v>6999450</v>
+        <v>6999364</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5078,24 +5072,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5106,26 +5090,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122828604</v>
+        <v>122828006</v>
       </c>
       <c r="B40" t="n">
-        <v>98368</v>
+        <v>57481</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5134,52 +5143,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529051</v>
+        <v>529145</v>
       </c>
       <c r="R40" t="n">
-        <v>6999391</v>
+        <v>6999399</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5209,19 +5209,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>16:27</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5236,22 +5231,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122828216</v>
+        <v>122828091</v>
       </c>
       <c r="B41" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5260,55 +5255,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529096</v>
+        <v>529125</v>
       </c>
       <c r="R41" t="n">
-        <v>6999434</v>
+        <v>6999359</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5335,21 +5316,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5358,26 +5329,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122827341</v>
+        <v>122827642</v>
       </c>
       <c r="B42" t="n">
-        <v>79851</v>
+        <v>98370</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5386,38 +5382,52 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528959</v>
+        <v>529076</v>
       </c>
       <c r="R42" t="n">
-        <v>6999360</v>
+        <v>6999342</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5447,9 +5457,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5464,22 +5484,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827232</v>
+        <v>122827285</v>
       </c>
       <c r="B43" t="n">
-        <v>79850</v>
+        <v>79853</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5492,39 +5512,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528947</v>
+        <v>528951</v>
       </c>
       <c r="R43" t="n">
-        <v>6999334</v>
+        <v>6999355</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5583,10 +5598,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122828537</v>
+        <v>122828815</v>
       </c>
       <c r="B44" t="n">
-        <v>78769</v>
+        <v>74850</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5595,25 +5610,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5623,13 +5638,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529161</v>
+        <v>529024</v>
       </c>
       <c r="R44" t="n">
-        <v>6999364</v>
+        <v>6999406</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5656,14 +5671,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5674,48 +5699,23 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122827543</v>
+        <v>122827484</v>
       </c>
       <c r="B45" t="n">
         <v>57481</v>
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529010</v>
+        <v>528970</v>
       </c>
       <c r="R45" t="n">
-        <v>6999427</v>
+        <v>6999399</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5793,19 +5793,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:57</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5825,22 +5815,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122827556</v>
+        <v>122828804</v>
       </c>
       <c r="B46" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5853,34 +5843,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528995</v>
+        <v>529036</v>
       </c>
       <c r="R46" t="n">
-        <v>6999419</v>
+        <v>6999404</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5913,6 +5908,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6074,7 +6074,7 @@
         <v>122827606</v>
       </c>
       <c r="B48" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>122828817</v>
       </c>
       <c r="B49" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122828604</v>
+        <v>122827543</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529051</v>
+        <v>529010</v>
       </c>
       <c r="R2" t="n">
-        <v>6999391</v>
+        <v>6999427</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,19 +785,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122827382</v>
+        <v>122828604</v>
       </c>
       <c r="B3" t="n">
         <v>98370</v>
@@ -836,7 +832,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -844,16 +840,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529080</v>
+        <v>529051</v>
       </c>
       <c r="R3" t="n">
-        <v>6999334</v>
+        <v>6999391</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827466</v>
+        <v>122827382</v>
       </c>
       <c r="B4" t="n">
         <v>98370</v>
@@ -962,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -970,21 +966,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529066</v>
+        <v>529080</v>
       </c>
       <c r="R4" t="n">
-        <v>6999328</v>
+        <v>6999334</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,7 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122827543</v>
+        <v>122827466</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,43 +1061,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529010</v>
+        <v>529066</v>
       </c>
       <c r="R5" t="n">
-        <v>6999427</v>
+        <v>6999328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1143,12 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,12 +1163,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122827556</v>
+        <v>122828175</v>
       </c>
       <c r="B11" t="n">
-        <v>79852</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,41 +1764,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528995</v>
+        <v>529118</v>
       </c>
       <c r="R11" t="n">
-        <v>6999419</v>
+        <v>6999441</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1825,9 +1839,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,22 +1866,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827617</v>
+        <v>122827556</v>
       </c>
       <c r="B12" t="n">
-        <v>74866</v>
+        <v>79852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,21 +1894,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1894,13 +1918,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528989</v>
+        <v>528995</v>
       </c>
       <c r="R12" t="n">
-        <v>6999409</v>
+        <v>6999419</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1927,24 +1951,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,22 +1968,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122827597</v>
+        <v>122827617</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>74866</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,55 +1992,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529078</v>
+        <v>528989</v>
       </c>
       <c r="R13" t="n">
-        <v>6999325</v>
+        <v>6999409</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2071,6 +2066,11 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2085,19 +2085,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827280</v>
+        <v>122827597</v>
       </c>
       <c r="B14" t="n">
         <v>98370</v>
@@ -2132,17 +2132,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529040</v>
+        <v>529078</v>
       </c>
       <c r="R14" t="n">
-        <v>6999362</v>
+        <v>6999325</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2196,12 +2196,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>3 vinterståndare i gammal granskog</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2228,7 +2223,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122828216</v>
+        <v>122827280</v>
       </c>
       <c r="B15" t="n">
         <v>98370</v>
@@ -2263,17 +2258,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2282,13 +2277,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529096</v>
+        <v>529040</v>
       </c>
       <c r="R15" t="n">
-        <v>6999434</v>
+        <v>6999362</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2317,7 +2312,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2327,7 +2322,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2354,7 +2354,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122828175</v>
+        <v>122828216</v>
       </c>
       <c r="B16" t="n">
         <v>98370</v>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529118</v>
+        <v>529096</v>
       </c>
       <c r="R16" t="n">
-        <v>6999441</v>
+        <v>6999434</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3268,10 +3268,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122827958</v>
+        <v>122828769</v>
       </c>
       <c r="B24" t="n">
-        <v>77704</v>
+        <v>79852</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3284,21 +3284,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3308,13 +3308,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529113</v>
+        <v>529028</v>
       </c>
       <c r="R24" t="n">
-        <v>6999364</v>
+        <v>6999409</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3373,7 +3373,7 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -3385,7 +3385,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122828769</v>
+        <v>122827410</v>
       </c>
       <c r="B25" t="n">
         <v>79852</v>
@@ -3425,10 +3425,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529028</v>
+        <v>528970</v>
       </c>
       <c r="R25" t="n">
-        <v>6999409</v>
+        <v>6999398</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3458,24 +3458,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3490,22 +3475,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122827410</v>
+        <v>122827958</v>
       </c>
       <c r="B26" t="n">
-        <v>79852</v>
+        <v>77704</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3518,21 +3503,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3542,13 +3527,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528970</v>
+        <v>529113</v>
       </c>
       <c r="R26" t="n">
-        <v>6999398</v>
+        <v>6999364</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3575,9 +3560,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3592,12 +3592,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122828815</v>
+        <v>122827484</v>
       </c>
       <c r="B44" t="n">
-        <v>74850</v>
+        <v>57481</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5610,38 +5610,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529024</v>
+        <v>528970</v>
       </c>
       <c r="R44" t="n">
-        <v>6999406</v>
+        <v>6999399</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5671,24 +5676,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5703,22 +5698,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122827484</v>
+        <v>122828815</v>
       </c>
       <c r="B45" t="n">
-        <v>57481</v>
+        <v>74850</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5727,43 +5722,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528970</v>
+        <v>529024</v>
       </c>
       <c r="R45" t="n">
-        <v>6999399</v>
+        <v>6999406</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5793,14 +5783,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5815,12 +5815,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 55465-2024 artfynd.xlsx
+++ b/artfynd/A 55465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122827543</v>
+        <v>122827617</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>74866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529010</v>
+        <v>528989</v>
       </c>
       <c r="R2" t="n">
-        <v>6999427</v>
+        <v>6999409</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122828604</v>
+        <v>122828216</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,17 +827,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529051</v>
+        <v>529096</v>
       </c>
       <c r="R3" t="n">
-        <v>6999391</v>
+        <v>6999434</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827382</v>
+        <v>122828442</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>77705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,47 +930,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529080</v>
+        <v>529071</v>
       </c>
       <c r="R4" t="n">
-        <v>6999334</v>
+        <v>6999422</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122827466</v>
+        <v>122827341</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>79854</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,52 +1047,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529066</v>
+        <v>528959</v>
       </c>
       <c r="R5" t="n">
-        <v>6999328</v>
+        <v>6999360</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,19 +1108,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122827825</v>
+        <v>122827366</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,39 +1153,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529088</v>
+        <v>528972</v>
       </c>
       <c r="R6" t="n">
-        <v>6999396</v>
+        <v>6999362</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,11 +1213,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122827232</v>
+        <v>122828091</v>
       </c>
       <c r="B7" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,42 +1255,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528947</v>
+        <v>529125</v>
       </c>
       <c r="R7" t="n">
-        <v>6999334</v>
+        <v>6999359</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1378,6 +1325,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1394,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122828672</v>
+        <v>122828006</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,49 +1378,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529025</v>
+        <v>529145</v>
       </c>
       <c r="R8" t="n">
         <v>6999399</v>
@@ -1481,19 +1444,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:29</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,22 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122828745</v>
+        <v>122827484</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,42 +1490,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529035</v>
+        <v>528970</v>
       </c>
       <c r="R9" t="n">
-        <v>6999405</v>
+        <v>6999399</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,6 +1559,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122827930</v>
+        <v>122827543</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,52 +1602,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529127</v>
+        <v>529010</v>
       </c>
       <c r="R10" t="n">
-        <v>6999402</v>
+        <v>6999427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1725,7 +1680,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,22 +1700,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122828175</v>
+        <v>122827410</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>79853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,55 +1724,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529118</v>
+        <v>528970</v>
       </c>
       <c r="R11" t="n">
-        <v>6999441</v>
+        <v>6999398</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1839,19 +1785,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,22 +1802,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122827556</v>
+        <v>122827825</v>
       </c>
       <c r="B12" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1894,34 +1830,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528995</v>
+        <v>529088</v>
       </c>
       <c r="R12" t="n">
-        <v>6999419</v>
+        <v>6999396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,6 +1895,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122827617</v>
+        <v>122827280</v>
       </c>
       <c r="B13" t="n">
-        <v>74866</v>
+        <v>98376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1992,41 +1938,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528989</v>
+        <v>529040</v>
       </c>
       <c r="R13" t="n">
-        <v>6999409</v>
+        <v>6999362</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2055,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2065,12 +2025,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2085,22 +2045,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122827597</v>
+        <v>122827466</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2132,17 +2092,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2151,10 +2111,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529078</v>
+        <v>529066</v>
       </c>
       <c r="R14" t="n">
-        <v>6999325</v>
+        <v>6999328</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2186,7 +2146,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2196,7 +2156,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2223,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122827280</v>
+        <v>122827556</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>79853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2235,52 +2195,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529040</v>
+        <v>528995</v>
       </c>
       <c r="R15" t="n">
-        <v>6999362</v>
+        <v>6999419</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2310,24 +2256,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>3 vinterståndare i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2342,22 +2273,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122828216</v>
+        <v>122828385</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>77705</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,55 +2297,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529096</v>
+        <v>529065</v>
       </c>
       <c r="R16" t="n">
-        <v>6999434</v>
+        <v>6999450</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2443,7 +2360,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2453,7 +2370,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2480,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122827366</v>
+        <v>122828537</v>
       </c>
       <c r="B17" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2496,21 +2418,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2520,13 +2442,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528972</v>
+        <v>529161</v>
       </c>
       <c r="R17" t="n">
-        <v>6999362</v>
+        <v>6999364</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2558,6 +2480,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2566,6 +2493,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2582,10 +2534,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122827504</v>
+        <v>122827958</v>
       </c>
       <c r="B18" t="n">
-        <v>78771</v>
+        <v>77705</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2598,21 +2550,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2622,13 +2574,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529070</v>
+        <v>529113</v>
       </c>
       <c r="R18" t="n">
-        <v>6999301</v>
+        <v>6999364</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2657,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2667,12 +2619,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2687,22 +2639,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122827848</v>
+        <v>122827285</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>79854</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2711,55 +2663,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529118</v>
+        <v>528951</v>
       </c>
       <c r="R19" t="n">
-        <v>6999379</v>
+        <v>6999355</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2786,19 +2724,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2813,22 +2741,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122827824</v>
+        <v>122827355</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>79854</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,42 +2769,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529074</v>
+        <v>528972</v>
       </c>
       <c r="R20" t="n">
-        <v>6999358</v>
+        <v>6999362</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2903,24 +2826,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,22 +2843,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122827178</v>
+        <v>122827232</v>
       </c>
       <c r="B21" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2981,16 +2889,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528960</v>
+        <v>528947</v>
       </c>
       <c r="R21" t="n">
-        <v>6999325</v>
+        <v>6999334</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3049,10 +2962,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122827341</v>
+        <v>122827275</v>
       </c>
       <c r="B22" t="n">
-        <v>79853</v>
+        <v>74866</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3065,21 +2978,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3089,10 +3002,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528959</v>
+        <v>529045</v>
       </c>
       <c r="R22" t="n">
-        <v>6999360</v>
+        <v>6999365</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3122,9 +3035,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3139,22 +3067,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122827275</v>
+        <v>122827848</v>
       </c>
       <c r="B23" t="n">
-        <v>74866</v>
+        <v>98376</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3163,41 +3091,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529045</v>
+        <v>529118</v>
       </c>
       <c r="R23" t="n">
-        <v>6999365</v>
+        <v>6999379</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3226,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3236,12 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3256,22 +3193,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122828769</v>
+        <v>122828745</v>
       </c>
       <c r="B24" t="n">
-        <v>79852</v>
+        <v>98376</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3280,38 +3217,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529028</v>
+        <v>529035</v>
       </c>
       <c r="R24" t="n">
-        <v>6999409</v>
+        <v>6999405</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3341,24 +3282,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3373,22 +3299,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122827410</v>
+        <v>122828815</v>
       </c>
       <c r="B25" t="n">
-        <v>79852</v>
+        <v>74850</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3397,25 +3323,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3425,10 +3351,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528970</v>
+        <v>529024</v>
       </c>
       <c r="R25" t="n">
-        <v>6999398</v>
+        <v>6999406</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3458,9 +3384,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3475,22 +3416,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122827958</v>
+        <v>122828804</v>
       </c>
       <c r="B26" t="n">
-        <v>77704</v>
+        <v>57481</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3503,37 +3444,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529113</v>
+        <v>529036</v>
       </c>
       <c r="R26" t="n">
-        <v>6999364</v>
+        <v>6999404</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3560,24 +3506,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3592,22 +3528,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122827290</v>
+        <v>122828672</v>
       </c>
       <c r="B27" t="n">
-        <v>79852</v>
+        <v>98376</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3616,31 +3552,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3649,10 +3594,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528951</v>
+        <v>529025</v>
       </c>
       <c r="R27" t="n">
-        <v>6999355</v>
+        <v>6999399</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3682,9 +3627,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3699,22 +3654,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122827180</v>
+        <v>122828175</v>
       </c>
       <c r="B28" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3723,41 +3678,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529019</v>
+        <v>529118</v>
       </c>
       <c r="R28" t="n">
-        <v>6999321</v>
+        <v>6999441</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3786,7 +3755,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3796,12 +3765,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3828,10 +3792,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122827390</v>
+        <v>122827290</v>
       </c>
       <c r="B29" t="n">
-        <v>98370</v>
+        <v>79853</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3840,35 +3804,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3877,10 +3837,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529042</v>
+        <v>528951</v>
       </c>
       <c r="R29" t="n">
-        <v>6999393</v>
+        <v>6999355</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3910,19 +3870,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3937,12 +3887,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3952,7 +3902,7 @@
         <v>122828304</v>
       </c>
       <c r="B30" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4075,10 +4025,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122827686</v>
+        <v>122827504</v>
       </c>
       <c r="B31" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4115,10 +4065,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529073</v>
+        <v>529070</v>
       </c>
       <c r="R31" t="n">
-        <v>6999336</v>
+        <v>6999301</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4150,7 +4100,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4160,12 +4110,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Längsta bål 60 cm</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4192,10 +4142,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122827718</v>
+        <v>122827390</v>
       </c>
       <c r="B32" t="n">
-        <v>74866</v>
+        <v>98376</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4204,38 +4154,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529085</v>
+        <v>529042</v>
       </c>
       <c r="R32" t="n">
-        <v>6999343</v>
+        <v>6999393</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4267,7 +4226,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4277,12 +4236,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal i gammal granskog</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4297,12 +4251,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4312,7 +4266,7 @@
         <v>122827187</v>
       </c>
       <c r="B33" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4423,17 +4377,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122828385</v>
+        <v>122827824</v>
       </c>
       <c r="B34" t="n">
-        <v>77704</v>
+        <v>57481</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4446,37 +4400,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529065</v>
+        <v>529074</v>
       </c>
       <c r="R34" t="n">
-        <v>6999450</v>
+        <v>6999358</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4505,7 +4464,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4515,12 +4474,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4535,22 +4494,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122827147</v>
+        <v>122827382</v>
       </c>
       <c r="B35" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4582,32 +4541,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529019</v>
+        <v>529080</v>
       </c>
       <c r="R35" t="n">
-        <v>6999321</v>
+        <v>6999334</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4636,7 +4590,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4646,12 +4600,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>1 vinterståndare på marken i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4678,10 +4632,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122827355</v>
+        <v>122827597</v>
       </c>
       <c r="B36" t="n">
-        <v>79853</v>
+        <v>98376</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4690,38 +4644,52 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528972</v>
+        <v>529078</v>
       </c>
       <c r="R36" t="n">
-        <v>6999362</v>
+        <v>6999325</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4751,9 +4719,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4768,22 +4746,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122828442</v>
+        <v>122827718</v>
       </c>
       <c r="B37" t="n">
-        <v>77704</v>
+        <v>74866</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4796,21 +4774,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4820,10 +4798,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529071</v>
+        <v>529085</v>
       </c>
       <c r="R37" t="n">
-        <v>6999422</v>
+        <v>6999343</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4855,7 +4833,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4865,12 +4843,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4890,17 +4868,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122827346</v>
+        <v>122827642</v>
       </c>
       <c r="B38" t="n">
-        <v>79852</v>
+        <v>98376</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4909,38 +4887,52 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528959</v>
+        <v>529076</v>
       </c>
       <c r="R38" t="n">
-        <v>6999360</v>
+        <v>6999342</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4970,9 +4962,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4987,22 +4989,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122828537</v>
+        <v>122827346</v>
       </c>
       <c r="B39" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5015,21 +5017,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5039,13 +5041,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529161</v>
+        <v>528959</v>
       </c>
       <c r="R39" t="n">
-        <v>6999364</v>
+        <v>6999360</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5077,11 +5079,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5090,31 +5087,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5131,10 +5103,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122828006</v>
+        <v>122827686</v>
       </c>
       <c r="B40" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5147,39 +5119,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529145</v>
+        <v>529073</v>
       </c>
       <c r="R40" t="n">
-        <v>6999399</v>
+        <v>6999336</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5209,14 +5176,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5231,22 +5208,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122828091</v>
+        <v>122827178</v>
       </c>
       <c r="B41" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5259,21 +5236,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5283,13 +5260,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529125</v>
+        <v>528960</v>
       </c>
       <c r="R41" t="n">
-        <v>6999359</v>
+        <v>6999325</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5329,31 +5306,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5370,10 +5322,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122827642</v>
+        <v>122827930</v>
       </c>
       <c r="B42" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5424,10 +5376,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529076</v>
+        <v>529127</v>
       </c>
       <c r="R42" t="n">
-        <v>6999342</v>
+        <v>6999402</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5459,7 +5411,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5469,7 +5421,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5496,10 +5448,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122827285</v>
+        <v>122827180</v>
       </c>
       <c r="B43" t="n">
-        <v>79853</v>
+        <v>78772</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5512,34 +5464,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528951</v>
+        <v>529019</v>
       </c>
       <c r="R43" t="n">
-        <v>6999355</v>
+        <v>6999321</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5569,9 +5521,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5586,22 +5553,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122827484</v>
+        <v>122828604</v>
       </c>
       <c r="B44" t="n">
-        <v>57481</v>
+        <v>98376</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5610,43 +5577,52 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528970</v>
+        <v>529051</v>
       </c>
       <c r="R44" t="n">
-        <v>6999399</v>
+        <v>6999391</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5676,14 +5652,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5698,22 +5679,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122828815</v>
+        <v>122827147</v>
       </c>
       <c r="B45" t="n">
-        <v>74850</v>
+        <v>98376</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5722,41 +5703,55 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529024</v>
+        <v>529019</v>
       </c>
       <c r="R45" t="n">
-        <v>6999406</v>
+        <v>6999321</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5785,7 +5780,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5795,12 +5790,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På sälgstubbe</t>
+          <t>1 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5827,10 +5822,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122828804</v>
+        <v>122828769</v>
       </c>
       <c r="B46" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5843,39 +5838,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Stugubäckmyran, Stugubäckmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529036</v>
+        <v>529028</v>
       </c>
       <c r="R46" t="n">
-        <v>6999404</v>
+        <v>6999409</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5905,14 +5895,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälgstubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5927,12 +5927,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6074,7 +6074,7 @@
         <v>122827606</v>
       </c>
       <c r="B48" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>122828817</v>
       </c>
       <c r="B49" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
